--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -1,98 +1,310 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.0"/>
-  <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\"/>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24375" windowHeight="10215" tabRatio="500"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-  </x:sheets>
-  <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
-</x:workbook>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B516D115-6240-499C-A90D-97DBE697F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4440" yWindow="1420" windowWidth="20360" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+  <si>
+    <t>EnemyId</t>
+  </si>
+  <si>
+    <t>Archetype</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
+    <t>AttackDamage</t>
+  </si>
+  <si>
+    <t>AttackWindup</t>
+  </si>
+  <si>
+    <t>AttackActiveDuration</t>
+  </si>
+  <si>
+    <t>AttackCooldown</t>
+  </si>
+  <si>
+    <t>AttackAreaRadius</t>
+  </si>
+  <si>
+    <t>ApproachRange</t>
+  </si>
+  <si>
+    <t>FacingTurnDelay</t>
+  </si>
+  <si>
+    <t>PostAttackFacingLock</t>
+  </si>
+  <si>
+    <t>KillExperience</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>BaseMaxHp</t>
+  </si>
+  <si>
+    <t>HpGrowthRate</t>
+  </si>
+  <si>
+    <t>LevelDifficultyOffset</t>
+  </si>
+  <si>
+    <t>CombatProfileId</t>
+  </si>
+  <si>
+    <t>ShowHpBar</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>적 ID</t>
+  </si>
+  <si>
+    <t>유형</t>
+  </si>
+  <si>
+    <t>이동 속도</t>
+  </si>
+  <si>
+    <t>공격 사거리</t>
+  </si>
+  <si>
+    <t>공격 피해</t>
+  </si>
+  <si>
+    <t>공격 준비 시간</t>
+  </si>
+  <si>
+    <t>공격 판정 시간</t>
+  </si>
+  <si>
+    <t>공격 재사용 대기</t>
+  </si>
+  <si>
+    <t>공격 범위 반경</t>
+  </si>
+  <si>
+    <t>접근 거리</t>
+  </si>
+  <si>
+    <t>방향 전환 지연</t>
+  </si>
+  <si>
+    <t>공격 후 방향 고정</t>
+  </si>
+  <si>
+    <t>처치 경험치</t>
+  </si>
+  <si>
+    <t>점수</t>
+  </si>
+  <si>
+    <t>기본 최대 체력</t>
+  </si>
+  <si>
+    <t>체력 성장률</t>
+  </si>
+  <si>
+    <t>레벨 난이도 보정</t>
+  </si>
+  <si>
+    <t>전투 프로필 ID</t>
+  </si>
+  <si>
+    <t>체력바 표시</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0" iLevel="0"/>
-  </x:cellStyles>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF35453B"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF48614F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+  </fonts>
+  <fills count="5">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCEAD4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF4E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48614F"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D4C5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D4C5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D4C5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D4C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{86C82044-7509-440E-905E-47CDB9439273}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0"/>
-</x:styleSheet>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="3a3c84"/>
+        <a:srgbClr val="3A3C84"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="faf3db"/>
+        <a:srgbClr val="FAF3DB"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="6182d6"/>
+        <a:srgbClr val="6182D6"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ff843a"/>
+        <a:srgbClr val="FF843A"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="b2b2b2"/>
+        <a:srgbClr val="B2B2B2"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffd700"/>
+        <a:srgbClr val="FFD700"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="289b6e"/>
+        <a:srgbClr val="289B6E"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="9d5cbb"/>
+        <a:srgbClr val="9D5CBB"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -110,7 +322,7 @@
         <a:cs typeface="HNC_GO_B_HINT_GS"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -306,13 +518,254 @@
       <a:lstStyle/>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:A1"/>
-  <x:sheetData/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30568285-19A2-44D7-AD56-A2F1768F5D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB19DCA-CADB-49EE-9751-1B89B2B84998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="1420" windowWidth="20360" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5120" yWindow="2100" windowWidth="20360" windowHeight="13180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,41 +20,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>폭발 화염구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+  <si>
+    <r>
+      <t>폭발</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화염구</t>
+    </r>
   </si>
   <si>
     <t>Grade</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Range</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Dot ATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>duration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대지 마법</t>
+  </si>
+  <si>
+    <t>Knockback</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>연쇄 번개</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>대못박기</t>
+  </si>
+  <si>
+    <t>수리마법</t>
+  </si>
+  <si>
+    <t>Heal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -83,8 +119,16 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -94,6 +138,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF48614F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00CC00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,14 +175,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{86C82044-7509-440E-905E-47CDB9439273}"/>
@@ -140,6 +200,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF008000"/>
+      <color rgb="FF00CC00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -407,7 +473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -417,27 +483,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -451,44 +515,302 @@
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
+      <c r="C2" s="3">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="B3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" s="6" customFormat="1">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" s="6" customFormat="1">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2">
-        <v>3</v>
-      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2EAAAD5D8F598F46F82CEF94EFDB587BC8B61F8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{D0FB02F3-AC79-444D-A0D3-EFF216B50AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C20CB0B9-25FA-4AD1-AD87-F85FD0D4A428}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="1910" windowWidth="20360" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <r>
       <rPr>
@@ -85,12 +83,6 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.5x + 10</t>
-  </si>
-  <si>
-    <t>0.01x + 2</t>
-  </si>
-  <si>
     <t>0.2x + 3</t>
   </si>
   <si>
@@ -103,48 +95,30 @@
     <t>all</t>
   </si>
   <si>
-    <t>0.8x + 15</t>
-  </si>
-  <si>
     <t>연쇄 번개</t>
   </si>
   <si>
     <t>count</t>
   </si>
   <si>
-    <t>0.4x + 3</t>
-  </si>
-  <si>
     <t>대못박기</t>
   </si>
   <si>
-    <t>0.6x + 20</t>
-  </si>
-  <si>
     <t>수리마법</t>
   </si>
   <si>
     <t>Heal</t>
   </si>
   <si>
-    <t>0.8x + 20</t>
-  </si>
-  <si>
     <t>역병 마법</t>
   </si>
   <si>
-    <t>0.2x + 5</t>
-  </si>
-  <si>
     <t>고드름 창</t>
   </si>
   <si>
     <t>Slow</t>
   </si>
   <si>
-    <t>0.6x+5</t>
-  </si>
-  <si>
     <t>x*0.01+0.3</t>
   </si>
   <si>
@@ -154,15 +128,9 @@
     <t>대폭발</t>
   </si>
   <si>
-    <t>2x+100</t>
-  </si>
-  <si>
     <t>30(반올림)</t>
   </si>
   <si>
-    <t>0.5x+30</t>
-  </si>
-  <si>
     <t>섬광탄</t>
   </si>
   <si>
@@ -257,9 +225,6 @@
   </si>
   <si>
     <t>skill_009</t>
-  </si>
-  <si>
-    <t>스톱워치 숫자를 반올림한 결과에 따라 적에게 피해를 줍니다.</t>
   </si>
   <si>
     <t>skill_010</t>
@@ -342,6 +307,197 @@
   </si>
   <si>
     <t>Bad</t>
+  </si>
+  <si>
+    <t>2x + 20</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1x + 2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3x + 18</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4x + 15</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x + 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>x + 12</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5x+20</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5x+12</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스톱워치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반올림한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF102A43"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6x+25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -351,7 +507,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.##;\-0.##;0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -442,6 +598,26 @@
       <color rgb="FFFFFFFF"/>
       <name val="돋움"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF102A43"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF102A43"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF102A43"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="14">
@@ -577,7 +753,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -704,6 +880,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -951,20 +1130,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.9140625" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.4140625" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="8" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" customWidth="1"/>
+    <col min="6" max="8" width="8.69921875" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="26" width="8.6640625" customWidth="1"/>
+    <col min="11" max="26" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16" customHeight="1">
+    <row r="1" spans="1:26" ht="16.05" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +1167,7 @@
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="35" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J1" s="35"/>
       <c r="K1" s="2"/>
@@ -1000,30 +1179,30 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="19" customHeight="1">
+    <row r="2" spans="1:26" ht="19.05" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="7"/>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3">
         <v>5</v>
       </c>
       <c r="F2" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3">
         <v>3</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="32" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
@@ -1039,14 +1218,14 @@
       <c r="B3" s="7"/>
       <c r="C3" s="3"/>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="33" t="str">
@@ -1066,9 +1245,9 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="13.4" customHeight="1">
+    <row r="4" spans="1:26" ht="13.35" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1083,7 +1262,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1119,10 +1298,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3">
         <v>3</v>
@@ -1151,11 +1330,11 @@
       <c r="B6" s="7"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1176,9 +1355,9 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="16" customHeight="1">
+    <row r="7" spans="1:26" ht="16.05" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>1</v>
@@ -1190,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -1221,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3">
         <v>7</v>
@@ -1230,7 +1409,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="36" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J8" s="36"/>
       <c r="K8" s="3"/>
@@ -1247,7 +1426,7 @@
       <c r="B9" s="7"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1264,9 +1443,9 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="10.4" customHeight="1">
+    <row r="10" spans="1:26" ht="10.35" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>1</v>
@@ -1300,14 +1479,14 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="13" customHeight="1">
+    <row r="11" spans="1:26" ht="13.05" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="7"/>
       <c r="C11" s="3">
         <v>2</v>
       </c>
       <c r="D11" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1324,12 +1503,12 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="14" customHeight="1">
+    <row r="12" spans="1:26" ht="13.95" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="7"/>
       <c r="C12" s="3"/>
       <c r="D12" s="6" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1346,9 +1525,9 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="10" customHeight="1">
+    <row r="13" spans="1:26" ht="10.050000000000001" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>1</v>
@@ -1357,7 +1536,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1400,15 +1579,15 @@
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:26" ht="13.4" customHeight="1">
+    <row r="16" spans="1:26" ht="13.35" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>1</v>
@@ -1444,14 +1623,14 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="12.65" customHeight="1">
+    <row r="17" spans="1:26" ht="12.6" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6">
         <v>3</v>
       </c>
       <c r="D17" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" s="6">
         <v>3</v>
@@ -1459,22 +1638,22 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:26" ht="14.65" customHeight="1">
+    <row r="18" spans="1:26" ht="14.7" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:26" ht="11" customHeight="1">
+    <row r="19" spans="1:26" ht="10.95" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1</v>
@@ -1486,7 +1665,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>6</v>
@@ -1519,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E20" s="6">
         <v>0.3</v>
@@ -1529,24 +1708,24 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:26" ht="13.4" customHeight="1">
+    <row r="21" spans="1:26" ht="13.35" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:26" ht="11.65" customHeight="1">
+    <row r="22" spans="1:26" ht="11.7" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>1</v>
@@ -1580,33 +1759,33 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="15.4" customHeight="1">
+    <row r="23" spans="1:26" ht="15.45" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6">
         <v>4</v>
       </c>
       <c r="D23" s="6">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:26" ht="11" customHeight="1">
+    <row r="24" spans="1:26" ht="10.95" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:26" ht="11" customHeight="1">
+    <row r="25" spans="1:26" ht="10.95" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>1</v>
@@ -1640,14 +1819,14 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="10" customHeight="1">
+    <row r="26" spans="1:26" ht="10.050000000000001" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6">
         <v>4</v>
       </c>
       <c r="D26" s="6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1658,15 +1837,15 @@
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="6" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:26" ht="11" customHeight="1">
+    <row r="28" spans="1:26" ht="10.95" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>1</v>
@@ -1700,7 +1879,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="9.4" customHeight="1">
+    <row r="29" spans="1:26" ht="9.4499999999999993" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6">
@@ -1713,20 +1892,20 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:26" ht="9.65" customHeight="1">
+    <row r="30" spans="1:26" ht="9.6" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:26" ht="11" customHeight="1">
+    <row r="31" spans="1:26" ht="10.95" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>1</v>
@@ -1758,7 +1937,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="15.4" customHeight="1">
+    <row r="32" spans="1:26" ht="15.45" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6">
@@ -1769,974 +1948,974 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" ht="4.9000000000000004" customHeight="1"/>
-    <row r="34" ht="4.9000000000000004" customHeight="1"/>
-    <row r="35" ht="4.9000000000000004" customHeight="1"/>
-    <row r="36" ht="4.9000000000000004" customHeight="1"/>
-    <row r="37" ht="4.9000000000000004" customHeight="1"/>
-    <row r="38" ht="4.9000000000000004" customHeight="1"/>
-    <row r="39" ht="4.9000000000000004" customHeight="1"/>
-    <row r="40" ht="4.9000000000000004" customHeight="1"/>
-    <row r="41" ht="4.9000000000000004" customHeight="1"/>
-    <row r="42" ht="4.9000000000000004" customHeight="1"/>
-    <row r="43" ht="4.9000000000000004" customHeight="1"/>
-    <row r="44" ht="4.9000000000000004" customHeight="1"/>
-    <row r="45" ht="4.9000000000000004" customHeight="1"/>
-    <row r="46" ht="4.9000000000000004" customHeight="1"/>
-    <row r="47" ht="4.9000000000000004" customHeight="1"/>
-    <row r="48" ht="4.9000000000000004" customHeight="1"/>
-    <row r="49" ht="4.9000000000000004" customHeight="1"/>
-    <row r="50" ht="4.9000000000000004" customHeight="1"/>
-    <row r="51" ht="4.9000000000000004" customHeight="1"/>
-    <row r="52" ht="4.9000000000000004" customHeight="1"/>
-    <row r="53" ht="4.9000000000000004" customHeight="1"/>
-    <row r="54" ht="4.9000000000000004" customHeight="1"/>
-    <row r="55" ht="4.9000000000000004" customHeight="1"/>
-    <row r="56" ht="4.9000000000000004" customHeight="1"/>
-    <row r="57" ht="4.9000000000000004" customHeight="1"/>
-    <row r="58" ht="4.9000000000000004" customHeight="1"/>
-    <row r="59" ht="4.9000000000000004" customHeight="1"/>
-    <row r="60" ht="4.9000000000000004" customHeight="1"/>
-    <row r="61" ht="4.9000000000000004" customHeight="1"/>
-    <row r="62" ht="4.9000000000000004" customHeight="1"/>
-    <row r="63" ht="4.9000000000000004" customHeight="1"/>
-    <row r="64" ht="4.9000000000000004" customHeight="1"/>
-    <row r="65" ht="4.9000000000000004" customHeight="1"/>
-    <row r="66" ht="4.9000000000000004" customHeight="1"/>
-    <row r="67" ht="4.9000000000000004" customHeight="1"/>
-    <row r="68" ht="4.9000000000000004" customHeight="1"/>
-    <row r="69" ht="4.9000000000000004" customHeight="1"/>
-    <row r="70" ht="4.9000000000000004" customHeight="1"/>
-    <row r="71" ht="4.9000000000000004" customHeight="1"/>
-    <row r="72" ht="4.9000000000000004" customHeight="1"/>
-    <row r="73" ht="4.9000000000000004" customHeight="1"/>
-    <row r="74" ht="4.9000000000000004" customHeight="1"/>
-    <row r="75" ht="4.9000000000000004" customHeight="1"/>
-    <row r="76" ht="4.9000000000000004" customHeight="1"/>
-    <row r="77" ht="4.9000000000000004" customHeight="1"/>
-    <row r="78" ht="4.9000000000000004" customHeight="1"/>
-    <row r="79" ht="4.9000000000000004" customHeight="1"/>
-    <row r="80" ht="4.9000000000000004" customHeight="1"/>
-    <row r="81" ht="4.9000000000000004" customHeight="1"/>
-    <row r="82" ht="4.9000000000000004" customHeight="1"/>
-    <row r="83" ht="4.9000000000000004" customHeight="1"/>
-    <row r="84" ht="4.9000000000000004" customHeight="1"/>
-    <row r="85" ht="4.9000000000000004" customHeight="1"/>
-    <row r="86" ht="4.9000000000000004" customHeight="1"/>
-    <row r="87" ht="4.9000000000000004" customHeight="1"/>
-    <row r="88" ht="4.9000000000000004" customHeight="1"/>
-    <row r="89" ht="4.9000000000000004" customHeight="1"/>
-    <row r="90" ht="4.9000000000000004" customHeight="1"/>
-    <row r="91" ht="4.9000000000000004" customHeight="1"/>
-    <row r="92" ht="4.9000000000000004" customHeight="1"/>
-    <row r="93" ht="4.9000000000000004" customHeight="1"/>
-    <row r="94" ht="4.9000000000000004" customHeight="1"/>
-    <row r="95" ht="4.9000000000000004" customHeight="1"/>
-    <row r="96" ht="4.9000000000000004" customHeight="1"/>
-    <row r="97" ht="4.9000000000000004" customHeight="1"/>
-    <row r="98" ht="4.9000000000000004" customHeight="1"/>
-    <row r="99" ht="4.9000000000000004" customHeight="1"/>
-    <row r="100" ht="4.9000000000000004" customHeight="1"/>
-    <row r="101" ht="4.9000000000000004" customHeight="1"/>
-    <row r="102" ht="4.9000000000000004" customHeight="1"/>
-    <row r="103" ht="4.9000000000000004" customHeight="1"/>
-    <row r="104" ht="4.9000000000000004" customHeight="1"/>
-    <row r="105" ht="4.9000000000000004" customHeight="1"/>
-    <row r="106" ht="4.9000000000000004" customHeight="1"/>
-    <row r="107" ht="4.9000000000000004" customHeight="1"/>
-    <row r="108" ht="4.9000000000000004" customHeight="1"/>
-    <row r="109" ht="4.9000000000000004" customHeight="1"/>
-    <row r="110" ht="4.9000000000000004" customHeight="1"/>
-    <row r="111" ht="4.9000000000000004" customHeight="1"/>
-    <row r="112" ht="4.9000000000000004" customHeight="1"/>
-    <row r="113" ht="4.9000000000000004" customHeight="1"/>
-    <row r="114" ht="4.9000000000000004" customHeight="1"/>
-    <row r="115" ht="4.9000000000000004" customHeight="1"/>
-    <row r="116" ht="4.9000000000000004" customHeight="1"/>
-    <row r="117" ht="4.9000000000000004" customHeight="1"/>
-    <row r="118" ht="4.9000000000000004" customHeight="1"/>
-    <row r="119" ht="4.9000000000000004" customHeight="1"/>
-    <row r="120" ht="4.9000000000000004" customHeight="1"/>
-    <row r="121" ht="4.9000000000000004" customHeight="1"/>
-    <row r="122" ht="4.9000000000000004" customHeight="1"/>
-    <row r="123" ht="4.9000000000000004" customHeight="1"/>
-    <row r="124" ht="4.9000000000000004" customHeight="1"/>
-    <row r="125" ht="4.9000000000000004" customHeight="1"/>
-    <row r="126" ht="4.9000000000000004" customHeight="1"/>
-    <row r="127" ht="4.9000000000000004" customHeight="1"/>
-    <row r="128" ht="4.9000000000000004" customHeight="1"/>
-    <row r="129" ht="4.9000000000000004" customHeight="1"/>
-    <row r="130" ht="4.9000000000000004" customHeight="1"/>
-    <row r="131" ht="4.9000000000000004" customHeight="1"/>
-    <row r="132" ht="4.9000000000000004" customHeight="1"/>
-    <row r="133" ht="4.9000000000000004" customHeight="1"/>
-    <row r="134" ht="4.9000000000000004" customHeight="1"/>
-    <row r="135" ht="4.9000000000000004" customHeight="1"/>
-    <row r="136" ht="4.9000000000000004" customHeight="1"/>
-    <row r="137" ht="4.9000000000000004" customHeight="1"/>
-    <row r="138" ht="4.9000000000000004" customHeight="1"/>
-    <row r="139" ht="4.9000000000000004" customHeight="1"/>
-    <row r="140" ht="4.9000000000000004" customHeight="1"/>
-    <row r="141" ht="4.9000000000000004" customHeight="1"/>
-    <row r="142" ht="4.9000000000000004" customHeight="1"/>
-    <row r="143" ht="4.9000000000000004" customHeight="1"/>
-    <row r="144" ht="4.9000000000000004" customHeight="1"/>
-    <row r="145" ht="4.9000000000000004" customHeight="1"/>
-    <row r="146" ht="4.9000000000000004" customHeight="1"/>
-    <row r="147" ht="4.9000000000000004" customHeight="1"/>
-    <row r="148" ht="4.9000000000000004" customHeight="1"/>
-    <row r="149" ht="4.9000000000000004" customHeight="1"/>
-    <row r="150" ht="4.9000000000000004" customHeight="1"/>
-    <row r="151" ht="4.9000000000000004" customHeight="1"/>
-    <row r="152" ht="4.9000000000000004" customHeight="1"/>
-    <row r="153" ht="4.9000000000000004" customHeight="1"/>
-    <row r="154" ht="4.9000000000000004" customHeight="1"/>
-    <row r="155" ht="4.9000000000000004" customHeight="1"/>
-    <row r="156" ht="4.9000000000000004" customHeight="1"/>
-    <row r="157" ht="4.9000000000000004" customHeight="1"/>
-    <row r="158" ht="4.9000000000000004" customHeight="1"/>
-    <row r="159" ht="4.9000000000000004" customHeight="1"/>
-    <row r="160" ht="4.9000000000000004" customHeight="1"/>
-    <row r="161" ht="4.9000000000000004" customHeight="1"/>
-    <row r="162" ht="4.9000000000000004" customHeight="1"/>
-    <row r="163" ht="4.9000000000000004" customHeight="1"/>
-    <row r="164" ht="4.9000000000000004" customHeight="1"/>
-    <row r="165" ht="4.9000000000000004" customHeight="1"/>
-    <row r="166" ht="4.9000000000000004" customHeight="1"/>
-    <row r="167" ht="4.9000000000000004" customHeight="1"/>
-    <row r="168" ht="4.9000000000000004" customHeight="1"/>
-    <row r="169" ht="4.9000000000000004" customHeight="1"/>
-    <row r="170" ht="4.9000000000000004" customHeight="1"/>
-    <row r="171" ht="4.9000000000000004" customHeight="1"/>
-    <row r="172" ht="4.9000000000000004" customHeight="1"/>
-    <row r="173" ht="4.9000000000000004" customHeight="1"/>
-    <row r="174" ht="4.9000000000000004" customHeight="1"/>
-    <row r="175" ht="4.9000000000000004" customHeight="1"/>
-    <row r="176" ht="4.9000000000000004" customHeight="1"/>
-    <row r="177" ht="4.9000000000000004" customHeight="1"/>
-    <row r="178" ht="4.9000000000000004" customHeight="1"/>
-    <row r="179" ht="4.9000000000000004" customHeight="1"/>
-    <row r="180" ht="4.9000000000000004" customHeight="1"/>
-    <row r="181" ht="4.9000000000000004" customHeight="1"/>
-    <row r="182" ht="4.9000000000000004" customHeight="1"/>
-    <row r="183" ht="4.9000000000000004" customHeight="1"/>
-    <row r="184" ht="4.9000000000000004" customHeight="1"/>
-    <row r="185" ht="4.9000000000000004" customHeight="1"/>
-    <row r="186" ht="4.9000000000000004" customHeight="1"/>
-    <row r="187" ht="4.9000000000000004" customHeight="1"/>
-    <row r="188" ht="4.9000000000000004" customHeight="1"/>
-    <row r="189" ht="4.9000000000000004" customHeight="1"/>
-    <row r="190" ht="4.9000000000000004" customHeight="1"/>
-    <row r="191" ht="4.9000000000000004" customHeight="1"/>
-    <row r="192" ht="4.9000000000000004" customHeight="1"/>
-    <row r="193" ht="4.9000000000000004" customHeight="1"/>
-    <row r="194" ht="4.9000000000000004" customHeight="1"/>
-    <row r="195" ht="4.9000000000000004" customHeight="1"/>
-    <row r="196" ht="4.9000000000000004" customHeight="1"/>
-    <row r="197" ht="4.9000000000000004" customHeight="1"/>
-    <row r="198" ht="4.9000000000000004" customHeight="1"/>
-    <row r="199" ht="4.9000000000000004" customHeight="1"/>
-    <row r="200" ht="4.9000000000000004" customHeight="1"/>
-    <row r="201" ht="4.9000000000000004" customHeight="1"/>
-    <row r="202" ht="4.9000000000000004" customHeight="1"/>
-    <row r="203" ht="4.9000000000000004" customHeight="1"/>
-    <row r="204" ht="4.9000000000000004" customHeight="1"/>
-    <row r="205" ht="4.9000000000000004" customHeight="1"/>
-    <row r="206" ht="4.9000000000000004" customHeight="1"/>
-    <row r="207" ht="4.9000000000000004" customHeight="1"/>
-    <row r="208" ht="4.9000000000000004" customHeight="1"/>
-    <row r="209" ht="4.9000000000000004" customHeight="1"/>
-    <row r="210" ht="4.9000000000000004" customHeight="1"/>
-    <row r="211" ht="4.9000000000000004" customHeight="1"/>
-    <row r="212" ht="4.9000000000000004" customHeight="1"/>
-    <row r="213" ht="4.9000000000000004" customHeight="1"/>
-    <row r="214" ht="4.9000000000000004" customHeight="1"/>
-    <row r="215" ht="4.9000000000000004" customHeight="1"/>
-    <row r="216" ht="4.9000000000000004" customHeight="1"/>
-    <row r="217" ht="4.9000000000000004" customHeight="1"/>
-    <row r="218" ht="4.9000000000000004" customHeight="1"/>
-    <row r="219" ht="4.9000000000000004" customHeight="1"/>
-    <row r="220" ht="4.9000000000000004" customHeight="1"/>
-    <row r="221" ht="4.9000000000000004" customHeight="1"/>
-    <row r="222" ht="4.9000000000000004" customHeight="1"/>
-    <row r="223" ht="4.9000000000000004" customHeight="1"/>
-    <row r="224" ht="4.9000000000000004" customHeight="1"/>
-    <row r="225" ht="4.9000000000000004" customHeight="1"/>
-    <row r="226" ht="4.9000000000000004" customHeight="1"/>
-    <row r="227" ht="4.9000000000000004" customHeight="1"/>
-    <row r="228" ht="4.9000000000000004" customHeight="1"/>
-    <row r="229" ht="4.9000000000000004" customHeight="1"/>
-    <row r="230" ht="4.9000000000000004" customHeight="1"/>
-    <row r="231" ht="4.9000000000000004" customHeight="1"/>
-    <row r="232" ht="4.9000000000000004" customHeight="1"/>
-    <row r="233" ht="4.9000000000000004" customHeight="1"/>
-    <row r="234" ht="4.9000000000000004" customHeight="1"/>
-    <row r="235" ht="4.9000000000000004" customHeight="1"/>
-    <row r="236" ht="4.9000000000000004" customHeight="1"/>
-    <row r="237" ht="4.9000000000000004" customHeight="1"/>
-    <row r="238" ht="4.9000000000000004" customHeight="1"/>
-    <row r="239" ht="4.9000000000000004" customHeight="1"/>
-    <row r="240" ht="4.9000000000000004" customHeight="1"/>
-    <row r="241" ht="4.9000000000000004" customHeight="1"/>
-    <row r="242" ht="4.9000000000000004" customHeight="1"/>
-    <row r="243" ht="4.9000000000000004" customHeight="1"/>
-    <row r="244" ht="4.9000000000000004" customHeight="1"/>
-    <row r="245" ht="4.9000000000000004" customHeight="1"/>
-    <row r="246" ht="4.9000000000000004" customHeight="1"/>
-    <row r="247" ht="4.9000000000000004" customHeight="1"/>
-    <row r="248" ht="4.9000000000000004" customHeight="1"/>
-    <row r="249" ht="4.9000000000000004" customHeight="1"/>
-    <row r="250" ht="4.9000000000000004" customHeight="1"/>
-    <row r="251" ht="4.9000000000000004" customHeight="1"/>
-    <row r="252" ht="4.9000000000000004" customHeight="1"/>
-    <row r="253" ht="4.9000000000000004" customHeight="1"/>
-    <row r="254" ht="4.9000000000000004" customHeight="1"/>
-    <row r="255" ht="4.9000000000000004" customHeight="1"/>
-    <row r="256" ht="4.9000000000000004" customHeight="1"/>
-    <row r="257" ht="4.9000000000000004" customHeight="1"/>
-    <row r="258" ht="4.9000000000000004" customHeight="1"/>
-    <row r="259" ht="4.9000000000000004" customHeight="1"/>
-    <row r="260" ht="4.9000000000000004" customHeight="1"/>
-    <row r="261" ht="4.9000000000000004" customHeight="1"/>
-    <row r="262" ht="4.9000000000000004" customHeight="1"/>
-    <row r="263" ht="4.9000000000000004" customHeight="1"/>
-    <row r="264" ht="4.9000000000000004" customHeight="1"/>
-    <row r="265" ht="4.9000000000000004" customHeight="1"/>
-    <row r="266" ht="4.9000000000000004" customHeight="1"/>
-    <row r="267" ht="4.9000000000000004" customHeight="1"/>
-    <row r="268" ht="4.9000000000000004" customHeight="1"/>
-    <row r="269" ht="4.9000000000000004" customHeight="1"/>
-    <row r="270" ht="4.9000000000000004" customHeight="1"/>
-    <row r="271" ht="4.9000000000000004" customHeight="1"/>
-    <row r="272" ht="4.9000000000000004" customHeight="1"/>
-    <row r="273" ht="4.9000000000000004" customHeight="1"/>
-    <row r="274" ht="4.9000000000000004" customHeight="1"/>
-    <row r="275" ht="4.9000000000000004" customHeight="1"/>
-    <row r="276" ht="4.9000000000000004" customHeight="1"/>
-    <row r="277" ht="4.9000000000000004" customHeight="1"/>
-    <row r="278" ht="4.9000000000000004" customHeight="1"/>
-    <row r="279" ht="4.9000000000000004" customHeight="1"/>
-    <row r="280" ht="4.9000000000000004" customHeight="1"/>
-    <row r="281" ht="4.9000000000000004" customHeight="1"/>
-    <row r="282" ht="4.9000000000000004" customHeight="1"/>
-    <row r="283" ht="4.9000000000000004" customHeight="1"/>
-    <row r="284" ht="4.9000000000000004" customHeight="1"/>
-    <row r="285" ht="4.9000000000000004" customHeight="1"/>
-    <row r="286" ht="4.9000000000000004" customHeight="1"/>
-    <row r="287" ht="4.9000000000000004" customHeight="1"/>
-    <row r="288" ht="4.9000000000000004" customHeight="1"/>
-    <row r="289" ht="4.9000000000000004" customHeight="1"/>
-    <row r="290" ht="4.9000000000000004" customHeight="1"/>
-    <row r="291" ht="4.9000000000000004" customHeight="1"/>
-    <row r="292" ht="4.9000000000000004" customHeight="1"/>
-    <row r="293" ht="4.9000000000000004" customHeight="1"/>
-    <row r="294" ht="4.9000000000000004" customHeight="1"/>
-    <row r="295" ht="4.9000000000000004" customHeight="1"/>
-    <row r="296" ht="4.9000000000000004" customHeight="1"/>
-    <row r="297" ht="4.9000000000000004" customHeight="1"/>
-    <row r="298" ht="4.9000000000000004" customHeight="1"/>
-    <row r="299" ht="4.9000000000000004" customHeight="1"/>
-    <row r="300" ht="4.9000000000000004" customHeight="1"/>
-    <row r="301" ht="4.9000000000000004" customHeight="1"/>
-    <row r="302" ht="4.9000000000000004" customHeight="1"/>
-    <row r="303" ht="4.9000000000000004" customHeight="1"/>
-    <row r="304" ht="4.9000000000000004" customHeight="1"/>
-    <row r="305" ht="4.9000000000000004" customHeight="1"/>
-    <row r="306" ht="4.9000000000000004" customHeight="1"/>
-    <row r="307" ht="4.9000000000000004" customHeight="1"/>
-    <row r="308" ht="4.9000000000000004" customHeight="1"/>
-    <row r="309" ht="4.9000000000000004" customHeight="1"/>
-    <row r="310" ht="4.9000000000000004" customHeight="1"/>
-    <row r="311" ht="4.9000000000000004" customHeight="1"/>
-    <row r="312" ht="4.9000000000000004" customHeight="1"/>
-    <row r="313" ht="4.9000000000000004" customHeight="1"/>
-    <row r="314" ht="4.9000000000000004" customHeight="1"/>
-    <row r="315" ht="4.9000000000000004" customHeight="1"/>
-    <row r="316" ht="4.9000000000000004" customHeight="1"/>
-    <row r="317" ht="4.9000000000000004" customHeight="1"/>
-    <row r="318" ht="4.9000000000000004" customHeight="1"/>
-    <row r="319" ht="4.9000000000000004" customHeight="1"/>
-    <row r="320" ht="4.9000000000000004" customHeight="1"/>
-    <row r="321" ht="4.9000000000000004" customHeight="1"/>
-    <row r="322" ht="4.9000000000000004" customHeight="1"/>
-    <row r="323" ht="4.9000000000000004" customHeight="1"/>
-    <row r="324" ht="4.9000000000000004" customHeight="1"/>
-    <row r="325" ht="4.9000000000000004" customHeight="1"/>
-    <row r="326" ht="4.9000000000000004" customHeight="1"/>
-    <row r="327" ht="4.9000000000000004" customHeight="1"/>
-    <row r="328" ht="4.9000000000000004" customHeight="1"/>
-    <row r="329" ht="4.9000000000000004" customHeight="1"/>
-    <row r="330" ht="4.9000000000000004" customHeight="1"/>
-    <row r="331" ht="4.9000000000000004" customHeight="1"/>
-    <row r="332" ht="4.9000000000000004" customHeight="1"/>
-    <row r="333" ht="4.9000000000000004" customHeight="1"/>
-    <row r="334" ht="4.9000000000000004" customHeight="1"/>
-    <row r="335" ht="4.9000000000000004" customHeight="1"/>
-    <row r="336" ht="4.9000000000000004" customHeight="1"/>
-    <row r="337" ht="4.9000000000000004" customHeight="1"/>
-    <row r="338" ht="4.9000000000000004" customHeight="1"/>
-    <row r="339" ht="4.9000000000000004" customHeight="1"/>
-    <row r="340" ht="4.9000000000000004" customHeight="1"/>
-    <row r="341" ht="4.9000000000000004" customHeight="1"/>
-    <row r="342" ht="4.9000000000000004" customHeight="1"/>
-    <row r="343" ht="4.9000000000000004" customHeight="1"/>
-    <row r="344" ht="4.9000000000000004" customHeight="1"/>
-    <row r="345" ht="4.9000000000000004" customHeight="1"/>
-    <row r="346" ht="4.9000000000000004" customHeight="1"/>
-    <row r="347" ht="4.9000000000000004" customHeight="1"/>
-    <row r="348" ht="4.9000000000000004" customHeight="1"/>
-    <row r="349" ht="4.9000000000000004" customHeight="1"/>
-    <row r="350" ht="4.9000000000000004" customHeight="1"/>
-    <row r="351" ht="4.9000000000000004" customHeight="1"/>
-    <row r="352" ht="4.9000000000000004" customHeight="1"/>
-    <row r="353" ht="4.9000000000000004" customHeight="1"/>
-    <row r="354" ht="4.9000000000000004" customHeight="1"/>
-    <row r="355" ht="4.9000000000000004" customHeight="1"/>
-    <row r="356" ht="4.9000000000000004" customHeight="1"/>
-    <row r="357" ht="4.9000000000000004" customHeight="1"/>
-    <row r="358" ht="4.9000000000000004" customHeight="1"/>
-    <row r="359" ht="4.9000000000000004" customHeight="1"/>
-    <row r="360" ht="4.9000000000000004" customHeight="1"/>
-    <row r="361" ht="4.9000000000000004" customHeight="1"/>
-    <row r="362" ht="4.9000000000000004" customHeight="1"/>
-    <row r="363" ht="4.9000000000000004" customHeight="1"/>
-    <row r="364" ht="4.9000000000000004" customHeight="1"/>
-    <row r="365" ht="4.9000000000000004" customHeight="1"/>
-    <row r="366" ht="4.9000000000000004" customHeight="1"/>
-    <row r="367" ht="4.9000000000000004" customHeight="1"/>
-    <row r="368" ht="4.9000000000000004" customHeight="1"/>
-    <row r="369" ht="4.9000000000000004" customHeight="1"/>
-    <row r="370" ht="4.9000000000000004" customHeight="1"/>
-    <row r="371" ht="4.9000000000000004" customHeight="1"/>
-    <row r="372" ht="4.9000000000000004" customHeight="1"/>
-    <row r="373" ht="4.9000000000000004" customHeight="1"/>
-    <row r="374" ht="4.9000000000000004" customHeight="1"/>
-    <row r="375" ht="4.9000000000000004" customHeight="1"/>
-    <row r="376" ht="4.9000000000000004" customHeight="1"/>
-    <row r="377" ht="4.9000000000000004" customHeight="1"/>
-    <row r="378" ht="4.9000000000000004" customHeight="1"/>
-    <row r="379" ht="4.9000000000000004" customHeight="1"/>
-    <row r="380" ht="4.9000000000000004" customHeight="1"/>
-    <row r="381" ht="4.9000000000000004" customHeight="1"/>
-    <row r="382" ht="4.9000000000000004" customHeight="1"/>
-    <row r="383" ht="4.9000000000000004" customHeight="1"/>
-    <row r="384" ht="4.9000000000000004" customHeight="1"/>
-    <row r="385" ht="4.9000000000000004" customHeight="1"/>
-    <row r="386" ht="4.9000000000000004" customHeight="1"/>
-    <row r="387" ht="4.9000000000000004" customHeight="1"/>
-    <row r="388" ht="4.9000000000000004" customHeight="1"/>
-    <row r="389" ht="4.9000000000000004" customHeight="1"/>
-    <row r="390" ht="4.9000000000000004" customHeight="1"/>
-    <row r="391" ht="4.9000000000000004" customHeight="1"/>
-    <row r="392" ht="4.9000000000000004" customHeight="1"/>
-    <row r="393" ht="4.9000000000000004" customHeight="1"/>
-    <row r="394" ht="4.9000000000000004" customHeight="1"/>
-    <row r="395" ht="4.9000000000000004" customHeight="1"/>
-    <row r="396" ht="4.9000000000000004" customHeight="1"/>
-    <row r="397" ht="4.9000000000000004" customHeight="1"/>
-    <row r="398" ht="4.9000000000000004" customHeight="1"/>
-    <row r="399" ht="4.9000000000000004" customHeight="1"/>
-    <row r="400" ht="4.9000000000000004" customHeight="1"/>
-    <row r="401" ht="4.9000000000000004" customHeight="1"/>
-    <row r="402" ht="4.9000000000000004" customHeight="1"/>
-    <row r="403" ht="4.9000000000000004" customHeight="1"/>
-    <row r="404" ht="4.9000000000000004" customHeight="1"/>
-    <row r="405" ht="4.9000000000000004" customHeight="1"/>
-    <row r="406" ht="4.9000000000000004" customHeight="1"/>
-    <row r="407" ht="4.9000000000000004" customHeight="1"/>
-    <row r="408" ht="4.9000000000000004" customHeight="1"/>
-    <row r="409" ht="4.9000000000000004" customHeight="1"/>
-    <row r="410" ht="4.9000000000000004" customHeight="1"/>
-    <row r="411" ht="4.9000000000000004" customHeight="1"/>
-    <row r="412" ht="4.9000000000000004" customHeight="1"/>
-    <row r="413" ht="4.9000000000000004" customHeight="1"/>
-    <row r="414" ht="4.9000000000000004" customHeight="1"/>
-    <row r="415" ht="4.9000000000000004" customHeight="1"/>
-    <row r="416" ht="4.9000000000000004" customHeight="1"/>
-    <row r="417" ht="4.9000000000000004" customHeight="1"/>
-    <row r="418" ht="4.9000000000000004" customHeight="1"/>
-    <row r="419" ht="4.9000000000000004" customHeight="1"/>
-    <row r="420" ht="4.9000000000000004" customHeight="1"/>
-    <row r="421" ht="4.9000000000000004" customHeight="1"/>
-    <row r="422" ht="4.9000000000000004" customHeight="1"/>
-    <row r="423" ht="4.9000000000000004" customHeight="1"/>
-    <row r="424" ht="4.9000000000000004" customHeight="1"/>
-    <row r="425" ht="4.9000000000000004" customHeight="1"/>
-    <row r="426" ht="4.9000000000000004" customHeight="1"/>
-    <row r="427" ht="4.9000000000000004" customHeight="1"/>
-    <row r="428" ht="4.9000000000000004" customHeight="1"/>
-    <row r="429" ht="4.9000000000000004" customHeight="1"/>
-    <row r="430" ht="4.9000000000000004" customHeight="1"/>
-    <row r="431" ht="4.9000000000000004" customHeight="1"/>
-    <row r="432" ht="4.9000000000000004" customHeight="1"/>
-    <row r="433" ht="4.9000000000000004" customHeight="1"/>
-    <row r="434" ht="4.9000000000000004" customHeight="1"/>
-    <row r="435" ht="4.9000000000000004" customHeight="1"/>
-    <row r="436" ht="4.9000000000000004" customHeight="1"/>
-    <row r="437" ht="4.9000000000000004" customHeight="1"/>
-    <row r="438" ht="4.9000000000000004" customHeight="1"/>
-    <row r="439" ht="4.9000000000000004" customHeight="1"/>
-    <row r="440" ht="4.9000000000000004" customHeight="1"/>
-    <row r="441" ht="4.9000000000000004" customHeight="1"/>
-    <row r="442" ht="4.9000000000000004" customHeight="1"/>
-    <row r="443" ht="4.9000000000000004" customHeight="1"/>
-    <row r="444" ht="4.9000000000000004" customHeight="1"/>
-    <row r="445" ht="4.9000000000000004" customHeight="1"/>
-    <row r="446" ht="4.9000000000000004" customHeight="1"/>
-    <row r="447" ht="4.9000000000000004" customHeight="1"/>
-    <row r="448" ht="4.9000000000000004" customHeight="1"/>
-    <row r="449" ht="4.9000000000000004" customHeight="1"/>
-    <row r="450" ht="4.9000000000000004" customHeight="1"/>
-    <row r="451" ht="4.9000000000000004" customHeight="1"/>
-    <row r="452" ht="4.9000000000000004" customHeight="1"/>
-    <row r="453" ht="4.9000000000000004" customHeight="1"/>
-    <row r="454" ht="4.9000000000000004" customHeight="1"/>
-    <row r="455" ht="4.9000000000000004" customHeight="1"/>
-    <row r="456" ht="4.9000000000000004" customHeight="1"/>
-    <row r="457" ht="4.9000000000000004" customHeight="1"/>
-    <row r="458" ht="4.9000000000000004" customHeight="1"/>
-    <row r="459" ht="4.9000000000000004" customHeight="1"/>
-    <row r="460" ht="4.9000000000000004" customHeight="1"/>
-    <row r="461" ht="4.9000000000000004" customHeight="1"/>
-    <row r="462" ht="4.9000000000000004" customHeight="1"/>
-    <row r="463" ht="4.9000000000000004" customHeight="1"/>
-    <row r="464" ht="4.9000000000000004" customHeight="1"/>
-    <row r="465" ht="4.9000000000000004" customHeight="1"/>
-    <row r="466" ht="4.9000000000000004" customHeight="1"/>
-    <row r="467" ht="4.9000000000000004" customHeight="1"/>
-    <row r="468" ht="4.9000000000000004" customHeight="1"/>
-    <row r="469" ht="4.9000000000000004" customHeight="1"/>
-    <row r="470" ht="4.9000000000000004" customHeight="1"/>
-    <row r="471" ht="4.9000000000000004" customHeight="1"/>
-    <row r="472" ht="4.9000000000000004" customHeight="1"/>
-    <row r="473" ht="4.9000000000000004" customHeight="1"/>
-    <row r="474" ht="4.9000000000000004" customHeight="1"/>
-    <row r="475" ht="4.9000000000000004" customHeight="1"/>
-    <row r="476" ht="4.9000000000000004" customHeight="1"/>
-    <row r="477" ht="4.9000000000000004" customHeight="1"/>
-    <row r="478" ht="4.9000000000000004" customHeight="1"/>
-    <row r="479" ht="4.9000000000000004" customHeight="1"/>
-    <row r="480" ht="4.9000000000000004" customHeight="1"/>
-    <row r="481" ht="4.9000000000000004" customHeight="1"/>
-    <row r="482" ht="4.9000000000000004" customHeight="1"/>
-    <row r="483" ht="4.9000000000000004" customHeight="1"/>
-    <row r="484" ht="4.9000000000000004" customHeight="1"/>
-    <row r="485" ht="4.9000000000000004" customHeight="1"/>
-    <row r="486" ht="4.9000000000000004" customHeight="1"/>
-    <row r="487" ht="4.9000000000000004" customHeight="1"/>
-    <row r="488" ht="4.9000000000000004" customHeight="1"/>
-    <row r="489" ht="4.9000000000000004" customHeight="1"/>
-    <row r="490" ht="4.9000000000000004" customHeight="1"/>
-    <row r="491" ht="4.9000000000000004" customHeight="1"/>
-    <row r="492" ht="4.9000000000000004" customHeight="1"/>
-    <row r="493" ht="4.9000000000000004" customHeight="1"/>
-    <row r="494" ht="4.9000000000000004" customHeight="1"/>
-    <row r="495" ht="4.9000000000000004" customHeight="1"/>
-    <row r="496" ht="4.9000000000000004" customHeight="1"/>
-    <row r="497" ht="4.9000000000000004" customHeight="1"/>
-    <row r="498" ht="4.9000000000000004" customHeight="1"/>
-    <row r="499" ht="4.9000000000000004" customHeight="1"/>
-    <row r="500" ht="4.9000000000000004" customHeight="1"/>
-    <row r="501" ht="4.9000000000000004" customHeight="1"/>
-    <row r="502" ht="4.9000000000000004" customHeight="1"/>
-    <row r="503" ht="4.9000000000000004" customHeight="1"/>
-    <row r="504" ht="4.9000000000000004" customHeight="1"/>
-    <row r="505" ht="4.9000000000000004" customHeight="1"/>
-    <row r="506" ht="4.9000000000000004" customHeight="1"/>
-    <row r="507" ht="4.9000000000000004" customHeight="1"/>
-    <row r="508" ht="4.9000000000000004" customHeight="1"/>
-    <row r="509" ht="4.9000000000000004" customHeight="1"/>
-    <row r="510" ht="4.9000000000000004" customHeight="1"/>
-    <row r="511" ht="4.9000000000000004" customHeight="1"/>
-    <row r="512" ht="4.9000000000000004" customHeight="1"/>
-    <row r="513" ht="4.9000000000000004" customHeight="1"/>
-    <row r="514" ht="4.9000000000000004" customHeight="1"/>
-    <row r="515" ht="4.9000000000000004" customHeight="1"/>
-    <row r="516" ht="4.9000000000000004" customHeight="1"/>
-    <row r="517" ht="4.9000000000000004" customHeight="1"/>
-    <row r="518" ht="4.9000000000000004" customHeight="1"/>
-    <row r="519" ht="4.9000000000000004" customHeight="1"/>
-    <row r="520" ht="4.9000000000000004" customHeight="1"/>
-    <row r="521" ht="4.9000000000000004" customHeight="1"/>
-    <row r="522" ht="4.9000000000000004" customHeight="1"/>
-    <row r="523" ht="4.9000000000000004" customHeight="1"/>
-    <row r="524" ht="4.9000000000000004" customHeight="1"/>
-    <row r="525" ht="4.9000000000000004" customHeight="1"/>
-    <row r="526" ht="4.9000000000000004" customHeight="1"/>
-    <row r="527" ht="4.9000000000000004" customHeight="1"/>
-    <row r="528" ht="4.9000000000000004" customHeight="1"/>
-    <row r="529" ht="4.9000000000000004" customHeight="1"/>
-    <row r="530" ht="4.9000000000000004" customHeight="1"/>
-    <row r="531" ht="4.9000000000000004" customHeight="1"/>
-    <row r="532" ht="4.9000000000000004" customHeight="1"/>
-    <row r="533" ht="4.9000000000000004" customHeight="1"/>
-    <row r="534" ht="4.9000000000000004" customHeight="1"/>
-    <row r="535" ht="4.9000000000000004" customHeight="1"/>
-    <row r="536" ht="4.9000000000000004" customHeight="1"/>
-    <row r="537" ht="4.9000000000000004" customHeight="1"/>
-    <row r="538" ht="4.9000000000000004" customHeight="1"/>
-    <row r="539" ht="4.9000000000000004" customHeight="1"/>
-    <row r="540" ht="4.9000000000000004" customHeight="1"/>
-    <row r="541" ht="4.9000000000000004" customHeight="1"/>
-    <row r="542" ht="4.9000000000000004" customHeight="1"/>
-    <row r="543" ht="4.9000000000000004" customHeight="1"/>
-    <row r="544" ht="4.9000000000000004" customHeight="1"/>
-    <row r="545" ht="4.9000000000000004" customHeight="1"/>
-    <row r="546" ht="4.9000000000000004" customHeight="1"/>
-    <row r="547" ht="4.9000000000000004" customHeight="1"/>
-    <row r="548" ht="4.9000000000000004" customHeight="1"/>
-    <row r="549" ht="4.9000000000000004" customHeight="1"/>
-    <row r="550" ht="4.9000000000000004" customHeight="1"/>
-    <row r="551" ht="4.9000000000000004" customHeight="1"/>
-    <row r="552" ht="4.9000000000000004" customHeight="1"/>
-    <row r="553" ht="4.9000000000000004" customHeight="1"/>
-    <row r="554" ht="4.9000000000000004" customHeight="1"/>
-    <row r="555" ht="4.9000000000000004" customHeight="1"/>
-    <row r="556" ht="4.9000000000000004" customHeight="1"/>
-    <row r="557" ht="4.9000000000000004" customHeight="1"/>
-    <row r="558" ht="4.9000000000000004" customHeight="1"/>
-    <row r="559" ht="4.9000000000000004" customHeight="1"/>
-    <row r="560" ht="4.9000000000000004" customHeight="1"/>
-    <row r="561" ht="4.9000000000000004" customHeight="1"/>
-    <row r="562" ht="4.9000000000000004" customHeight="1"/>
-    <row r="563" ht="4.9000000000000004" customHeight="1"/>
-    <row r="564" ht="4.9000000000000004" customHeight="1"/>
-    <row r="565" ht="4.9000000000000004" customHeight="1"/>
-    <row r="566" ht="4.9000000000000004" customHeight="1"/>
-    <row r="567" ht="4.9000000000000004" customHeight="1"/>
-    <row r="568" ht="4.9000000000000004" customHeight="1"/>
-    <row r="569" ht="4.9000000000000004" customHeight="1"/>
-    <row r="570" ht="4.9000000000000004" customHeight="1"/>
-    <row r="571" ht="4.9000000000000004" customHeight="1"/>
-    <row r="572" ht="4.9000000000000004" customHeight="1"/>
-    <row r="573" ht="4.9000000000000004" customHeight="1"/>
-    <row r="574" ht="4.9000000000000004" customHeight="1"/>
-    <row r="575" ht="4.9000000000000004" customHeight="1"/>
-    <row r="576" ht="4.9000000000000004" customHeight="1"/>
-    <row r="577" ht="4.9000000000000004" customHeight="1"/>
-    <row r="578" ht="4.9000000000000004" customHeight="1"/>
-    <row r="579" ht="4.9000000000000004" customHeight="1"/>
-    <row r="580" ht="4.9000000000000004" customHeight="1"/>
-    <row r="581" ht="4.9000000000000004" customHeight="1"/>
-    <row r="582" ht="4.9000000000000004" customHeight="1"/>
-    <row r="583" ht="4.9000000000000004" customHeight="1"/>
-    <row r="584" ht="4.9000000000000004" customHeight="1"/>
-    <row r="585" ht="4.9000000000000004" customHeight="1"/>
-    <row r="586" ht="4.9000000000000004" customHeight="1"/>
-    <row r="587" ht="4.9000000000000004" customHeight="1"/>
-    <row r="588" ht="4.9000000000000004" customHeight="1"/>
-    <row r="589" ht="4.9000000000000004" customHeight="1"/>
-    <row r="590" ht="4.9000000000000004" customHeight="1"/>
-    <row r="591" ht="4.9000000000000004" customHeight="1"/>
-    <row r="592" ht="4.9000000000000004" customHeight="1"/>
-    <row r="593" ht="4.9000000000000004" customHeight="1"/>
-    <row r="594" ht="4.9000000000000004" customHeight="1"/>
-    <row r="595" ht="4.9000000000000004" customHeight="1"/>
-    <row r="596" ht="4.9000000000000004" customHeight="1"/>
-    <row r="597" ht="4.9000000000000004" customHeight="1"/>
-    <row r="598" ht="4.9000000000000004" customHeight="1"/>
-    <row r="599" ht="4.9000000000000004" customHeight="1"/>
-    <row r="600" ht="4.9000000000000004" customHeight="1"/>
-    <row r="601" ht="4.9000000000000004" customHeight="1"/>
-    <row r="602" ht="4.9000000000000004" customHeight="1"/>
-    <row r="603" ht="4.9000000000000004" customHeight="1"/>
-    <row r="604" ht="4.9000000000000004" customHeight="1"/>
-    <row r="605" ht="4.9000000000000004" customHeight="1"/>
-    <row r="606" ht="4.9000000000000004" customHeight="1"/>
-    <row r="607" ht="4.9000000000000004" customHeight="1"/>
-    <row r="608" ht="4.9000000000000004" customHeight="1"/>
-    <row r="609" ht="4.9000000000000004" customHeight="1"/>
-    <row r="610" ht="4.9000000000000004" customHeight="1"/>
-    <row r="611" ht="4.9000000000000004" customHeight="1"/>
-    <row r="612" ht="4.9000000000000004" customHeight="1"/>
-    <row r="613" ht="4.9000000000000004" customHeight="1"/>
-    <row r="614" ht="4.9000000000000004" customHeight="1"/>
-    <row r="615" ht="4.9000000000000004" customHeight="1"/>
-    <row r="616" ht="4.9000000000000004" customHeight="1"/>
-    <row r="617" ht="4.9000000000000004" customHeight="1"/>
-    <row r="618" ht="4.9000000000000004" customHeight="1"/>
-    <row r="619" ht="4.9000000000000004" customHeight="1"/>
-    <row r="620" ht="4.9000000000000004" customHeight="1"/>
-    <row r="621" ht="4.9000000000000004" customHeight="1"/>
-    <row r="622" ht="4.9000000000000004" customHeight="1"/>
-    <row r="623" ht="4.9000000000000004" customHeight="1"/>
-    <row r="624" ht="4.9000000000000004" customHeight="1"/>
-    <row r="625" ht="4.9000000000000004" customHeight="1"/>
-    <row r="626" ht="4.9000000000000004" customHeight="1"/>
-    <row r="627" ht="4.9000000000000004" customHeight="1"/>
-    <row r="628" ht="4.9000000000000004" customHeight="1"/>
-    <row r="629" ht="4.9000000000000004" customHeight="1"/>
-    <row r="630" ht="4.9000000000000004" customHeight="1"/>
-    <row r="631" ht="4.9000000000000004" customHeight="1"/>
-    <row r="632" ht="4.9000000000000004" customHeight="1"/>
-    <row r="633" ht="4.9000000000000004" customHeight="1"/>
-    <row r="634" ht="4.9000000000000004" customHeight="1"/>
-    <row r="635" ht="4.9000000000000004" customHeight="1"/>
-    <row r="636" ht="4.9000000000000004" customHeight="1"/>
-    <row r="637" ht="4.9000000000000004" customHeight="1"/>
-    <row r="638" ht="4.9000000000000004" customHeight="1"/>
-    <row r="639" ht="4.9000000000000004" customHeight="1"/>
-    <row r="640" ht="4.9000000000000004" customHeight="1"/>
-    <row r="641" ht="4.9000000000000004" customHeight="1"/>
-    <row r="642" ht="4.9000000000000004" customHeight="1"/>
-    <row r="643" ht="4.9000000000000004" customHeight="1"/>
-    <row r="644" ht="4.9000000000000004" customHeight="1"/>
-    <row r="645" ht="4.9000000000000004" customHeight="1"/>
-    <row r="646" ht="4.9000000000000004" customHeight="1"/>
-    <row r="647" ht="4.9000000000000004" customHeight="1"/>
-    <row r="648" ht="4.9000000000000004" customHeight="1"/>
-    <row r="649" ht="4.9000000000000004" customHeight="1"/>
-    <row r="650" ht="4.9000000000000004" customHeight="1"/>
-    <row r="651" ht="4.9000000000000004" customHeight="1"/>
-    <row r="652" ht="4.9000000000000004" customHeight="1"/>
-    <row r="653" ht="4.9000000000000004" customHeight="1"/>
-    <row r="654" ht="4.9000000000000004" customHeight="1"/>
-    <row r="655" ht="4.9000000000000004" customHeight="1"/>
-    <row r="656" ht="4.9000000000000004" customHeight="1"/>
-    <row r="657" ht="4.9000000000000004" customHeight="1"/>
-    <row r="658" ht="4.9000000000000004" customHeight="1"/>
-    <row r="659" ht="4.9000000000000004" customHeight="1"/>
-    <row r="660" ht="4.9000000000000004" customHeight="1"/>
-    <row r="661" ht="4.9000000000000004" customHeight="1"/>
-    <row r="662" ht="4.9000000000000004" customHeight="1"/>
-    <row r="663" ht="4.9000000000000004" customHeight="1"/>
-    <row r="664" ht="4.9000000000000004" customHeight="1"/>
-    <row r="665" ht="4.9000000000000004" customHeight="1"/>
-    <row r="666" ht="4.9000000000000004" customHeight="1"/>
-    <row r="667" ht="4.9000000000000004" customHeight="1"/>
-    <row r="668" ht="4.9000000000000004" customHeight="1"/>
-    <row r="669" ht="4.9000000000000004" customHeight="1"/>
-    <row r="670" ht="4.9000000000000004" customHeight="1"/>
-    <row r="671" ht="4.9000000000000004" customHeight="1"/>
-    <row r="672" ht="4.9000000000000004" customHeight="1"/>
-    <row r="673" ht="4.9000000000000004" customHeight="1"/>
-    <row r="674" ht="4.9000000000000004" customHeight="1"/>
-    <row r="675" ht="4.9000000000000004" customHeight="1"/>
-    <row r="676" ht="4.9000000000000004" customHeight="1"/>
-    <row r="677" ht="4.9000000000000004" customHeight="1"/>
-    <row r="678" ht="4.9000000000000004" customHeight="1"/>
-    <row r="679" ht="4.9000000000000004" customHeight="1"/>
-    <row r="680" ht="4.9000000000000004" customHeight="1"/>
-    <row r="681" ht="4.9000000000000004" customHeight="1"/>
-    <row r="682" ht="4.9000000000000004" customHeight="1"/>
-    <row r="683" ht="4.9000000000000004" customHeight="1"/>
-    <row r="684" ht="4.9000000000000004" customHeight="1"/>
-    <row r="685" ht="4.9000000000000004" customHeight="1"/>
-    <row r="686" ht="4.9000000000000004" customHeight="1"/>
-    <row r="687" ht="4.9000000000000004" customHeight="1"/>
-    <row r="688" ht="4.9000000000000004" customHeight="1"/>
-    <row r="689" ht="4.9000000000000004" customHeight="1"/>
-    <row r="690" ht="4.9000000000000004" customHeight="1"/>
-    <row r="691" ht="4.9000000000000004" customHeight="1"/>
-    <row r="692" ht="4.9000000000000004" customHeight="1"/>
-    <row r="693" ht="4.9000000000000004" customHeight="1"/>
-    <row r="694" ht="4.9000000000000004" customHeight="1"/>
-    <row r="695" ht="4.9000000000000004" customHeight="1"/>
-    <row r="696" ht="4.9000000000000004" customHeight="1"/>
-    <row r="697" ht="4.9000000000000004" customHeight="1"/>
-    <row r="698" ht="4.9000000000000004" customHeight="1"/>
-    <row r="699" ht="4.9000000000000004" customHeight="1"/>
-    <row r="700" ht="4.9000000000000004" customHeight="1"/>
-    <row r="701" ht="4.9000000000000004" customHeight="1"/>
-    <row r="702" ht="4.9000000000000004" customHeight="1"/>
-    <row r="703" ht="4.9000000000000004" customHeight="1"/>
-    <row r="704" ht="4.9000000000000004" customHeight="1"/>
-    <row r="705" ht="4.9000000000000004" customHeight="1"/>
-    <row r="706" ht="4.9000000000000004" customHeight="1"/>
-    <row r="707" ht="4.9000000000000004" customHeight="1"/>
-    <row r="708" ht="4.9000000000000004" customHeight="1"/>
-    <row r="709" ht="4.9000000000000004" customHeight="1"/>
-    <row r="710" ht="4.9000000000000004" customHeight="1"/>
-    <row r="711" ht="4.9000000000000004" customHeight="1"/>
-    <row r="712" ht="4.9000000000000004" customHeight="1"/>
-    <row r="713" ht="4.9000000000000004" customHeight="1"/>
-    <row r="714" ht="4.9000000000000004" customHeight="1"/>
-    <row r="715" ht="4.9000000000000004" customHeight="1"/>
-    <row r="716" ht="4.9000000000000004" customHeight="1"/>
-    <row r="717" ht="4.9000000000000004" customHeight="1"/>
-    <row r="718" ht="4.9000000000000004" customHeight="1"/>
-    <row r="719" ht="4.9000000000000004" customHeight="1"/>
-    <row r="720" ht="4.9000000000000004" customHeight="1"/>
-    <row r="721" ht="4.9000000000000004" customHeight="1"/>
-    <row r="722" ht="4.9000000000000004" customHeight="1"/>
-    <row r="723" ht="4.9000000000000004" customHeight="1"/>
-    <row r="724" ht="4.9000000000000004" customHeight="1"/>
-    <row r="725" ht="4.9000000000000004" customHeight="1"/>
-    <row r="726" ht="4.9000000000000004" customHeight="1"/>
-    <row r="727" ht="4.9000000000000004" customHeight="1"/>
-    <row r="728" ht="4.9000000000000004" customHeight="1"/>
-    <row r="729" ht="4.9000000000000004" customHeight="1"/>
-    <row r="730" ht="4.9000000000000004" customHeight="1"/>
-    <row r="731" ht="4.9000000000000004" customHeight="1"/>
-    <row r="732" ht="4.9000000000000004" customHeight="1"/>
-    <row r="733" ht="4.9000000000000004" customHeight="1"/>
-    <row r="734" ht="4.9000000000000004" customHeight="1"/>
-    <row r="735" ht="4.9000000000000004" customHeight="1"/>
-    <row r="736" ht="4.9000000000000004" customHeight="1"/>
-    <row r="737" ht="4.9000000000000004" customHeight="1"/>
-    <row r="738" ht="4.9000000000000004" customHeight="1"/>
-    <row r="739" ht="4.9000000000000004" customHeight="1"/>
-    <row r="740" ht="4.9000000000000004" customHeight="1"/>
-    <row r="741" ht="4.9000000000000004" customHeight="1"/>
-    <row r="742" ht="4.9000000000000004" customHeight="1"/>
-    <row r="743" ht="4.9000000000000004" customHeight="1"/>
-    <row r="744" ht="4.9000000000000004" customHeight="1"/>
-    <row r="745" ht="4.9000000000000004" customHeight="1"/>
-    <row r="746" ht="4.9000000000000004" customHeight="1"/>
-    <row r="747" ht="4.9000000000000004" customHeight="1"/>
-    <row r="748" ht="4.9000000000000004" customHeight="1"/>
-    <row r="749" ht="4.9000000000000004" customHeight="1"/>
-    <row r="750" ht="4.9000000000000004" customHeight="1"/>
-    <row r="751" ht="4.9000000000000004" customHeight="1"/>
-    <row r="752" ht="4.9000000000000004" customHeight="1"/>
-    <row r="753" ht="4.9000000000000004" customHeight="1"/>
-    <row r="754" ht="4.9000000000000004" customHeight="1"/>
-    <row r="755" ht="4.9000000000000004" customHeight="1"/>
-    <row r="756" ht="4.9000000000000004" customHeight="1"/>
-    <row r="757" ht="4.9000000000000004" customHeight="1"/>
-    <row r="758" ht="4.9000000000000004" customHeight="1"/>
-    <row r="759" ht="4.9000000000000004" customHeight="1"/>
-    <row r="760" ht="4.9000000000000004" customHeight="1"/>
-    <row r="761" ht="4.9000000000000004" customHeight="1"/>
-    <row r="762" ht="4.9000000000000004" customHeight="1"/>
-    <row r="763" ht="4.9000000000000004" customHeight="1"/>
-    <row r="764" ht="4.9000000000000004" customHeight="1"/>
-    <row r="765" ht="4.9000000000000004" customHeight="1"/>
-    <row r="766" ht="4.9000000000000004" customHeight="1"/>
-    <row r="767" ht="4.9000000000000004" customHeight="1"/>
-    <row r="768" ht="4.9000000000000004" customHeight="1"/>
-    <row r="769" ht="4.9000000000000004" customHeight="1"/>
-    <row r="770" ht="4.9000000000000004" customHeight="1"/>
-    <row r="771" ht="4.9000000000000004" customHeight="1"/>
-    <row r="772" ht="4.9000000000000004" customHeight="1"/>
-    <row r="773" ht="4.9000000000000004" customHeight="1"/>
-    <row r="774" ht="4.9000000000000004" customHeight="1"/>
-    <row r="775" ht="4.9000000000000004" customHeight="1"/>
-    <row r="776" ht="4.9000000000000004" customHeight="1"/>
-    <row r="777" ht="4.9000000000000004" customHeight="1"/>
-    <row r="778" ht="4.9000000000000004" customHeight="1"/>
-    <row r="779" ht="4.9000000000000004" customHeight="1"/>
-    <row r="780" ht="4.9000000000000004" customHeight="1"/>
-    <row r="781" ht="4.9000000000000004" customHeight="1"/>
-    <row r="782" ht="4.9000000000000004" customHeight="1"/>
-    <row r="783" ht="4.9000000000000004" customHeight="1"/>
-    <row r="784" ht="4.9000000000000004" customHeight="1"/>
-    <row r="785" ht="4.9000000000000004" customHeight="1"/>
-    <row r="786" ht="4.9000000000000004" customHeight="1"/>
-    <row r="787" ht="4.9000000000000004" customHeight="1"/>
-    <row r="788" ht="4.9000000000000004" customHeight="1"/>
-    <row r="789" ht="4.9000000000000004" customHeight="1"/>
-    <row r="790" ht="4.9000000000000004" customHeight="1"/>
-    <row r="791" ht="4.9000000000000004" customHeight="1"/>
-    <row r="792" ht="4.9000000000000004" customHeight="1"/>
-    <row r="793" ht="4.9000000000000004" customHeight="1"/>
-    <row r="794" ht="4.9000000000000004" customHeight="1"/>
-    <row r="795" ht="4.9000000000000004" customHeight="1"/>
-    <row r="796" ht="4.9000000000000004" customHeight="1"/>
-    <row r="797" ht="4.9000000000000004" customHeight="1"/>
-    <row r="798" ht="4.9000000000000004" customHeight="1"/>
-    <row r="799" ht="4.9000000000000004" customHeight="1"/>
-    <row r="800" ht="4.9000000000000004" customHeight="1"/>
-    <row r="801" ht="4.9000000000000004" customHeight="1"/>
-    <row r="802" ht="4.9000000000000004" customHeight="1"/>
-    <row r="803" ht="4.9000000000000004" customHeight="1"/>
-    <row r="804" ht="4.9000000000000004" customHeight="1"/>
-    <row r="805" ht="4.9000000000000004" customHeight="1"/>
-    <row r="806" ht="4.9000000000000004" customHeight="1"/>
-    <row r="807" ht="4.9000000000000004" customHeight="1"/>
-    <row r="808" ht="4.9000000000000004" customHeight="1"/>
-    <row r="809" ht="4.9000000000000004" customHeight="1"/>
-    <row r="810" ht="4.9000000000000004" customHeight="1"/>
-    <row r="811" ht="4.9000000000000004" customHeight="1"/>
-    <row r="812" ht="4.9000000000000004" customHeight="1"/>
-    <row r="813" ht="4.9000000000000004" customHeight="1"/>
-    <row r="814" ht="4.9000000000000004" customHeight="1"/>
-    <row r="815" ht="4.9000000000000004" customHeight="1"/>
-    <row r="816" ht="4.9000000000000004" customHeight="1"/>
-    <row r="817" ht="4.9000000000000004" customHeight="1"/>
-    <row r="818" ht="4.9000000000000004" customHeight="1"/>
-    <row r="819" ht="4.9000000000000004" customHeight="1"/>
-    <row r="820" ht="4.9000000000000004" customHeight="1"/>
-    <row r="821" ht="4.9000000000000004" customHeight="1"/>
-    <row r="822" ht="4.9000000000000004" customHeight="1"/>
-    <row r="823" ht="4.9000000000000004" customHeight="1"/>
-    <row r="824" ht="4.9000000000000004" customHeight="1"/>
-    <row r="825" ht="4.9000000000000004" customHeight="1"/>
-    <row r="826" ht="4.9000000000000004" customHeight="1"/>
-    <row r="827" ht="4.9000000000000004" customHeight="1"/>
-    <row r="828" ht="4.9000000000000004" customHeight="1"/>
-    <row r="829" ht="4.9000000000000004" customHeight="1"/>
-    <row r="830" ht="4.9000000000000004" customHeight="1"/>
-    <row r="831" ht="4.9000000000000004" customHeight="1"/>
-    <row r="832" ht="4.9000000000000004" customHeight="1"/>
-    <row r="833" ht="4.9000000000000004" customHeight="1"/>
-    <row r="834" ht="4.9000000000000004" customHeight="1"/>
-    <row r="835" ht="4.9000000000000004" customHeight="1"/>
-    <row r="836" ht="4.9000000000000004" customHeight="1"/>
-    <row r="837" ht="4.9000000000000004" customHeight="1"/>
-    <row r="838" ht="4.9000000000000004" customHeight="1"/>
-    <row r="839" ht="4.9000000000000004" customHeight="1"/>
-    <row r="840" ht="4.9000000000000004" customHeight="1"/>
-    <row r="841" ht="4.9000000000000004" customHeight="1"/>
-    <row r="842" ht="4.9000000000000004" customHeight="1"/>
-    <row r="843" ht="4.9000000000000004" customHeight="1"/>
-    <row r="844" ht="4.9000000000000004" customHeight="1"/>
-    <row r="845" ht="4.9000000000000004" customHeight="1"/>
-    <row r="846" ht="4.9000000000000004" customHeight="1"/>
-    <row r="847" ht="4.9000000000000004" customHeight="1"/>
-    <row r="848" ht="4.9000000000000004" customHeight="1"/>
-    <row r="849" ht="4.9000000000000004" customHeight="1"/>
-    <row r="850" ht="4.9000000000000004" customHeight="1"/>
-    <row r="851" ht="4.9000000000000004" customHeight="1"/>
-    <row r="852" ht="4.9000000000000004" customHeight="1"/>
-    <row r="853" ht="4.9000000000000004" customHeight="1"/>
-    <row r="854" ht="4.9000000000000004" customHeight="1"/>
-    <row r="855" ht="4.9000000000000004" customHeight="1"/>
-    <row r="856" ht="4.9000000000000004" customHeight="1"/>
-    <row r="857" ht="4.9000000000000004" customHeight="1"/>
-    <row r="858" ht="4.9000000000000004" customHeight="1"/>
-    <row r="859" ht="4.9000000000000004" customHeight="1"/>
-    <row r="860" ht="4.9000000000000004" customHeight="1"/>
-    <row r="861" ht="4.9000000000000004" customHeight="1"/>
-    <row r="862" ht="4.9000000000000004" customHeight="1"/>
-    <row r="863" ht="4.9000000000000004" customHeight="1"/>
-    <row r="864" ht="4.9000000000000004" customHeight="1"/>
-    <row r="865" ht="4.9000000000000004" customHeight="1"/>
-    <row r="866" ht="4.9000000000000004" customHeight="1"/>
-    <row r="867" ht="4.9000000000000004" customHeight="1"/>
-    <row r="868" ht="4.9000000000000004" customHeight="1"/>
-    <row r="869" ht="4.9000000000000004" customHeight="1"/>
-    <row r="870" ht="4.9000000000000004" customHeight="1"/>
-    <row r="871" ht="4.9000000000000004" customHeight="1"/>
-    <row r="872" ht="4.9000000000000004" customHeight="1"/>
-    <row r="873" ht="4.9000000000000004" customHeight="1"/>
-    <row r="874" ht="4.9000000000000004" customHeight="1"/>
-    <row r="875" ht="4.9000000000000004" customHeight="1"/>
-    <row r="876" ht="4.9000000000000004" customHeight="1"/>
-    <row r="877" ht="4.9000000000000004" customHeight="1"/>
-    <row r="878" ht="4.9000000000000004" customHeight="1"/>
-    <row r="879" ht="4.9000000000000004" customHeight="1"/>
-    <row r="880" ht="4.9000000000000004" customHeight="1"/>
-    <row r="881" ht="4.9000000000000004" customHeight="1"/>
-    <row r="882" ht="4.9000000000000004" customHeight="1"/>
-    <row r="883" ht="4.9000000000000004" customHeight="1"/>
-    <row r="884" ht="4.9000000000000004" customHeight="1"/>
-    <row r="885" ht="4.9000000000000004" customHeight="1"/>
-    <row r="886" ht="4.9000000000000004" customHeight="1"/>
-    <row r="887" ht="4.9000000000000004" customHeight="1"/>
-    <row r="888" ht="4.9000000000000004" customHeight="1"/>
-    <row r="889" ht="4.9000000000000004" customHeight="1"/>
-    <row r="890" ht="4.9000000000000004" customHeight="1"/>
-    <row r="891" ht="4.9000000000000004" customHeight="1"/>
-    <row r="892" ht="4.9000000000000004" customHeight="1"/>
-    <row r="893" ht="4.9000000000000004" customHeight="1"/>
-    <row r="894" ht="4.9000000000000004" customHeight="1"/>
-    <row r="895" ht="4.9000000000000004" customHeight="1"/>
-    <row r="896" ht="4.9000000000000004" customHeight="1"/>
-    <row r="897" ht="4.9000000000000004" customHeight="1"/>
-    <row r="898" ht="4.9000000000000004" customHeight="1"/>
-    <row r="899" ht="4.9000000000000004" customHeight="1"/>
-    <row r="900" ht="4.9000000000000004" customHeight="1"/>
-    <row r="901" ht="4.9000000000000004" customHeight="1"/>
-    <row r="902" ht="4.9000000000000004" customHeight="1"/>
-    <row r="903" ht="4.9000000000000004" customHeight="1"/>
-    <row r="904" ht="4.9000000000000004" customHeight="1"/>
-    <row r="905" ht="4.9000000000000004" customHeight="1"/>
-    <row r="906" ht="4.9000000000000004" customHeight="1"/>
-    <row r="907" ht="4.9000000000000004" customHeight="1"/>
-    <row r="908" ht="4.9000000000000004" customHeight="1"/>
-    <row r="909" ht="4.9000000000000004" customHeight="1"/>
-    <row r="910" ht="4.9000000000000004" customHeight="1"/>
-    <row r="911" ht="4.9000000000000004" customHeight="1"/>
-    <row r="912" ht="4.9000000000000004" customHeight="1"/>
-    <row r="913" ht="4.9000000000000004" customHeight="1"/>
-    <row r="914" ht="4.9000000000000004" customHeight="1"/>
-    <row r="915" ht="4.9000000000000004" customHeight="1"/>
-    <row r="916" ht="4.9000000000000004" customHeight="1"/>
-    <row r="917" ht="4.9000000000000004" customHeight="1"/>
-    <row r="918" ht="4.9000000000000004" customHeight="1"/>
-    <row r="919" ht="4.9000000000000004" customHeight="1"/>
-    <row r="920" ht="4.9000000000000004" customHeight="1"/>
-    <row r="921" ht="4.9000000000000004" customHeight="1"/>
-    <row r="922" ht="4.9000000000000004" customHeight="1"/>
-    <row r="923" ht="4.9000000000000004" customHeight="1"/>
-    <row r="924" ht="4.9000000000000004" customHeight="1"/>
-    <row r="925" ht="4.9000000000000004" customHeight="1"/>
-    <row r="926" ht="4.9000000000000004" customHeight="1"/>
-    <row r="927" ht="4.9000000000000004" customHeight="1"/>
-    <row r="928" ht="4.9000000000000004" customHeight="1"/>
-    <row r="929" ht="4.9000000000000004" customHeight="1"/>
-    <row r="930" ht="4.9000000000000004" customHeight="1"/>
-    <row r="931" ht="4.9000000000000004" customHeight="1"/>
-    <row r="932" ht="4.9000000000000004" customHeight="1"/>
-    <row r="933" ht="4.9000000000000004" customHeight="1"/>
-    <row r="934" ht="4.9000000000000004" customHeight="1"/>
-    <row r="935" ht="4.9000000000000004" customHeight="1"/>
-    <row r="936" ht="4.9000000000000004" customHeight="1"/>
-    <row r="937" ht="4.9000000000000004" customHeight="1"/>
-    <row r="938" ht="4.9000000000000004" customHeight="1"/>
-    <row r="939" ht="4.9000000000000004" customHeight="1"/>
-    <row r="940" ht="4.9000000000000004" customHeight="1"/>
-    <row r="941" ht="4.9000000000000004" customHeight="1"/>
-    <row r="942" ht="4.9000000000000004" customHeight="1"/>
-    <row r="943" ht="4.9000000000000004" customHeight="1"/>
-    <row r="944" ht="4.9000000000000004" customHeight="1"/>
-    <row r="945" ht="4.9000000000000004" customHeight="1"/>
-    <row r="946" ht="4.9000000000000004" customHeight="1"/>
-    <row r="947" ht="4.9000000000000004" customHeight="1"/>
-    <row r="948" ht="4.9000000000000004" customHeight="1"/>
-    <row r="949" ht="4.9000000000000004" customHeight="1"/>
-    <row r="950" ht="4.9000000000000004" customHeight="1"/>
-    <row r="951" ht="4.9000000000000004" customHeight="1"/>
-    <row r="952" ht="4.9000000000000004" customHeight="1"/>
-    <row r="953" ht="4.9000000000000004" customHeight="1"/>
-    <row r="954" ht="4.9000000000000004" customHeight="1"/>
-    <row r="955" ht="4.9000000000000004" customHeight="1"/>
-    <row r="956" ht="4.9000000000000004" customHeight="1"/>
-    <row r="957" ht="4.9000000000000004" customHeight="1"/>
-    <row r="958" ht="4.9000000000000004" customHeight="1"/>
-    <row r="959" ht="4.9000000000000004" customHeight="1"/>
-    <row r="960" ht="4.9000000000000004" customHeight="1"/>
-    <row r="961" ht="4.9000000000000004" customHeight="1"/>
-    <row r="962" ht="4.9000000000000004" customHeight="1"/>
-    <row r="963" ht="4.9000000000000004" customHeight="1"/>
-    <row r="964" ht="4.9000000000000004" customHeight="1"/>
-    <row r="965" ht="4.9000000000000004" customHeight="1"/>
-    <row r="966" ht="4.9000000000000004" customHeight="1"/>
-    <row r="967" ht="4.9000000000000004" customHeight="1"/>
-    <row r="968" ht="4.9000000000000004" customHeight="1"/>
-    <row r="969" ht="4.9000000000000004" customHeight="1"/>
-    <row r="970" ht="4.9000000000000004" customHeight="1"/>
-    <row r="971" ht="4.9000000000000004" customHeight="1"/>
-    <row r="972" ht="4.9000000000000004" customHeight="1"/>
-    <row r="973" ht="4.9000000000000004" customHeight="1"/>
-    <row r="974" ht="4.9000000000000004" customHeight="1"/>
-    <row r="975" ht="4.9000000000000004" customHeight="1"/>
-    <row r="976" ht="4.9000000000000004" customHeight="1"/>
-    <row r="977" ht="4.9000000000000004" customHeight="1"/>
-    <row r="978" ht="4.9000000000000004" customHeight="1"/>
-    <row r="979" ht="4.9000000000000004" customHeight="1"/>
-    <row r="980" ht="4.9000000000000004" customHeight="1"/>
-    <row r="981" ht="4.9000000000000004" customHeight="1"/>
-    <row r="982" ht="4.9000000000000004" customHeight="1"/>
-    <row r="983" ht="4.9000000000000004" customHeight="1"/>
-    <row r="984" ht="4.9000000000000004" customHeight="1"/>
-    <row r="985" ht="4.9000000000000004" customHeight="1"/>
-    <row r="986" ht="4.9000000000000004" customHeight="1"/>
-    <row r="987" ht="4.9000000000000004" customHeight="1"/>
-    <row r="988" ht="4.9000000000000004" customHeight="1"/>
-    <row r="989" ht="4.9000000000000004" customHeight="1"/>
-    <row r="990" ht="4.9000000000000004" customHeight="1"/>
-    <row r="991" ht="4.9000000000000004" customHeight="1"/>
-    <row r="992" ht="4.9000000000000004" customHeight="1"/>
-    <row r="993" ht="4.9000000000000004" customHeight="1"/>
-    <row r="994" ht="4.9000000000000004" customHeight="1"/>
-    <row r="995" ht="4.9000000000000004" customHeight="1"/>
-    <row r="996" ht="4.9000000000000004" customHeight="1"/>
-    <row r="997" ht="4.9000000000000004" customHeight="1"/>
-    <row r="998" ht="4.9000000000000004" customHeight="1"/>
-    <row r="999" ht="4.9000000000000004" customHeight="1"/>
-    <row r="1000" ht="4.9000000000000004" customHeight="1"/>
+    <row r="33" ht="4.95" customHeight="1"/>
+    <row r="34" ht="4.95" customHeight="1"/>
+    <row r="35" ht="4.95" customHeight="1"/>
+    <row r="36" ht="4.95" customHeight="1"/>
+    <row r="37" ht="4.95" customHeight="1"/>
+    <row r="38" ht="4.95" customHeight="1"/>
+    <row r="39" ht="4.95" customHeight="1"/>
+    <row r="40" ht="4.95" customHeight="1"/>
+    <row r="41" ht="4.95" customHeight="1"/>
+    <row r="42" ht="4.95" customHeight="1"/>
+    <row r="43" ht="4.95" customHeight="1"/>
+    <row r="44" ht="4.95" customHeight="1"/>
+    <row r="45" ht="4.95" customHeight="1"/>
+    <row r="46" ht="4.95" customHeight="1"/>
+    <row r="47" ht="4.95" customHeight="1"/>
+    <row r="48" ht="4.95" customHeight="1"/>
+    <row r="49" ht="4.95" customHeight="1"/>
+    <row r="50" ht="4.95" customHeight="1"/>
+    <row r="51" ht="4.95" customHeight="1"/>
+    <row r="52" ht="4.95" customHeight="1"/>
+    <row r="53" ht="4.95" customHeight="1"/>
+    <row r="54" ht="4.95" customHeight="1"/>
+    <row r="55" ht="4.95" customHeight="1"/>
+    <row r="56" ht="4.95" customHeight="1"/>
+    <row r="57" ht="4.95" customHeight="1"/>
+    <row r="58" ht="4.95" customHeight="1"/>
+    <row r="59" ht="4.95" customHeight="1"/>
+    <row r="60" ht="4.95" customHeight="1"/>
+    <row r="61" ht="4.95" customHeight="1"/>
+    <row r="62" ht="4.95" customHeight="1"/>
+    <row r="63" ht="4.95" customHeight="1"/>
+    <row r="64" ht="4.95" customHeight="1"/>
+    <row r="65" ht="4.95" customHeight="1"/>
+    <row r="66" ht="4.95" customHeight="1"/>
+    <row r="67" ht="4.95" customHeight="1"/>
+    <row r="68" ht="4.95" customHeight="1"/>
+    <row r="69" ht="4.95" customHeight="1"/>
+    <row r="70" ht="4.95" customHeight="1"/>
+    <row r="71" ht="4.95" customHeight="1"/>
+    <row r="72" ht="4.95" customHeight="1"/>
+    <row r="73" ht="4.95" customHeight="1"/>
+    <row r="74" ht="4.95" customHeight="1"/>
+    <row r="75" ht="4.95" customHeight="1"/>
+    <row r="76" ht="4.95" customHeight="1"/>
+    <row r="77" ht="4.95" customHeight="1"/>
+    <row r="78" ht="4.95" customHeight="1"/>
+    <row r="79" ht="4.95" customHeight="1"/>
+    <row r="80" ht="4.95" customHeight="1"/>
+    <row r="81" ht="4.95" customHeight="1"/>
+    <row r="82" ht="4.95" customHeight="1"/>
+    <row r="83" ht="4.95" customHeight="1"/>
+    <row r="84" ht="4.95" customHeight="1"/>
+    <row r="85" ht="4.95" customHeight="1"/>
+    <row r="86" ht="4.95" customHeight="1"/>
+    <row r="87" ht="4.95" customHeight="1"/>
+    <row r="88" ht="4.95" customHeight="1"/>
+    <row r="89" ht="4.95" customHeight="1"/>
+    <row r="90" ht="4.95" customHeight="1"/>
+    <row r="91" ht="4.95" customHeight="1"/>
+    <row r="92" ht="4.95" customHeight="1"/>
+    <row r="93" ht="4.95" customHeight="1"/>
+    <row r="94" ht="4.95" customHeight="1"/>
+    <row r="95" ht="4.95" customHeight="1"/>
+    <row r="96" ht="4.95" customHeight="1"/>
+    <row r="97" ht="4.95" customHeight="1"/>
+    <row r="98" ht="4.95" customHeight="1"/>
+    <row r="99" ht="4.95" customHeight="1"/>
+    <row r="100" ht="4.95" customHeight="1"/>
+    <row r="101" ht="4.95" customHeight="1"/>
+    <row r="102" ht="4.95" customHeight="1"/>
+    <row r="103" ht="4.95" customHeight="1"/>
+    <row r="104" ht="4.95" customHeight="1"/>
+    <row r="105" ht="4.95" customHeight="1"/>
+    <row r="106" ht="4.95" customHeight="1"/>
+    <row r="107" ht="4.95" customHeight="1"/>
+    <row r="108" ht="4.95" customHeight="1"/>
+    <row r="109" ht="4.95" customHeight="1"/>
+    <row r="110" ht="4.95" customHeight="1"/>
+    <row r="111" ht="4.95" customHeight="1"/>
+    <row r="112" ht="4.95" customHeight="1"/>
+    <row r="113" ht="4.95" customHeight="1"/>
+    <row r="114" ht="4.95" customHeight="1"/>
+    <row r="115" ht="4.95" customHeight="1"/>
+    <row r="116" ht="4.95" customHeight="1"/>
+    <row r="117" ht="4.95" customHeight="1"/>
+    <row r="118" ht="4.95" customHeight="1"/>
+    <row r="119" ht="4.95" customHeight="1"/>
+    <row r="120" ht="4.95" customHeight="1"/>
+    <row r="121" ht="4.95" customHeight="1"/>
+    <row r="122" ht="4.95" customHeight="1"/>
+    <row r="123" ht="4.95" customHeight="1"/>
+    <row r="124" ht="4.95" customHeight="1"/>
+    <row r="125" ht="4.95" customHeight="1"/>
+    <row r="126" ht="4.95" customHeight="1"/>
+    <row r="127" ht="4.95" customHeight="1"/>
+    <row r="128" ht="4.95" customHeight="1"/>
+    <row r="129" ht="4.95" customHeight="1"/>
+    <row r="130" ht="4.95" customHeight="1"/>
+    <row r="131" ht="4.95" customHeight="1"/>
+    <row r="132" ht="4.95" customHeight="1"/>
+    <row r="133" ht="4.95" customHeight="1"/>
+    <row r="134" ht="4.95" customHeight="1"/>
+    <row r="135" ht="4.95" customHeight="1"/>
+    <row r="136" ht="4.95" customHeight="1"/>
+    <row r="137" ht="4.95" customHeight="1"/>
+    <row r="138" ht="4.95" customHeight="1"/>
+    <row r="139" ht="4.95" customHeight="1"/>
+    <row r="140" ht="4.95" customHeight="1"/>
+    <row r="141" ht="4.95" customHeight="1"/>
+    <row r="142" ht="4.95" customHeight="1"/>
+    <row r="143" ht="4.95" customHeight="1"/>
+    <row r="144" ht="4.95" customHeight="1"/>
+    <row r="145" ht="4.95" customHeight="1"/>
+    <row r="146" ht="4.95" customHeight="1"/>
+    <row r="147" ht="4.95" customHeight="1"/>
+    <row r="148" ht="4.95" customHeight="1"/>
+    <row r="149" ht="4.95" customHeight="1"/>
+    <row r="150" ht="4.95" customHeight="1"/>
+    <row r="151" ht="4.95" customHeight="1"/>
+    <row r="152" ht="4.95" customHeight="1"/>
+    <row r="153" ht="4.95" customHeight="1"/>
+    <row r="154" ht="4.95" customHeight="1"/>
+    <row r="155" ht="4.95" customHeight="1"/>
+    <row r="156" ht="4.95" customHeight="1"/>
+    <row r="157" ht="4.95" customHeight="1"/>
+    <row r="158" ht="4.95" customHeight="1"/>
+    <row r="159" ht="4.95" customHeight="1"/>
+    <row r="160" ht="4.95" customHeight="1"/>
+    <row r="161" ht="4.95" customHeight="1"/>
+    <row r="162" ht="4.95" customHeight="1"/>
+    <row r="163" ht="4.95" customHeight="1"/>
+    <row r="164" ht="4.95" customHeight="1"/>
+    <row r="165" ht="4.95" customHeight="1"/>
+    <row r="166" ht="4.95" customHeight="1"/>
+    <row r="167" ht="4.95" customHeight="1"/>
+    <row r="168" ht="4.95" customHeight="1"/>
+    <row r="169" ht="4.95" customHeight="1"/>
+    <row r="170" ht="4.95" customHeight="1"/>
+    <row r="171" ht="4.95" customHeight="1"/>
+    <row r="172" ht="4.95" customHeight="1"/>
+    <row r="173" ht="4.95" customHeight="1"/>
+    <row r="174" ht="4.95" customHeight="1"/>
+    <row r="175" ht="4.95" customHeight="1"/>
+    <row r="176" ht="4.95" customHeight="1"/>
+    <row r="177" ht="4.95" customHeight="1"/>
+    <row r="178" ht="4.95" customHeight="1"/>
+    <row r="179" ht="4.95" customHeight="1"/>
+    <row r="180" ht="4.95" customHeight="1"/>
+    <row r="181" ht="4.95" customHeight="1"/>
+    <row r="182" ht="4.95" customHeight="1"/>
+    <row r="183" ht="4.95" customHeight="1"/>
+    <row r="184" ht="4.95" customHeight="1"/>
+    <row r="185" ht="4.95" customHeight="1"/>
+    <row r="186" ht="4.95" customHeight="1"/>
+    <row r="187" ht="4.95" customHeight="1"/>
+    <row r="188" ht="4.95" customHeight="1"/>
+    <row r="189" ht="4.95" customHeight="1"/>
+    <row r="190" ht="4.95" customHeight="1"/>
+    <row r="191" ht="4.95" customHeight="1"/>
+    <row r="192" ht="4.95" customHeight="1"/>
+    <row r="193" ht="4.95" customHeight="1"/>
+    <row r="194" ht="4.95" customHeight="1"/>
+    <row r="195" ht="4.95" customHeight="1"/>
+    <row r="196" ht="4.95" customHeight="1"/>
+    <row r="197" ht="4.95" customHeight="1"/>
+    <row r="198" ht="4.95" customHeight="1"/>
+    <row r="199" ht="4.95" customHeight="1"/>
+    <row r="200" ht="4.95" customHeight="1"/>
+    <row r="201" ht="4.95" customHeight="1"/>
+    <row r="202" ht="4.95" customHeight="1"/>
+    <row r="203" ht="4.95" customHeight="1"/>
+    <row r="204" ht="4.95" customHeight="1"/>
+    <row r="205" ht="4.95" customHeight="1"/>
+    <row r="206" ht="4.95" customHeight="1"/>
+    <row r="207" ht="4.95" customHeight="1"/>
+    <row r="208" ht="4.95" customHeight="1"/>
+    <row r="209" ht="4.95" customHeight="1"/>
+    <row r="210" ht="4.95" customHeight="1"/>
+    <row r="211" ht="4.95" customHeight="1"/>
+    <row r="212" ht="4.95" customHeight="1"/>
+    <row r="213" ht="4.95" customHeight="1"/>
+    <row r="214" ht="4.95" customHeight="1"/>
+    <row r="215" ht="4.95" customHeight="1"/>
+    <row r="216" ht="4.95" customHeight="1"/>
+    <row r="217" ht="4.95" customHeight="1"/>
+    <row r="218" ht="4.95" customHeight="1"/>
+    <row r="219" ht="4.95" customHeight="1"/>
+    <row r="220" ht="4.95" customHeight="1"/>
+    <row r="221" ht="4.95" customHeight="1"/>
+    <row r="222" ht="4.95" customHeight="1"/>
+    <row r="223" ht="4.95" customHeight="1"/>
+    <row r="224" ht="4.95" customHeight="1"/>
+    <row r="225" ht="4.95" customHeight="1"/>
+    <row r="226" ht="4.95" customHeight="1"/>
+    <row r="227" ht="4.95" customHeight="1"/>
+    <row r="228" ht="4.95" customHeight="1"/>
+    <row r="229" ht="4.95" customHeight="1"/>
+    <row r="230" ht="4.95" customHeight="1"/>
+    <row r="231" ht="4.95" customHeight="1"/>
+    <row r="232" ht="4.95" customHeight="1"/>
+    <row r="233" ht="4.95" customHeight="1"/>
+    <row r="234" ht="4.95" customHeight="1"/>
+    <row r="235" ht="4.95" customHeight="1"/>
+    <row r="236" ht="4.95" customHeight="1"/>
+    <row r="237" ht="4.95" customHeight="1"/>
+    <row r="238" ht="4.95" customHeight="1"/>
+    <row r="239" ht="4.95" customHeight="1"/>
+    <row r="240" ht="4.95" customHeight="1"/>
+    <row r="241" ht="4.95" customHeight="1"/>
+    <row r="242" ht="4.95" customHeight="1"/>
+    <row r="243" ht="4.95" customHeight="1"/>
+    <row r="244" ht="4.95" customHeight="1"/>
+    <row r="245" ht="4.95" customHeight="1"/>
+    <row r="246" ht="4.95" customHeight="1"/>
+    <row r="247" ht="4.95" customHeight="1"/>
+    <row r="248" ht="4.95" customHeight="1"/>
+    <row r="249" ht="4.95" customHeight="1"/>
+    <row r="250" ht="4.95" customHeight="1"/>
+    <row r="251" ht="4.95" customHeight="1"/>
+    <row r="252" ht="4.95" customHeight="1"/>
+    <row r="253" ht="4.95" customHeight="1"/>
+    <row r="254" ht="4.95" customHeight="1"/>
+    <row r="255" ht="4.95" customHeight="1"/>
+    <row r="256" ht="4.95" customHeight="1"/>
+    <row r="257" ht="4.95" customHeight="1"/>
+    <row r="258" ht="4.95" customHeight="1"/>
+    <row r="259" ht="4.95" customHeight="1"/>
+    <row r="260" ht="4.95" customHeight="1"/>
+    <row r="261" ht="4.95" customHeight="1"/>
+    <row r="262" ht="4.95" customHeight="1"/>
+    <row r="263" ht="4.95" customHeight="1"/>
+    <row r="264" ht="4.95" customHeight="1"/>
+    <row r="265" ht="4.95" customHeight="1"/>
+    <row r="266" ht="4.95" customHeight="1"/>
+    <row r="267" ht="4.95" customHeight="1"/>
+    <row r="268" ht="4.95" customHeight="1"/>
+    <row r="269" ht="4.95" customHeight="1"/>
+    <row r="270" ht="4.95" customHeight="1"/>
+    <row r="271" ht="4.95" customHeight="1"/>
+    <row r="272" ht="4.95" customHeight="1"/>
+    <row r="273" ht="4.95" customHeight="1"/>
+    <row r="274" ht="4.95" customHeight="1"/>
+    <row r="275" ht="4.95" customHeight="1"/>
+    <row r="276" ht="4.95" customHeight="1"/>
+    <row r="277" ht="4.95" customHeight="1"/>
+    <row r="278" ht="4.95" customHeight="1"/>
+    <row r="279" ht="4.95" customHeight="1"/>
+    <row r="280" ht="4.95" customHeight="1"/>
+    <row r="281" ht="4.95" customHeight="1"/>
+    <row r="282" ht="4.95" customHeight="1"/>
+    <row r="283" ht="4.95" customHeight="1"/>
+    <row r="284" ht="4.95" customHeight="1"/>
+    <row r="285" ht="4.95" customHeight="1"/>
+    <row r="286" ht="4.95" customHeight="1"/>
+    <row r="287" ht="4.95" customHeight="1"/>
+    <row r="288" ht="4.95" customHeight="1"/>
+    <row r="289" ht="4.95" customHeight="1"/>
+    <row r="290" ht="4.95" customHeight="1"/>
+    <row r="291" ht="4.95" customHeight="1"/>
+    <row r="292" ht="4.95" customHeight="1"/>
+    <row r="293" ht="4.95" customHeight="1"/>
+    <row r="294" ht="4.95" customHeight="1"/>
+    <row r="295" ht="4.95" customHeight="1"/>
+    <row r="296" ht="4.95" customHeight="1"/>
+    <row r="297" ht="4.95" customHeight="1"/>
+    <row r="298" ht="4.95" customHeight="1"/>
+    <row r="299" ht="4.95" customHeight="1"/>
+    <row r="300" ht="4.95" customHeight="1"/>
+    <row r="301" ht="4.95" customHeight="1"/>
+    <row r="302" ht="4.95" customHeight="1"/>
+    <row r="303" ht="4.95" customHeight="1"/>
+    <row r="304" ht="4.95" customHeight="1"/>
+    <row r="305" ht="4.95" customHeight="1"/>
+    <row r="306" ht="4.95" customHeight="1"/>
+    <row r="307" ht="4.95" customHeight="1"/>
+    <row r="308" ht="4.95" customHeight="1"/>
+    <row r="309" ht="4.95" customHeight="1"/>
+    <row r="310" ht="4.95" customHeight="1"/>
+    <row r="311" ht="4.95" customHeight="1"/>
+    <row r="312" ht="4.95" customHeight="1"/>
+    <row r="313" ht="4.95" customHeight="1"/>
+    <row r="314" ht="4.95" customHeight="1"/>
+    <row r="315" ht="4.95" customHeight="1"/>
+    <row r="316" ht="4.95" customHeight="1"/>
+    <row r="317" ht="4.95" customHeight="1"/>
+    <row r="318" ht="4.95" customHeight="1"/>
+    <row r="319" ht="4.95" customHeight="1"/>
+    <row r="320" ht="4.95" customHeight="1"/>
+    <row r="321" ht="4.95" customHeight="1"/>
+    <row r="322" ht="4.95" customHeight="1"/>
+    <row r="323" ht="4.95" customHeight="1"/>
+    <row r="324" ht="4.95" customHeight="1"/>
+    <row r="325" ht="4.95" customHeight="1"/>
+    <row r="326" ht="4.95" customHeight="1"/>
+    <row r="327" ht="4.95" customHeight="1"/>
+    <row r="328" ht="4.95" customHeight="1"/>
+    <row r="329" ht="4.95" customHeight="1"/>
+    <row r="330" ht="4.95" customHeight="1"/>
+    <row r="331" ht="4.95" customHeight="1"/>
+    <row r="332" ht="4.95" customHeight="1"/>
+    <row r="333" ht="4.95" customHeight="1"/>
+    <row r="334" ht="4.95" customHeight="1"/>
+    <row r="335" ht="4.95" customHeight="1"/>
+    <row r="336" ht="4.95" customHeight="1"/>
+    <row r="337" ht="4.95" customHeight="1"/>
+    <row r="338" ht="4.95" customHeight="1"/>
+    <row r="339" ht="4.95" customHeight="1"/>
+    <row r="340" ht="4.95" customHeight="1"/>
+    <row r="341" ht="4.95" customHeight="1"/>
+    <row r="342" ht="4.95" customHeight="1"/>
+    <row r="343" ht="4.95" customHeight="1"/>
+    <row r="344" ht="4.95" customHeight="1"/>
+    <row r="345" ht="4.95" customHeight="1"/>
+    <row r="346" ht="4.95" customHeight="1"/>
+    <row r="347" ht="4.95" customHeight="1"/>
+    <row r="348" ht="4.95" customHeight="1"/>
+    <row r="349" ht="4.95" customHeight="1"/>
+    <row r="350" ht="4.95" customHeight="1"/>
+    <row r="351" ht="4.95" customHeight="1"/>
+    <row r="352" ht="4.95" customHeight="1"/>
+    <row r="353" ht="4.95" customHeight="1"/>
+    <row r="354" ht="4.95" customHeight="1"/>
+    <row r="355" ht="4.95" customHeight="1"/>
+    <row r="356" ht="4.95" customHeight="1"/>
+    <row r="357" ht="4.95" customHeight="1"/>
+    <row r="358" ht="4.95" customHeight="1"/>
+    <row r="359" ht="4.95" customHeight="1"/>
+    <row r="360" ht="4.95" customHeight="1"/>
+    <row r="361" ht="4.95" customHeight="1"/>
+    <row r="362" ht="4.95" customHeight="1"/>
+    <row r="363" ht="4.95" customHeight="1"/>
+    <row r="364" ht="4.95" customHeight="1"/>
+    <row r="365" ht="4.95" customHeight="1"/>
+    <row r="366" ht="4.95" customHeight="1"/>
+    <row r="367" ht="4.95" customHeight="1"/>
+    <row r="368" ht="4.95" customHeight="1"/>
+    <row r="369" ht="4.95" customHeight="1"/>
+    <row r="370" ht="4.95" customHeight="1"/>
+    <row r="371" ht="4.95" customHeight="1"/>
+    <row r="372" ht="4.95" customHeight="1"/>
+    <row r="373" ht="4.95" customHeight="1"/>
+    <row r="374" ht="4.95" customHeight="1"/>
+    <row r="375" ht="4.95" customHeight="1"/>
+    <row r="376" ht="4.95" customHeight="1"/>
+    <row r="377" ht="4.95" customHeight="1"/>
+    <row r="378" ht="4.95" customHeight="1"/>
+    <row r="379" ht="4.95" customHeight="1"/>
+    <row r="380" ht="4.95" customHeight="1"/>
+    <row r="381" ht="4.95" customHeight="1"/>
+    <row r="382" ht="4.95" customHeight="1"/>
+    <row r="383" ht="4.95" customHeight="1"/>
+    <row r="384" ht="4.95" customHeight="1"/>
+    <row r="385" ht="4.95" customHeight="1"/>
+    <row r="386" ht="4.95" customHeight="1"/>
+    <row r="387" ht="4.95" customHeight="1"/>
+    <row r="388" ht="4.95" customHeight="1"/>
+    <row r="389" ht="4.95" customHeight="1"/>
+    <row r="390" ht="4.95" customHeight="1"/>
+    <row r="391" ht="4.95" customHeight="1"/>
+    <row r="392" ht="4.95" customHeight="1"/>
+    <row r="393" ht="4.95" customHeight="1"/>
+    <row r="394" ht="4.95" customHeight="1"/>
+    <row r="395" ht="4.95" customHeight="1"/>
+    <row r="396" ht="4.95" customHeight="1"/>
+    <row r="397" ht="4.95" customHeight="1"/>
+    <row r="398" ht="4.95" customHeight="1"/>
+    <row r="399" ht="4.95" customHeight="1"/>
+    <row r="400" ht="4.95" customHeight="1"/>
+    <row r="401" ht="4.95" customHeight="1"/>
+    <row r="402" ht="4.95" customHeight="1"/>
+    <row r="403" ht="4.95" customHeight="1"/>
+    <row r="404" ht="4.95" customHeight="1"/>
+    <row r="405" ht="4.95" customHeight="1"/>
+    <row r="406" ht="4.95" customHeight="1"/>
+    <row r="407" ht="4.95" customHeight="1"/>
+    <row r="408" ht="4.95" customHeight="1"/>
+    <row r="409" ht="4.95" customHeight="1"/>
+    <row r="410" ht="4.95" customHeight="1"/>
+    <row r="411" ht="4.95" customHeight="1"/>
+    <row r="412" ht="4.95" customHeight="1"/>
+    <row r="413" ht="4.95" customHeight="1"/>
+    <row r="414" ht="4.95" customHeight="1"/>
+    <row r="415" ht="4.95" customHeight="1"/>
+    <row r="416" ht="4.95" customHeight="1"/>
+    <row r="417" ht="4.95" customHeight="1"/>
+    <row r="418" ht="4.95" customHeight="1"/>
+    <row r="419" ht="4.95" customHeight="1"/>
+    <row r="420" ht="4.95" customHeight="1"/>
+    <row r="421" ht="4.95" customHeight="1"/>
+    <row r="422" ht="4.95" customHeight="1"/>
+    <row r="423" ht="4.95" customHeight="1"/>
+    <row r="424" ht="4.95" customHeight="1"/>
+    <row r="425" ht="4.95" customHeight="1"/>
+    <row r="426" ht="4.95" customHeight="1"/>
+    <row r="427" ht="4.95" customHeight="1"/>
+    <row r="428" ht="4.95" customHeight="1"/>
+    <row r="429" ht="4.95" customHeight="1"/>
+    <row r="430" ht="4.95" customHeight="1"/>
+    <row r="431" ht="4.95" customHeight="1"/>
+    <row r="432" ht="4.95" customHeight="1"/>
+    <row r="433" ht="4.95" customHeight="1"/>
+    <row r="434" ht="4.95" customHeight="1"/>
+    <row r="435" ht="4.95" customHeight="1"/>
+    <row r="436" ht="4.95" customHeight="1"/>
+    <row r="437" ht="4.95" customHeight="1"/>
+    <row r="438" ht="4.95" customHeight="1"/>
+    <row r="439" ht="4.95" customHeight="1"/>
+    <row r="440" ht="4.95" customHeight="1"/>
+    <row r="441" ht="4.95" customHeight="1"/>
+    <row r="442" ht="4.95" customHeight="1"/>
+    <row r="443" ht="4.95" customHeight="1"/>
+    <row r="444" ht="4.95" customHeight="1"/>
+    <row r="445" ht="4.95" customHeight="1"/>
+    <row r="446" ht="4.95" customHeight="1"/>
+    <row r="447" ht="4.95" customHeight="1"/>
+    <row r="448" ht="4.95" customHeight="1"/>
+    <row r="449" ht="4.95" customHeight="1"/>
+    <row r="450" ht="4.95" customHeight="1"/>
+    <row r="451" ht="4.95" customHeight="1"/>
+    <row r="452" ht="4.95" customHeight="1"/>
+    <row r="453" ht="4.95" customHeight="1"/>
+    <row r="454" ht="4.95" customHeight="1"/>
+    <row r="455" ht="4.95" customHeight="1"/>
+    <row r="456" ht="4.95" customHeight="1"/>
+    <row r="457" ht="4.95" customHeight="1"/>
+    <row r="458" ht="4.95" customHeight="1"/>
+    <row r="459" ht="4.95" customHeight="1"/>
+    <row r="460" ht="4.95" customHeight="1"/>
+    <row r="461" ht="4.95" customHeight="1"/>
+    <row r="462" ht="4.95" customHeight="1"/>
+    <row r="463" ht="4.95" customHeight="1"/>
+    <row r="464" ht="4.95" customHeight="1"/>
+    <row r="465" ht="4.95" customHeight="1"/>
+    <row r="466" ht="4.95" customHeight="1"/>
+    <row r="467" ht="4.95" customHeight="1"/>
+    <row r="468" ht="4.95" customHeight="1"/>
+    <row r="469" ht="4.95" customHeight="1"/>
+    <row r="470" ht="4.95" customHeight="1"/>
+    <row r="471" ht="4.95" customHeight="1"/>
+    <row r="472" ht="4.95" customHeight="1"/>
+    <row r="473" ht="4.95" customHeight="1"/>
+    <row r="474" ht="4.95" customHeight="1"/>
+    <row r="475" ht="4.95" customHeight="1"/>
+    <row r="476" ht="4.95" customHeight="1"/>
+    <row r="477" ht="4.95" customHeight="1"/>
+    <row r="478" ht="4.95" customHeight="1"/>
+    <row r="479" ht="4.95" customHeight="1"/>
+    <row r="480" ht="4.95" customHeight="1"/>
+    <row r="481" ht="4.95" customHeight="1"/>
+    <row r="482" ht="4.95" customHeight="1"/>
+    <row r="483" ht="4.95" customHeight="1"/>
+    <row r="484" ht="4.95" customHeight="1"/>
+    <row r="485" ht="4.95" customHeight="1"/>
+    <row r="486" ht="4.95" customHeight="1"/>
+    <row r="487" ht="4.95" customHeight="1"/>
+    <row r="488" ht="4.95" customHeight="1"/>
+    <row r="489" ht="4.95" customHeight="1"/>
+    <row r="490" ht="4.95" customHeight="1"/>
+    <row r="491" ht="4.95" customHeight="1"/>
+    <row r="492" ht="4.95" customHeight="1"/>
+    <row r="493" ht="4.95" customHeight="1"/>
+    <row r="494" ht="4.95" customHeight="1"/>
+    <row r="495" ht="4.95" customHeight="1"/>
+    <row r="496" ht="4.95" customHeight="1"/>
+    <row r="497" ht="4.95" customHeight="1"/>
+    <row r="498" ht="4.95" customHeight="1"/>
+    <row r="499" ht="4.95" customHeight="1"/>
+    <row r="500" ht="4.95" customHeight="1"/>
+    <row r="501" ht="4.95" customHeight="1"/>
+    <row r="502" ht="4.95" customHeight="1"/>
+    <row r="503" ht="4.95" customHeight="1"/>
+    <row r="504" ht="4.95" customHeight="1"/>
+    <row r="505" ht="4.95" customHeight="1"/>
+    <row r="506" ht="4.95" customHeight="1"/>
+    <row r="507" ht="4.95" customHeight="1"/>
+    <row r="508" ht="4.95" customHeight="1"/>
+    <row r="509" ht="4.95" customHeight="1"/>
+    <row r="510" ht="4.95" customHeight="1"/>
+    <row r="511" ht="4.95" customHeight="1"/>
+    <row r="512" ht="4.95" customHeight="1"/>
+    <row r="513" ht="4.95" customHeight="1"/>
+    <row r="514" ht="4.95" customHeight="1"/>
+    <row r="515" ht="4.95" customHeight="1"/>
+    <row r="516" ht="4.95" customHeight="1"/>
+    <row r="517" ht="4.95" customHeight="1"/>
+    <row r="518" ht="4.95" customHeight="1"/>
+    <row r="519" ht="4.95" customHeight="1"/>
+    <row r="520" ht="4.95" customHeight="1"/>
+    <row r="521" ht="4.95" customHeight="1"/>
+    <row r="522" ht="4.95" customHeight="1"/>
+    <row r="523" ht="4.95" customHeight="1"/>
+    <row r="524" ht="4.95" customHeight="1"/>
+    <row r="525" ht="4.95" customHeight="1"/>
+    <row r="526" ht="4.95" customHeight="1"/>
+    <row r="527" ht="4.95" customHeight="1"/>
+    <row r="528" ht="4.95" customHeight="1"/>
+    <row r="529" ht="4.95" customHeight="1"/>
+    <row r="530" ht="4.95" customHeight="1"/>
+    <row r="531" ht="4.95" customHeight="1"/>
+    <row r="532" ht="4.95" customHeight="1"/>
+    <row r="533" ht="4.95" customHeight="1"/>
+    <row r="534" ht="4.95" customHeight="1"/>
+    <row r="535" ht="4.95" customHeight="1"/>
+    <row r="536" ht="4.95" customHeight="1"/>
+    <row r="537" ht="4.95" customHeight="1"/>
+    <row r="538" ht="4.95" customHeight="1"/>
+    <row r="539" ht="4.95" customHeight="1"/>
+    <row r="540" ht="4.95" customHeight="1"/>
+    <row r="541" ht="4.95" customHeight="1"/>
+    <row r="542" ht="4.95" customHeight="1"/>
+    <row r="543" ht="4.95" customHeight="1"/>
+    <row r="544" ht="4.95" customHeight="1"/>
+    <row r="545" ht="4.95" customHeight="1"/>
+    <row r="546" ht="4.95" customHeight="1"/>
+    <row r="547" ht="4.95" customHeight="1"/>
+    <row r="548" ht="4.95" customHeight="1"/>
+    <row r="549" ht="4.95" customHeight="1"/>
+    <row r="550" ht="4.95" customHeight="1"/>
+    <row r="551" ht="4.95" customHeight="1"/>
+    <row r="552" ht="4.95" customHeight="1"/>
+    <row r="553" ht="4.95" customHeight="1"/>
+    <row r="554" ht="4.95" customHeight="1"/>
+    <row r="555" ht="4.95" customHeight="1"/>
+    <row r="556" ht="4.95" customHeight="1"/>
+    <row r="557" ht="4.95" customHeight="1"/>
+    <row r="558" ht="4.95" customHeight="1"/>
+    <row r="559" ht="4.95" customHeight="1"/>
+    <row r="560" ht="4.95" customHeight="1"/>
+    <row r="561" ht="4.95" customHeight="1"/>
+    <row r="562" ht="4.95" customHeight="1"/>
+    <row r="563" ht="4.95" customHeight="1"/>
+    <row r="564" ht="4.95" customHeight="1"/>
+    <row r="565" ht="4.95" customHeight="1"/>
+    <row r="566" ht="4.95" customHeight="1"/>
+    <row r="567" ht="4.95" customHeight="1"/>
+    <row r="568" ht="4.95" customHeight="1"/>
+    <row r="569" ht="4.95" customHeight="1"/>
+    <row r="570" ht="4.95" customHeight="1"/>
+    <row r="571" ht="4.95" customHeight="1"/>
+    <row r="572" ht="4.95" customHeight="1"/>
+    <row r="573" ht="4.95" customHeight="1"/>
+    <row r="574" ht="4.95" customHeight="1"/>
+    <row r="575" ht="4.95" customHeight="1"/>
+    <row r="576" ht="4.95" customHeight="1"/>
+    <row r="577" ht="4.95" customHeight="1"/>
+    <row r="578" ht="4.95" customHeight="1"/>
+    <row r="579" ht="4.95" customHeight="1"/>
+    <row r="580" ht="4.95" customHeight="1"/>
+    <row r="581" ht="4.95" customHeight="1"/>
+    <row r="582" ht="4.95" customHeight="1"/>
+    <row r="583" ht="4.95" customHeight="1"/>
+    <row r="584" ht="4.95" customHeight="1"/>
+    <row r="585" ht="4.95" customHeight="1"/>
+    <row r="586" ht="4.95" customHeight="1"/>
+    <row r="587" ht="4.95" customHeight="1"/>
+    <row r="588" ht="4.95" customHeight="1"/>
+    <row r="589" ht="4.95" customHeight="1"/>
+    <row r="590" ht="4.95" customHeight="1"/>
+    <row r="591" ht="4.95" customHeight="1"/>
+    <row r="592" ht="4.95" customHeight="1"/>
+    <row r="593" ht="4.95" customHeight="1"/>
+    <row r="594" ht="4.95" customHeight="1"/>
+    <row r="595" ht="4.95" customHeight="1"/>
+    <row r="596" ht="4.95" customHeight="1"/>
+    <row r="597" ht="4.95" customHeight="1"/>
+    <row r="598" ht="4.95" customHeight="1"/>
+    <row r="599" ht="4.95" customHeight="1"/>
+    <row r="600" ht="4.95" customHeight="1"/>
+    <row r="601" ht="4.95" customHeight="1"/>
+    <row r="602" ht="4.95" customHeight="1"/>
+    <row r="603" ht="4.95" customHeight="1"/>
+    <row r="604" ht="4.95" customHeight="1"/>
+    <row r="605" ht="4.95" customHeight="1"/>
+    <row r="606" ht="4.95" customHeight="1"/>
+    <row r="607" ht="4.95" customHeight="1"/>
+    <row r="608" ht="4.95" customHeight="1"/>
+    <row r="609" ht="4.95" customHeight="1"/>
+    <row r="610" ht="4.95" customHeight="1"/>
+    <row r="611" ht="4.95" customHeight="1"/>
+    <row r="612" ht="4.95" customHeight="1"/>
+    <row r="613" ht="4.95" customHeight="1"/>
+    <row r="614" ht="4.95" customHeight="1"/>
+    <row r="615" ht="4.95" customHeight="1"/>
+    <row r="616" ht="4.95" customHeight="1"/>
+    <row r="617" ht="4.95" customHeight="1"/>
+    <row r="618" ht="4.95" customHeight="1"/>
+    <row r="619" ht="4.95" customHeight="1"/>
+    <row r="620" ht="4.95" customHeight="1"/>
+    <row r="621" ht="4.95" customHeight="1"/>
+    <row r="622" ht="4.95" customHeight="1"/>
+    <row r="623" ht="4.95" customHeight="1"/>
+    <row r="624" ht="4.95" customHeight="1"/>
+    <row r="625" ht="4.95" customHeight="1"/>
+    <row r="626" ht="4.95" customHeight="1"/>
+    <row r="627" ht="4.95" customHeight="1"/>
+    <row r="628" ht="4.95" customHeight="1"/>
+    <row r="629" ht="4.95" customHeight="1"/>
+    <row r="630" ht="4.95" customHeight="1"/>
+    <row r="631" ht="4.95" customHeight="1"/>
+    <row r="632" ht="4.95" customHeight="1"/>
+    <row r="633" ht="4.95" customHeight="1"/>
+    <row r="634" ht="4.95" customHeight="1"/>
+    <row r="635" ht="4.95" customHeight="1"/>
+    <row r="636" ht="4.95" customHeight="1"/>
+    <row r="637" ht="4.95" customHeight="1"/>
+    <row r="638" ht="4.95" customHeight="1"/>
+    <row r="639" ht="4.95" customHeight="1"/>
+    <row r="640" ht="4.95" customHeight="1"/>
+    <row r="641" ht="4.95" customHeight="1"/>
+    <row r="642" ht="4.95" customHeight="1"/>
+    <row r="643" ht="4.95" customHeight="1"/>
+    <row r="644" ht="4.95" customHeight="1"/>
+    <row r="645" ht="4.95" customHeight="1"/>
+    <row r="646" ht="4.95" customHeight="1"/>
+    <row r="647" ht="4.95" customHeight="1"/>
+    <row r="648" ht="4.95" customHeight="1"/>
+    <row r="649" ht="4.95" customHeight="1"/>
+    <row r="650" ht="4.95" customHeight="1"/>
+    <row r="651" ht="4.95" customHeight="1"/>
+    <row r="652" ht="4.95" customHeight="1"/>
+    <row r="653" ht="4.95" customHeight="1"/>
+    <row r="654" ht="4.95" customHeight="1"/>
+    <row r="655" ht="4.95" customHeight="1"/>
+    <row r="656" ht="4.95" customHeight="1"/>
+    <row r="657" ht="4.95" customHeight="1"/>
+    <row r="658" ht="4.95" customHeight="1"/>
+    <row r="659" ht="4.95" customHeight="1"/>
+    <row r="660" ht="4.95" customHeight="1"/>
+    <row r="661" ht="4.95" customHeight="1"/>
+    <row r="662" ht="4.95" customHeight="1"/>
+    <row r="663" ht="4.95" customHeight="1"/>
+    <row r="664" ht="4.95" customHeight="1"/>
+    <row r="665" ht="4.95" customHeight="1"/>
+    <row r="666" ht="4.95" customHeight="1"/>
+    <row r="667" ht="4.95" customHeight="1"/>
+    <row r="668" ht="4.95" customHeight="1"/>
+    <row r="669" ht="4.95" customHeight="1"/>
+    <row r="670" ht="4.95" customHeight="1"/>
+    <row r="671" ht="4.95" customHeight="1"/>
+    <row r="672" ht="4.95" customHeight="1"/>
+    <row r="673" ht="4.95" customHeight="1"/>
+    <row r="674" ht="4.95" customHeight="1"/>
+    <row r="675" ht="4.95" customHeight="1"/>
+    <row r="676" ht="4.95" customHeight="1"/>
+    <row r="677" ht="4.95" customHeight="1"/>
+    <row r="678" ht="4.95" customHeight="1"/>
+    <row r="679" ht="4.95" customHeight="1"/>
+    <row r="680" ht="4.95" customHeight="1"/>
+    <row r="681" ht="4.95" customHeight="1"/>
+    <row r="682" ht="4.95" customHeight="1"/>
+    <row r="683" ht="4.95" customHeight="1"/>
+    <row r="684" ht="4.95" customHeight="1"/>
+    <row r="685" ht="4.95" customHeight="1"/>
+    <row r="686" ht="4.95" customHeight="1"/>
+    <row r="687" ht="4.95" customHeight="1"/>
+    <row r="688" ht="4.95" customHeight="1"/>
+    <row r="689" ht="4.95" customHeight="1"/>
+    <row r="690" ht="4.95" customHeight="1"/>
+    <row r="691" ht="4.95" customHeight="1"/>
+    <row r="692" ht="4.95" customHeight="1"/>
+    <row r="693" ht="4.95" customHeight="1"/>
+    <row r="694" ht="4.95" customHeight="1"/>
+    <row r="695" ht="4.95" customHeight="1"/>
+    <row r="696" ht="4.95" customHeight="1"/>
+    <row r="697" ht="4.95" customHeight="1"/>
+    <row r="698" ht="4.95" customHeight="1"/>
+    <row r="699" ht="4.95" customHeight="1"/>
+    <row r="700" ht="4.95" customHeight="1"/>
+    <row r="701" ht="4.95" customHeight="1"/>
+    <row r="702" ht="4.95" customHeight="1"/>
+    <row r="703" ht="4.95" customHeight="1"/>
+    <row r="704" ht="4.95" customHeight="1"/>
+    <row r="705" ht="4.95" customHeight="1"/>
+    <row r="706" ht="4.95" customHeight="1"/>
+    <row r="707" ht="4.95" customHeight="1"/>
+    <row r="708" ht="4.95" customHeight="1"/>
+    <row r="709" ht="4.95" customHeight="1"/>
+    <row r="710" ht="4.95" customHeight="1"/>
+    <row r="711" ht="4.95" customHeight="1"/>
+    <row r="712" ht="4.95" customHeight="1"/>
+    <row r="713" ht="4.95" customHeight="1"/>
+    <row r="714" ht="4.95" customHeight="1"/>
+    <row r="715" ht="4.95" customHeight="1"/>
+    <row r="716" ht="4.95" customHeight="1"/>
+    <row r="717" ht="4.95" customHeight="1"/>
+    <row r="718" ht="4.95" customHeight="1"/>
+    <row r="719" ht="4.95" customHeight="1"/>
+    <row r="720" ht="4.95" customHeight="1"/>
+    <row r="721" ht="4.95" customHeight="1"/>
+    <row r="722" ht="4.95" customHeight="1"/>
+    <row r="723" ht="4.95" customHeight="1"/>
+    <row r="724" ht="4.95" customHeight="1"/>
+    <row r="725" ht="4.95" customHeight="1"/>
+    <row r="726" ht="4.95" customHeight="1"/>
+    <row r="727" ht="4.95" customHeight="1"/>
+    <row r="728" ht="4.95" customHeight="1"/>
+    <row r="729" ht="4.95" customHeight="1"/>
+    <row r="730" ht="4.95" customHeight="1"/>
+    <row r="731" ht="4.95" customHeight="1"/>
+    <row r="732" ht="4.95" customHeight="1"/>
+    <row r="733" ht="4.95" customHeight="1"/>
+    <row r="734" ht="4.95" customHeight="1"/>
+    <row r="735" ht="4.95" customHeight="1"/>
+    <row r="736" ht="4.95" customHeight="1"/>
+    <row r="737" ht="4.95" customHeight="1"/>
+    <row r="738" ht="4.95" customHeight="1"/>
+    <row r="739" ht="4.95" customHeight="1"/>
+    <row r="740" ht="4.95" customHeight="1"/>
+    <row r="741" ht="4.95" customHeight="1"/>
+    <row r="742" ht="4.95" customHeight="1"/>
+    <row r="743" ht="4.95" customHeight="1"/>
+    <row r="744" ht="4.95" customHeight="1"/>
+    <row r="745" ht="4.95" customHeight="1"/>
+    <row r="746" ht="4.95" customHeight="1"/>
+    <row r="747" ht="4.95" customHeight="1"/>
+    <row r="748" ht="4.95" customHeight="1"/>
+    <row r="749" ht="4.95" customHeight="1"/>
+    <row r="750" ht="4.95" customHeight="1"/>
+    <row r="751" ht="4.95" customHeight="1"/>
+    <row r="752" ht="4.95" customHeight="1"/>
+    <row r="753" ht="4.95" customHeight="1"/>
+    <row r="754" ht="4.95" customHeight="1"/>
+    <row r="755" ht="4.95" customHeight="1"/>
+    <row r="756" ht="4.95" customHeight="1"/>
+    <row r="757" ht="4.95" customHeight="1"/>
+    <row r="758" ht="4.95" customHeight="1"/>
+    <row r="759" ht="4.95" customHeight="1"/>
+    <row r="760" ht="4.95" customHeight="1"/>
+    <row r="761" ht="4.95" customHeight="1"/>
+    <row r="762" ht="4.95" customHeight="1"/>
+    <row r="763" ht="4.95" customHeight="1"/>
+    <row r="764" ht="4.95" customHeight="1"/>
+    <row r="765" ht="4.95" customHeight="1"/>
+    <row r="766" ht="4.95" customHeight="1"/>
+    <row r="767" ht="4.95" customHeight="1"/>
+    <row r="768" ht="4.95" customHeight="1"/>
+    <row r="769" ht="4.95" customHeight="1"/>
+    <row r="770" ht="4.95" customHeight="1"/>
+    <row r="771" ht="4.95" customHeight="1"/>
+    <row r="772" ht="4.95" customHeight="1"/>
+    <row r="773" ht="4.95" customHeight="1"/>
+    <row r="774" ht="4.95" customHeight="1"/>
+    <row r="775" ht="4.95" customHeight="1"/>
+    <row r="776" ht="4.95" customHeight="1"/>
+    <row r="777" ht="4.95" customHeight="1"/>
+    <row r="778" ht="4.95" customHeight="1"/>
+    <row r="779" ht="4.95" customHeight="1"/>
+    <row r="780" ht="4.95" customHeight="1"/>
+    <row r="781" ht="4.95" customHeight="1"/>
+    <row r="782" ht="4.95" customHeight="1"/>
+    <row r="783" ht="4.95" customHeight="1"/>
+    <row r="784" ht="4.95" customHeight="1"/>
+    <row r="785" ht="4.95" customHeight="1"/>
+    <row r="786" ht="4.95" customHeight="1"/>
+    <row r="787" ht="4.95" customHeight="1"/>
+    <row r="788" ht="4.95" customHeight="1"/>
+    <row r="789" ht="4.95" customHeight="1"/>
+    <row r="790" ht="4.95" customHeight="1"/>
+    <row r="791" ht="4.95" customHeight="1"/>
+    <row r="792" ht="4.95" customHeight="1"/>
+    <row r="793" ht="4.95" customHeight="1"/>
+    <row r="794" ht="4.95" customHeight="1"/>
+    <row r="795" ht="4.95" customHeight="1"/>
+    <row r="796" ht="4.95" customHeight="1"/>
+    <row r="797" ht="4.95" customHeight="1"/>
+    <row r="798" ht="4.95" customHeight="1"/>
+    <row r="799" ht="4.95" customHeight="1"/>
+    <row r="800" ht="4.95" customHeight="1"/>
+    <row r="801" ht="4.95" customHeight="1"/>
+    <row r="802" ht="4.95" customHeight="1"/>
+    <row r="803" ht="4.95" customHeight="1"/>
+    <row r="804" ht="4.95" customHeight="1"/>
+    <row r="805" ht="4.95" customHeight="1"/>
+    <row r="806" ht="4.95" customHeight="1"/>
+    <row r="807" ht="4.95" customHeight="1"/>
+    <row r="808" ht="4.95" customHeight="1"/>
+    <row r="809" ht="4.95" customHeight="1"/>
+    <row r="810" ht="4.95" customHeight="1"/>
+    <row r="811" ht="4.95" customHeight="1"/>
+    <row r="812" ht="4.95" customHeight="1"/>
+    <row r="813" ht="4.95" customHeight="1"/>
+    <row r="814" ht="4.95" customHeight="1"/>
+    <row r="815" ht="4.95" customHeight="1"/>
+    <row r="816" ht="4.95" customHeight="1"/>
+    <row r="817" ht="4.95" customHeight="1"/>
+    <row r="818" ht="4.95" customHeight="1"/>
+    <row r="819" ht="4.95" customHeight="1"/>
+    <row r="820" ht="4.95" customHeight="1"/>
+    <row r="821" ht="4.95" customHeight="1"/>
+    <row r="822" ht="4.95" customHeight="1"/>
+    <row r="823" ht="4.95" customHeight="1"/>
+    <row r="824" ht="4.95" customHeight="1"/>
+    <row r="825" ht="4.95" customHeight="1"/>
+    <row r="826" ht="4.95" customHeight="1"/>
+    <row r="827" ht="4.95" customHeight="1"/>
+    <row r="828" ht="4.95" customHeight="1"/>
+    <row r="829" ht="4.95" customHeight="1"/>
+    <row r="830" ht="4.95" customHeight="1"/>
+    <row r="831" ht="4.95" customHeight="1"/>
+    <row r="832" ht="4.95" customHeight="1"/>
+    <row r="833" ht="4.95" customHeight="1"/>
+    <row r="834" ht="4.95" customHeight="1"/>
+    <row r="835" ht="4.95" customHeight="1"/>
+    <row r="836" ht="4.95" customHeight="1"/>
+    <row r="837" ht="4.95" customHeight="1"/>
+    <row r="838" ht="4.95" customHeight="1"/>
+    <row r="839" ht="4.95" customHeight="1"/>
+    <row r="840" ht="4.95" customHeight="1"/>
+    <row r="841" ht="4.95" customHeight="1"/>
+    <row r="842" ht="4.95" customHeight="1"/>
+    <row r="843" ht="4.95" customHeight="1"/>
+    <row r="844" ht="4.95" customHeight="1"/>
+    <row r="845" ht="4.95" customHeight="1"/>
+    <row r="846" ht="4.95" customHeight="1"/>
+    <row r="847" ht="4.95" customHeight="1"/>
+    <row r="848" ht="4.95" customHeight="1"/>
+    <row r="849" ht="4.95" customHeight="1"/>
+    <row r="850" ht="4.95" customHeight="1"/>
+    <row r="851" ht="4.95" customHeight="1"/>
+    <row r="852" ht="4.95" customHeight="1"/>
+    <row r="853" ht="4.95" customHeight="1"/>
+    <row r="854" ht="4.95" customHeight="1"/>
+    <row r="855" ht="4.95" customHeight="1"/>
+    <row r="856" ht="4.95" customHeight="1"/>
+    <row r="857" ht="4.95" customHeight="1"/>
+    <row r="858" ht="4.95" customHeight="1"/>
+    <row r="859" ht="4.95" customHeight="1"/>
+    <row r="860" ht="4.95" customHeight="1"/>
+    <row r="861" ht="4.95" customHeight="1"/>
+    <row r="862" ht="4.95" customHeight="1"/>
+    <row r="863" ht="4.95" customHeight="1"/>
+    <row r="864" ht="4.95" customHeight="1"/>
+    <row r="865" ht="4.95" customHeight="1"/>
+    <row r="866" ht="4.95" customHeight="1"/>
+    <row r="867" ht="4.95" customHeight="1"/>
+    <row r="868" ht="4.95" customHeight="1"/>
+    <row r="869" ht="4.95" customHeight="1"/>
+    <row r="870" ht="4.95" customHeight="1"/>
+    <row r="871" ht="4.95" customHeight="1"/>
+    <row r="872" ht="4.95" customHeight="1"/>
+    <row r="873" ht="4.95" customHeight="1"/>
+    <row r="874" ht="4.95" customHeight="1"/>
+    <row r="875" ht="4.95" customHeight="1"/>
+    <row r="876" ht="4.95" customHeight="1"/>
+    <row r="877" ht="4.95" customHeight="1"/>
+    <row r="878" ht="4.95" customHeight="1"/>
+    <row r="879" ht="4.95" customHeight="1"/>
+    <row r="880" ht="4.95" customHeight="1"/>
+    <row r="881" ht="4.95" customHeight="1"/>
+    <row r="882" ht="4.95" customHeight="1"/>
+    <row r="883" ht="4.95" customHeight="1"/>
+    <row r="884" ht="4.95" customHeight="1"/>
+    <row r="885" ht="4.95" customHeight="1"/>
+    <row r="886" ht="4.95" customHeight="1"/>
+    <row r="887" ht="4.95" customHeight="1"/>
+    <row r="888" ht="4.95" customHeight="1"/>
+    <row r="889" ht="4.95" customHeight="1"/>
+    <row r="890" ht="4.95" customHeight="1"/>
+    <row r="891" ht="4.95" customHeight="1"/>
+    <row r="892" ht="4.95" customHeight="1"/>
+    <row r="893" ht="4.95" customHeight="1"/>
+    <row r="894" ht="4.95" customHeight="1"/>
+    <row r="895" ht="4.95" customHeight="1"/>
+    <row r="896" ht="4.95" customHeight="1"/>
+    <row r="897" ht="4.95" customHeight="1"/>
+    <row r="898" ht="4.95" customHeight="1"/>
+    <row r="899" ht="4.95" customHeight="1"/>
+    <row r="900" ht="4.95" customHeight="1"/>
+    <row r="901" ht="4.95" customHeight="1"/>
+    <row r="902" ht="4.95" customHeight="1"/>
+    <row r="903" ht="4.95" customHeight="1"/>
+    <row r="904" ht="4.95" customHeight="1"/>
+    <row r="905" ht="4.95" customHeight="1"/>
+    <row r="906" ht="4.95" customHeight="1"/>
+    <row r="907" ht="4.95" customHeight="1"/>
+    <row r="908" ht="4.95" customHeight="1"/>
+    <row r="909" ht="4.95" customHeight="1"/>
+    <row r="910" ht="4.95" customHeight="1"/>
+    <row r="911" ht="4.95" customHeight="1"/>
+    <row r="912" ht="4.95" customHeight="1"/>
+    <row r="913" ht="4.95" customHeight="1"/>
+    <row r="914" ht="4.95" customHeight="1"/>
+    <row r="915" ht="4.95" customHeight="1"/>
+    <row r="916" ht="4.95" customHeight="1"/>
+    <row r="917" ht="4.95" customHeight="1"/>
+    <row r="918" ht="4.95" customHeight="1"/>
+    <row r="919" ht="4.95" customHeight="1"/>
+    <row r="920" ht="4.95" customHeight="1"/>
+    <row r="921" ht="4.95" customHeight="1"/>
+    <row r="922" ht="4.95" customHeight="1"/>
+    <row r="923" ht="4.95" customHeight="1"/>
+    <row r="924" ht="4.95" customHeight="1"/>
+    <row r="925" ht="4.95" customHeight="1"/>
+    <row r="926" ht="4.95" customHeight="1"/>
+    <row r="927" ht="4.95" customHeight="1"/>
+    <row r="928" ht="4.95" customHeight="1"/>
+    <row r="929" ht="4.95" customHeight="1"/>
+    <row r="930" ht="4.95" customHeight="1"/>
+    <row r="931" ht="4.95" customHeight="1"/>
+    <row r="932" ht="4.95" customHeight="1"/>
+    <row r="933" ht="4.95" customHeight="1"/>
+    <row r="934" ht="4.95" customHeight="1"/>
+    <row r="935" ht="4.95" customHeight="1"/>
+    <row r="936" ht="4.95" customHeight="1"/>
+    <row r="937" ht="4.95" customHeight="1"/>
+    <row r="938" ht="4.95" customHeight="1"/>
+    <row r="939" ht="4.95" customHeight="1"/>
+    <row r="940" ht="4.95" customHeight="1"/>
+    <row r="941" ht="4.95" customHeight="1"/>
+    <row r="942" ht="4.95" customHeight="1"/>
+    <row r="943" ht="4.95" customHeight="1"/>
+    <row r="944" ht="4.95" customHeight="1"/>
+    <row r="945" ht="4.95" customHeight="1"/>
+    <row r="946" ht="4.95" customHeight="1"/>
+    <row r="947" ht="4.95" customHeight="1"/>
+    <row r="948" ht="4.95" customHeight="1"/>
+    <row r="949" ht="4.95" customHeight="1"/>
+    <row r="950" ht="4.95" customHeight="1"/>
+    <row r="951" ht="4.95" customHeight="1"/>
+    <row r="952" ht="4.95" customHeight="1"/>
+    <row r="953" ht="4.95" customHeight="1"/>
+    <row r="954" ht="4.95" customHeight="1"/>
+    <row r="955" ht="4.95" customHeight="1"/>
+    <row r="956" ht="4.95" customHeight="1"/>
+    <row r="957" ht="4.95" customHeight="1"/>
+    <row r="958" ht="4.95" customHeight="1"/>
+    <row r="959" ht="4.95" customHeight="1"/>
+    <row r="960" ht="4.95" customHeight="1"/>
+    <row r="961" ht="4.95" customHeight="1"/>
+    <row r="962" ht="4.95" customHeight="1"/>
+    <row r="963" ht="4.95" customHeight="1"/>
+    <row r="964" ht="4.95" customHeight="1"/>
+    <row r="965" ht="4.95" customHeight="1"/>
+    <row r="966" ht="4.95" customHeight="1"/>
+    <row r="967" ht="4.95" customHeight="1"/>
+    <row r="968" ht="4.95" customHeight="1"/>
+    <row r="969" ht="4.95" customHeight="1"/>
+    <row r="970" ht="4.95" customHeight="1"/>
+    <row r="971" ht="4.95" customHeight="1"/>
+    <row r="972" ht="4.95" customHeight="1"/>
+    <row r="973" ht="4.95" customHeight="1"/>
+    <row r="974" ht="4.95" customHeight="1"/>
+    <row r="975" ht="4.95" customHeight="1"/>
+    <row r="976" ht="4.95" customHeight="1"/>
+    <row r="977" ht="4.95" customHeight="1"/>
+    <row r="978" ht="4.95" customHeight="1"/>
+    <row r="979" ht="4.95" customHeight="1"/>
+    <row r="980" ht="4.95" customHeight="1"/>
+    <row r="981" ht="4.95" customHeight="1"/>
+    <row r="982" ht="4.95" customHeight="1"/>
+    <row r="983" ht="4.95" customHeight="1"/>
+    <row r="984" ht="4.95" customHeight="1"/>
+    <row r="985" ht="4.95" customHeight="1"/>
+    <row r="986" ht="4.95" customHeight="1"/>
+    <row r="987" ht="4.95" customHeight="1"/>
+    <row r="988" ht="4.95" customHeight="1"/>
+    <row r="989" ht="4.95" customHeight="1"/>
+    <row r="990" ht="4.95" customHeight="1"/>
+    <row r="991" ht="4.95" customHeight="1"/>
+    <row r="992" ht="4.95" customHeight="1"/>
+    <row r="993" ht="4.95" customHeight="1"/>
+    <row r="994" ht="4.95" customHeight="1"/>
+    <row r="995" ht="4.95" customHeight="1"/>
+    <row r="996" ht="4.95" customHeight="1"/>
+    <row r="997" ht="4.95" customHeight="1"/>
+    <row r="998" ht="4.95" customHeight="1"/>
+    <row r="999" ht="4.95" customHeight="1"/>
+    <row r="1000" ht="4.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="I1:J1"/>
@@ -2750,7 +2929,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -2765,48 +2944,48 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E2" s="13">
         <v>2</v>
@@ -2816,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I2" s="25">
         <v>0</v>
@@ -2827,16 +3006,16 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E3" s="19">
         <v>3</v>
@@ -2846,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I3" s="26">
         <v>0</v>
@@ -2857,16 +3036,16 @@
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E4" s="13">
         <v>1</v>
@@ -2876,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I4" s="25">
         <v>0</v>
@@ -2887,16 +3066,16 @@
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E5" s="19">
         <v>2</v>
@@ -2906,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I5" s="26">
         <v>0</v>
@@ -2917,16 +3096,16 @@
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E6" s="13">
         <v>2</v>
@@ -2936,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I6" s="25">
         <v>0</v>
@@ -2947,16 +3126,16 @@
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E7" s="19">
         <v>3</v>
@@ -2966,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I7" s="26">
         <v>0</v>
@@ -2977,16 +3156,16 @@
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E8" s="13">
         <v>1</v>
@@ -2996,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I8" s="25">
         <v>0</v>
@@ -3007,16 +3186,16 @@
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E9" s="19">
         <v>4</v>
@@ -3026,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I9" s="26">
         <v>0</v>
@@ -3037,16 +3216,16 @@
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>65</v>
+        <v>22</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>90</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E10" s="13">
         <v>4</v>
@@ -3056,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I10" s="25">
         <v>0</v>
@@ -3067,16 +3246,16 @@
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E11" s="19">
         <v>3</v>
@@ -3086,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I11" s="26">
         <v>0</v>
@@ -3097,16 +3276,16 @@
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E12" s="13">
         <v>3</v>
@@ -3116,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I12" s="25">
         <v>0</v>
@@ -3127,16 +3306,16 @@
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E13" s="21">
         <v>0</v>
@@ -3146,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I13" s="26">
         <v>100</v>
@@ -3157,16 +3336,16 @@
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E14" s="23">
         <v>0</v>
@@ -3176,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I14" s="25">
         <v>0.05</v>
@@ -3187,16 +3366,16 @@
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E15" s="21">
         <v>0</v>
@@ -3206,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I15" s="26">
         <v>0.1</v>
@@ -3242,46 +3421,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.05" customHeight="1">
       <c r="A2" s="28" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B2" s="30">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1">
+    <row r="3" spans="1:2" ht="28.05" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B3" s="31">
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1">
+    <row r="4" spans="1:2" ht="28.05" customHeight="1">
       <c r="A4" s="28" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B4" s="30">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1">
+    <row r="5" spans="1:2" ht="28.05" customHeight="1">
       <c r="A5" s="29" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B5" s="31">
         <v>0.2</v>

--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re27c2db32d25454d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillInfo" sheetId="2" r:id="Rf5c0c683b0644ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JudgementBalance" sheetId="3" r:id="Rbc9f191d30b54324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R41ef72d302a0447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillInfo" sheetId="2" r:id="Rd7abc928e5494e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JudgementBalance" sheetId="3" r:id="Rb63dda4cbe8e4583"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -463,9 +463,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="176" formatCode="0.##;\-0.##;0"/>
     <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.0#"/>
   </x:numFmts>
   <x:fonts count="18">
     <x:font>
@@ -684,7 +685,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -816,6 +817,7 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -842,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SkillInfoTable" displayName="SkillInfoTable" ref="A1:K15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="11">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SkillInfoTable" displayName="SkillInfoTable" ref="A1:N15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="DisplayName"/>
     <x:tableColumn id="3" name="Description"/>
@@ -855,6 +857,9 @@
     <x:tableColumn id="9" name="StatValue"/>
     <x:tableColumn id="10" name="StatCap"/>
     <x:tableColumn id="11" name="BaseDamage"/>
+    <x:tableColumn id="12" name="BaseDamage"/>
+    <x:tableColumn id="13" name="BaseDamage"/>
+    <x:tableColumn id="14" name="BaseDamage"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -2861,7 +2866,10 @@
     <x:col min="7" max="7" width="10" customWidth="1"/>
     <x:col min="8" max="8" width="22" customWidth="1"/>
     <x:col min="9" max="10" width="13" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -2898,6 +2906,15 @@
       <x:c r="K1" t="str">
         <x:v>BaseDamage</x:v>
       </x:c>
+      <x:c r="L1" t="str">
+        <x:v>DamagePerLevel</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>BaseDotDamage</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>DotDamagePerLevel</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="9" t="s">
@@ -2931,7 +2948,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K2" s="38" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L2" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" s="38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N2" s="39" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2966,7 +2992,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K3" s="38" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L3" s="39" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="M3" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -2999,7 +3034,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="38" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L4" s="39" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="M4" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
@@ -3034,7 +3078,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="38" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L5" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M5" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -3069,6 +3122,15 @@
       <x:c r="K6" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L6" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="15" t="s">
@@ -3102,7 +3164,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="38" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="38" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="39" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -3137,7 +3208,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="38" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L8" s="39" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="M8" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -3172,7 +3252,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K9" s="38" t="n">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L9" s="39" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="M9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -3205,7 +3294,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="38" t="n">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L10" s="39" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M10" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -3242,6 +3340,15 @@
       <x:c r="K11" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L11" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="9" t="s">
@@ -3275,6 +3382,15 @@
       <x:c r="K12" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L12" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="15" t="s">
@@ -3308,6 +3424,15 @@
       <x:c r="K13" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L13" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="9" t="s">
@@ -3341,6 +3466,15 @@
       <x:c r="K14" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="L14" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="15" t="s">
@@ -3372,6 +3506,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -3393,7 +3536,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc420ca8d22f54c19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4401990b31a74698"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Stop-Defence\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac19dd172dbe555/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3E5636-9D51-4BAE-8777-65F3452C4FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{3B26A40C-113A-40F0-A386-44846F16F515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E9EA32-E4BF-478D-B503-8CCA22FA73FE}"/>
   <bookViews>
-    <workbookView xWindow="3250" yWindow="2100" windowWidth="20360" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="104">
   <si>
     <r>
       <rPr>
@@ -94,9 +92,6 @@
     <t>데미지 배율</t>
   </si>
   <si>
-    <t>2x + 20</t>
-  </si>
-  <si>
     <t>0.1x + 2</t>
   </si>
   <si>
@@ -110,9 +105,6 @@
   </si>
   <si>
     <t>all</t>
-  </si>
-  <si>
-    <t>1.3x + 18</t>
   </si>
   <si>
     <t>연쇄 번개</t>
@@ -125,15 +117,9 @@
 Unity: Tools &gt; Game Data &gt; Import Skill Data</t>
   </si>
   <si>
-    <t>1.4x + 15</t>
-  </si>
-  <si>
     <t>대못박기</t>
   </si>
   <si>
-    <t>2x + 30</t>
-  </si>
-  <si>
     <t>수리마법</t>
   </si>
   <si>
@@ -143,9 +129,6 @@
     <t>역병 마법</t>
   </si>
   <si>
-    <t>x + 12</t>
-  </si>
-  <si>
     <t>고드름 창</t>
   </si>
   <si>
@@ -372,6 +355,30 @@
   </si>
   <si>
     <t>AttackPowerLevel</t>
+  </si>
+  <si>
+    <t>2x + 25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3x + 23</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4x + 20</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x + 100</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x + 40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>x + 15</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -382,7 +389,7 @@
     <numFmt numFmtId="176" formatCode="0.##;\-0.##;0"/>
     <numFmt numFmtId="177" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -466,6 +473,11 @@
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF102A43"/>
+      <name val="Carlito"/>
     </font>
     <font>
       <b/>
@@ -608,7 +620,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -650,9 +662,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -673,9 +685,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
       </extLst>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -684,9 +696,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
       </extLst>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -695,9 +707,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
       </extLst>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -729,14 +741,17 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
+        <x:ext xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -764,24 +779,24 @@
 </file>
 
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SkillInfoTable" displayName="SkillInfoTable" ref="A1:N15" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SkillInfoTable" displayName="SkillInfoTable" ref="A1:N16" totalsRowShown="0">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SkillId"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
@@ -998,20 +1013,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.9140625" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.4140625" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="8" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" customWidth="1"/>
+    <col min="6" max="8" width="8.69921875" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="26" width="8.6640625" customWidth="1"/>
+    <col min="11" max="26" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="10.65" customHeight="1">
+    <row r="1" spans="1:26" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,10 +1049,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="2"/>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38"/>
+      <c r="J1" s="39"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -1047,14 +1062,14 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="12.65" customHeight="1">
+    <row r="2" spans="1:26" ht="15.15" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="7"/>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3">
         <v>5</v>
@@ -1081,19 +1096,19 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="7.65" customHeight="1">
+    <row r="3" spans="1:26" ht="9.15" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="7"/>
       <c r="C3" s="3"/>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="33" t="str">
@@ -1113,9 +1128,9 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="8.9" customHeight="1">
+    <row r="4" spans="1:26" ht="10.65" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1130,7 +1145,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1159,17 +1174,17 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" spans="1:26" ht="9.65" customHeight="1">
+    <row r="5" spans="1:26" ht="11.55" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="7"/>
       <c r="C5" s="3">
         <v>3</v>
       </c>
       <c r="D5" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3">
         <v>3</v>
@@ -1193,16 +1208,16 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="15.15" customHeight="1">
+    <row r="6" spans="1:26" ht="18.149999999999999" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="7"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1223,9 +1238,9 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="10.65" customHeight="1">
+    <row r="7" spans="1:26" ht="12.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>1</v>
@@ -1237,7 +1252,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -1261,14 +1276,14 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" ht="15.15" customHeight="1">
+    <row r="8" spans="1:26" ht="18.149999999999999" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="7"/>
       <c r="C8" s="3">
         <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3">
         <v>7</v>
@@ -1276,10 +1291,10 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="39"/>
+      <c r="I8" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="40"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -1289,19 +1304,19 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="15.15" customHeight="1">
+    <row r="9" spans="1:26" ht="18.149999999999999" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="7"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -1311,9 +1326,9 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="6.9" customHeight="1">
+    <row r="10" spans="1:26" ht="8.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>1</v>
@@ -1347,14 +1362,14 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" ht="8.75" customHeight="1">
+    <row r="11" spans="1:26" ht="10.5" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="7"/>
       <c r="C11" s="3">
         <v>2</v>
       </c>
       <c r="D11" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1371,12 +1386,12 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="9.25" customHeight="1">
+    <row r="12" spans="1:26" ht="11.1" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="7"/>
       <c r="C12" s="3"/>
       <c r="D12" s="6" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1393,9 +1408,9 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="6.75" customHeight="1">
+    <row r="13" spans="1:26" ht="8.1" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>1</v>
@@ -1404,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1429,33 +1444,33 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" ht="8" customHeight="1">
+    <row r="14" spans="1:26" ht="9.6" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6">
         <v>2</v>
       </c>
       <c r="D14" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:26" ht="9.65" customHeight="1">
+    <row r="15" spans="1:26" ht="11.55" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:26" ht="8.9" customHeight="1">
+    <row r="16" spans="1:26" ht="10.65" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>1</v>
@@ -1491,14 +1506,14 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="8.4" customHeight="1">
+    <row r="17" spans="1:26" ht="10.050000000000001" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6">
         <v>3</v>
       </c>
       <c r="D17" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" s="6">
         <v>3</v>
@@ -1506,22 +1521,22 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:26" ht="9.75" customHeight="1">
+    <row r="18" spans="1:26" ht="11.7" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:26" ht="7.25" customHeight="1">
+    <row r="19" spans="1:26" ht="8.6999999999999993" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1</v>
@@ -1533,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>6</v>
@@ -1559,14 +1574,14 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="7.15" customHeight="1">
+    <row r="20" spans="1:26" ht="8.5500000000000007" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6">
         <v>1</v>
       </c>
       <c r="D20" s="6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E20" s="6">
         <v>0.3</v>
@@ -1576,24 +1591,24 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:26" ht="8.9" customHeight="1">
+    <row r="21" spans="1:26" ht="10.65" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:26" ht="7.75" customHeight="1">
+    <row r="22" spans="1:26" ht="9.3000000000000007" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>1</v>
@@ -1627,31 +1642,31 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="10.25" customHeight="1">
+    <row r="23" spans="1:26" ht="12.3" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6">
         <v>4</v>
       </c>
       <c r="D23" s="6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:26" ht="7.25" customHeight="1">
+    <row r="24" spans="1:26" ht="8.6999999999999993" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:26" ht="7.25" customHeight="1">
+    <row r="25" spans="1:26" ht="8.6999999999999993" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1679,7 +1694,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="6.75" customHeight="1">
+    <row r="26" spans="1:26" ht="8.1" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
@@ -1688,7 +1703,7 @@
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:26" ht="9.65" customHeight="1">
+    <row r="27" spans="1:26" ht="11.55" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1697,9 +1712,9 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:26" ht="7.25" customHeight="1">
+    <row r="28" spans="1:26" ht="8.6999999999999993" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>1</v>
@@ -1733,7 +1748,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="6.25" customHeight="1">
+    <row r="29" spans="1:26" ht="7.5" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6">
@@ -1746,20 +1761,20 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:26" ht="6.4" customHeight="1">
+    <row r="30" spans="1:26" ht="7.65" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:26" ht="7.25" customHeight="1">
+    <row r="31" spans="1:26" ht="8.6999999999999993" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>1</v>
@@ -1791,7 +1806,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="10.25" customHeight="1">
+    <row r="32" spans="1:26" ht="12.3" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6">
@@ -1802,974 +1817,974 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" ht="3.25" customHeight="1"/>
-    <row r="34" ht="3.25" customHeight="1"/>
-    <row r="35" ht="3.25" customHeight="1"/>
-    <row r="36" ht="3.25" customHeight="1"/>
-    <row r="37" ht="3.25" customHeight="1"/>
-    <row r="38" ht="3.25" customHeight="1"/>
-    <row r="39" ht="3.25" customHeight="1"/>
-    <row r="40" ht="3.25" customHeight="1"/>
-    <row r="41" ht="3.25" customHeight="1"/>
-    <row r="42" ht="3.25" customHeight="1"/>
-    <row r="43" ht="3.25" customHeight="1"/>
-    <row r="44" ht="3.25" customHeight="1"/>
-    <row r="45" ht="3.25" customHeight="1"/>
-    <row r="46" ht="3.25" customHeight="1"/>
-    <row r="47" ht="3.25" customHeight="1"/>
-    <row r="48" ht="3.25" customHeight="1"/>
-    <row r="49" ht="3.25" customHeight="1"/>
-    <row r="50" ht="3.25" customHeight="1"/>
-    <row r="51" ht="3.25" customHeight="1"/>
-    <row r="52" ht="3.25" customHeight="1"/>
-    <row r="53" ht="3.25" customHeight="1"/>
-    <row r="54" ht="3.25" customHeight="1"/>
-    <row r="55" ht="3.25" customHeight="1"/>
-    <row r="56" ht="3.25" customHeight="1"/>
-    <row r="57" ht="3.25" customHeight="1"/>
-    <row r="58" ht="3.25" customHeight="1"/>
-    <row r="59" ht="3.25" customHeight="1"/>
-    <row r="60" ht="3.25" customHeight="1"/>
-    <row r="61" ht="3.25" customHeight="1"/>
-    <row r="62" ht="3.25" customHeight="1"/>
-    <row r="63" ht="3.25" customHeight="1"/>
-    <row r="64" ht="3.25" customHeight="1"/>
-    <row r="65" ht="3.25" customHeight="1"/>
-    <row r="66" ht="3.25" customHeight="1"/>
-    <row r="67" ht="3.25" customHeight="1"/>
-    <row r="68" ht="3.25" customHeight="1"/>
-    <row r="69" ht="3.25" customHeight="1"/>
-    <row r="70" ht="3.25" customHeight="1"/>
-    <row r="71" ht="3.25" customHeight="1"/>
-    <row r="72" ht="3.25" customHeight="1"/>
-    <row r="73" ht="3.25" customHeight="1"/>
-    <row r="74" ht="3.25" customHeight="1"/>
-    <row r="75" ht="3.25" customHeight="1"/>
-    <row r="76" ht="3.25" customHeight="1"/>
-    <row r="77" ht="3.25" customHeight="1"/>
-    <row r="78" ht="3.25" customHeight="1"/>
-    <row r="79" ht="3.25" customHeight="1"/>
-    <row r="80" ht="3.25" customHeight="1"/>
-    <row r="81" ht="3.25" customHeight="1"/>
-    <row r="82" ht="3.25" customHeight="1"/>
-    <row r="83" ht="3.25" customHeight="1"/>
-    <row r="84" ht="3.25" customHeight="1"/>
-    <row r="85" ht="3.25" customHeight="1"/>
-    <row r="86" ht="3.25" customHeight="1"/>
-    <row r="87" ht="3.25" customHeight="1"/>
-    <row r="88" ht="3.25" customHeight="1"/>
-    <row r="89" ht="3.25" customHeight="1"/>
-    <row r="90" ht="3.25" customHeight="1"/>
-    <row r="91" ht="3.25" customHeight="1"/>
-    <row r="92" ht="3.25" customHeight="1"/>
-    <row r="93" ht="3.25" customHeight="1"/>
-    <row r="94" ht="3.25" customHeight="1"/>
-    <row r="95" ht="3.25" customHeight="1"/>
-    <row r="96" ht="3.25" customHeight="1"/>
-    <row r="97" ht="3.25" customHeight="1"/>
-    <row r="98" ht="3.25" customHeight="1"/>
-    <row r="99" ht="3.25" customHeight="1"/>
-    <row r="100" ht="3.25" customHeight="1"/>
-    <row r="101" ht="3.25" customHeight="1"/>
-    <row r="102" ht="3.25" customHeight="1"/>
-    <row r="103" ht="3.25" customHeight="1"/>
-    <row r="104" ht="3.25" customHeight="1"/>
-    <row r="105" ht="3.25" customHeight="1"/>
-    <row r="106" ht="3.25" customHeight="1"/>
-    <row r="107" ht="3.25" customHeight="1"/>
-    <row r="108" ht="3.25" customHeight="1"/>
-    <row r="109" ht="3.25" customHeight="1"/>
-    <row r="110" ht="3.25" customHeight="1"/>
-    <row r="111" ht="3.25" customHeight="1"/>
-    <row r="112" ht="3.25" customHeight="1"/>
-    <row r="113" ht="3.25" customHeight="1"/>
-    <row r="114" ht="3.25" customHeight="1"/>
-    <row r="115" ht="3.25" customHeight="1"/>
-    <row r="116" ht="3.25" customHeight="1"/>
-    <row r="117" ht="3.25" customHeight="1"/>
-    <row r="118" ht="3.25" customHeight="1"/>
-    <row r="119" ht="3.25" customHeight="1"/>
-    <row r="120" ht="3.25" customHeight="1"/>
-    <row r="121" ht="3.25" customHeight="1"/>
-    <row r="122" ht="3.25" customHeight="1"/>
-    <row r="123" ht="3.25" customHeight="1"/>
-    <row r="124" ht="3.25" customHeight="1"/>
-    <row r="125" ht="3.25" customHeight="1"/>
-    <row r="126" ht="3.25" customHeight="1"/>
-    <row r="127" ht="3.25" customHeight="1"/>
-    <row r="128" ht="3.25" customHeight="1"/>
-    <row r="129" ht="3.25" customHeight="1"/>
-    <row r="130" ht="3.25" customHeight="1"/>
-    <row r="131" ht="3.25" customHeight="1"/>
-    <row r="132" ht="3.25" customHeight="1"/>
-    <row r="133" ht="3.25" customHeight="1"/>
-    <row r="134" ht="3.25" customHeight="1"/>
-    <row r="135" ht="3.25" customHeight="1"/>
-    <row r="136" ht="3.25" customHeight="1"/>
-    <row r="137" ht="3.25" customHeight="1"/>
-    <row r="138" ht="3.25" customHeight="1"/>
-    <row r="139" ht="3.25" customHeight="1"/>
-    <row r="140" ht="3.25" customHeight="1"/>
-    <row r="141" ht="3.25" customHeight="1"/>
-    <row r="142" ht="3.25" customHeight="1"/>
-    <row r="143" ht="3.25" customHeight="1"/>
-    <row r="144" ht="3.25" customHeight="1"/>
-    <row r="145" ht="3.25" customHeight="1"/>
-    <row r="146" ht="3.25" customHeight="1"/>
-    <row r="147" ht="3.25" customHeight="1"/>
-    <row r="148" ht="3.25" customHeight="1"/>
-    <row r="149" ht="3.25" customHeight="1"/>
-    <row r="150" ht="3.25" customHeight="1"/>
-    <row r="151" ht="3.25" customHeight="1"/>
-    <row r="152" ht="3.25" customHeight="1"/>
-    <row r="153" ht="3.25" customHeight="1"/>
-    <row r="154" ht="3.25" customHeight="1"/>
-    <row r="155" ht="3.25" customHeight="1"/>
-    <row r="156" ht="3.25" customHeight="1"/>
-    <row r="157" ht="3.25" customHeight="1"/>
-    <row r="158" ht="3.25" customHeight="1"/>
-    <row r="159" ht="3.25" customHeight="1"/>
-    <row r="160" ht="3.25" customHeight="1"/>
-    <row r="161" ht="3.25" customHeight="1"/>
-    <row r="162" ht="3.25" customHeight="1"/>
-    <row r="163" ht="3.25" customHeight="1"/>
-    <row r="164" ht="3.25" customHeight="1"/>
-    <row r="165" ht="3.25" customHeight="1"/>
-    <row r="166" ht="3.25" customHeight="1"/>
-    <row r="167" ht="3.25" customHeight="1"/>
-    <row r="168" ht="3.25" customHeight="1"/>
-    <row r="169" ht="3.25" customHeight="1"/>
-    <row r="170" ht="3.25" customHeight="1"/>
-    <row r="171" ht="3.25" customHeight="1"/>
-    <row r="172" ht="3.25" customHeight="1"/>
-    <row r="173" ht="3.25" customHeight="1"/>
-    <row r="174" ht="3.25" customHeight="1"/>
-    <row r="175" ht="3.25" customHeight="1"/>
-    <row r="176" ht="3.25" customHeight="1"/>
-    <row r="177" ht="3.25" customHeight="1"/>
-    <row r="178" ht="3.25" customHeight="1"/>
-    <row r="179" ht="3.25" customHeight="1"/>
-    <row r="180" ht="3.25" customHeight="1"/>
-    <row r="181" ht="3.25" customHeight="1"/>
-    <row r="182" ht="3.25" customHeight="1"/>
-    <row r="183" ht="3.25" customHeight="1"/>
-    <row r="184" ht="3.25" customHeight="1"/>
-    <row r="185" ht="3.25" customHeight="1"/>
-    <row r="186" ht="3.25" customHeight="1"/>
-    <row r="187" ht="3.25" customHeight="1"/>
-    <row r="188" ht="3.25" customHeight="1"/>
-    <row r="189" ht="3.25" customHeight="1"/>
-    <row r="190" ht="3.25" customHeight="1"/>
-    <row r="191" ht="3.25" customHeight="1"/>
-    <row r="192" ht="3.25" customHeight="1"/>
-    <row r="193" ht="3.25" customHeight="1"/>
-    <row r="194" ht="3.25" customHeight="1"/>
-    <row r="195" ht="3.25" customHeight="1"/>
-    <row r="196" ht="3.25" customHeight="1"/>
-    <row r="197" ht="3.25" customHeight="1"/>
-    <row r="198" ht="3.25" customHeight="1"/>
-    <row r="199" ht="3.25" customHeight="1"/>
-    <row r="200" ht="3.25" customHeight="1"/>
-    <row r="201" ht="3.25" customHeight="1"/>
-    <row r="202" ht="3.25" customHeight="1"/>
-    <row r="203" ht="3.25" customHeight="1"/>
-    <row r="204" ht="3.25" customHeight="1"/>
-    <row r="205" ht="3.25" customHeight="1"/>
-    <row r="206" ht="3.25" customHeight="1"/>
-    <row r="207" ht="3.25" customHeight="1"/>
-    <row r="208" ht="3.25" customHeight="1"/>
-    <row r="209" ht="3.25" customHeight="1"/>
-    <row r="210" ht="3.25" customHeight="1"/>
-    <row r="211" ht="3.25" customHeight="1"/>
-    <row r="212" ht="3.25" customHeight="1"/>
-    <row r="213" ht="3.25" customHeight="1"/>
-    <row r="214" ht="3.25" customHeight="1"/>
-    <row r="215" ht="3.25" customHeight="1"/>
-    <row r="216" ht="3.25" customHeight="1"/>
-    <row r="217" ht="3.25" customHeight="1"/>
-    <row r="218" ht="3.25" customHeight="1"/>
-    <row r="219" ht="3.25" customHeight="1"/>
-    <row r="220" ht="3.25" customHeight="1"/>
-    <row r="221" ht="3.25" customHeight="1"/>
-    <row r="222" ht="3.25" customHeight="1"/>
-    <row r="223" ht="3.25" customHeight="1"/>
-    <row r="224" ht="3.25" customHeight="1"/>
-    <row r="225" ht="3.25" customHeight="1"/>
-    <row r="226" ht="3.25" customHeight="1"/>
-    <row r="227" ht="3.25" customHeight="1"/>
-    <row r="228" ht="3.25" customHeight="1"/>
-    <row r="229" ht="3.25" customHeight="1"/>
-    <row r="230" ht="3.25" customHeight="1"/>
-    <row r="231" ht="3.25" customHeight="1"/>
-    <row r="232" ht="3.25" customHeight="1"/>
-    <row r="233" ht="3.25" customHeight="1"/>
-    <row r="234" ht="3.25" customHeight="1"/>
-    <row r="235" ht="3.25" customHeight="1"/>
-    <row r="236" ht="3.25" customHeight="1"/>
-    <row r="237" ht="3.25" customHeight="1"/>
-    <row r="238" ht="3.25" customHeight="1"/>
-    <row r="239" ht="3.25" customHeight="1"/>
-    <row r="240" ht="3.25" customHeight="1"/>
-    <row r="241" ht="3.25" customHeight="1"/>
-    <row r="242" ht="3.25" customHeight="1"/>
-    <row r="243" ht="3.25" customHeight="1"/>
-    <row r="244" ht="3.25" customHeight="1"/>
-    <row r="245" ht="3.25" customHeight="1"/>
-    <row r="246" ht="3.25" customHeight="1"/>
-    <row r="247" ht="3.25" customHeight="1"/>
-    <row r="248" ht="3.25" customHeight="1"/>
-    <row r="249" ht="3.25" customHeight="1"/>
-    <row r="250" ht="3.25" customHeight="1"/>
-    <row r="251" ht="3.25" customHeight="1"/>
-    <row r="252" ht="3.25" customHeight="1"/>
-    <row r="253" ht="3.25" customHeight="1"/>
-    <row r="254" ht="3.25" customHeight="1"/>
-    <row r="255" ht="3.25" customHeight="1"/>
-    <row r="256" ht="3.25" customHeight="1"/>
-    <row r="257" ht="3.25" customHeight="1"/>
-    <row r="258" ht="3.25" customHeight="1"/>
-    <row r="259" ht="3.25" customHeight="1"/>
-    <row r="260" ht="3.25" customHeight="1"/>
-    <row r="261" ht="3.25" customHeight="1"/>
-    <row r="262" ht="3.25" customHeight="1"/>
-    <row r="263" ht="3.25" customHeight="1"/>
-    <row r="264" ht="3.25" customHeight="1"/>
-    <row r="265" ht="3.25" customHeight="1"/>
-    <row r="266" ht="3.25" customHeight="1"/>
-    <row r="267" ht="3.25" customHeight="1"/>
-    <row r="268" ht="3.25" customHeight="1"/>
-    <row r="269" ht="3.25" customHeight="1"/>
-    <row r="270" ht="3.25" customHeight="1"/>
-    <row r="271" ht="3.25" customHeight="1"/>
-    <row r="272" ht="3.25" customHeight="1"/>
-    <row r="273" ht="3.25" customHeight="1"/>
-    <row r="274" ht="3.25" customHeight="1"/>
-    <row r="275" ht="3.25" customHeight="1"/>
-    <row r="276" ht="3.25" customHeight="1"/>
-    <row r="277" ht="3.25" customHeight="1"/>
-    <row r="278" ht="3.25" customHeight="1"/>
-    <row r="279" ht="3.25" customHeight="1"/>
-    <row r="280" ht="3.25" customHeight="1"/>
-    <row r="281" ht="3.25" customHeight="1"/>
-    <row r="282" ht="3.25" customHeight="1"/>
-    <row r="283" ht="3.25" customHeight="1"/>
-    <row r="284" ht="3.25" customHeight="1"/>
-    <row r="285" ht="3.25" customHeight="1"/>
-    <row r="286" ht="3.25" customHeight="1"/>
-    <row r="287" ht="3.25" customHeight="1"/>
-    <row r="288" ht="3.25" customHeight="1"/>
-    <row r="289" ht="3.25" customHeight="1"/>
-    <row r="290" ht="3.25" customHeight="1"/>
-    <row r="291" ht="3.25" customHeight="1"/>
-    <row r="292" ht="3.25" customHeight="1"/>
-    <row r="293" ht="3.25" customHeight="1"/>
-    <row r="294" ht="3.25" customHeight="1"/>
-    <row r="295" ht="3.25" customHeight="1"/>
-    <row r="296" ht="3.25" customHeight="1"/>
-    <row r="297" ht="3.25" customHeight="1"/>
-    <row r="298" ht="3.25" customHeight="1"/>
-    <row r="299" ht="3.25" customHeight="1"/>
-    <row r="300" ht="3.25" customHeight="1"/>
-    <row r="301" ht="3.25" customHeight="1"/>
-    <row r="302" ht="3.25" customHeight="1"/>
-    <row r="303" ht="3.25" customHeight="1"/>
-    <row r="304" ht="3.25" customHeight="1"/>
-    <row r="305" ht="3.25" customHeight="1"/>
-    <row r="306" ht="3.25" customHeight="1"/>
-    <row r="307" ht="3.25" customHeight="1"/>
-    <row r="308" ht="3.25" customHeight="1"/>
-    <row r="309" ht="3.25" customHeight="1"/>
-    <row r="310" ht="3.25" customHeight="1"/>
-    <row r="311" ht="3.25" customHeight="1"/>
-    <row r="312" ht="3.25" customHeight="1"/>
-    <row r="313" ht="3.25" customHeight="1"/>
-    <row r="314" ht="3.25" customHeight="1"/>
-    <row r="315" ht="3.25" customHeight="1"/>
-    <row r="316" ht="3.25" customHeight="1"/>
-    <row r="317" ht="3.25" customHeight="1"/>
-    <row r="318" ht="3.25" customHeight="1"/>
-    <row r="319" ht="3.25" customHeight="1"/>
-    <row r="320" ht="3.25" customHeight="1"/>
-    <row r="321" ht="3.25" customHeight="1"/>
-    <row r="322" ht="3.25" customHeight="1"/>
-    <row r="323" ht="3.25" customHeight="1"/>
-    <row r="324" ht="3.25" customHeight="1"/>
-    <row r="325" ht="3.25" customHeight="1"/>
-    <row r="326" ht="3.25" customHeight="1"/>
-    <row r="327" ht="3.25" customHeight="1"/>
-    <row r="328" ht="3.25" customHeight="1"/>
-    <row r="329" ht="3.25" customHeight="1"/>
-    <row r="330" ht="3.25" customHeight="1"/>
-    <row r="331" ht="3.25" customHeight="1"/>
-    <row r="332" ht="3.25" customHeight="1"/>
-    <row r="333" ht="3.25" customHeight="1"/>
-    <row r="334" ht="3.25" customHeight="1"/>
-    <row r="335" ht="3.25" customHeight="1"/>
-    <row r="336" ht="3.25" customHeight="1"/>
-    <row r="337" ht="3.25" customHeight="1"/>
-    <row r="338" ht="3.25" customHeight="1"/>
-    <row r="339" ht="3.25" customHeight="1"/>
-    <row r="340" ht="3.25" customHeight="1"/>
-    <row r="341" ht="3.25" customHeight="1"/>
-    <row r="342" ht="3.25" customHeight="1"/>
-    <row r="343" ht="3.25" customHeight="1"/>
-    <row r="344" ht="3.25" customHeight="1"/>
-    <row r="345" ht="3.25" customHeight="1"/>
-    <row r="346" ht="3.25" customHeight="1"/>
-    <row r="347" ht="3.25" customHeight="1"/>
-    <row r="348" ht="3.25" customHeight="1"/>
-    <row r="349" ht="3.25" customHeight="1"/>
-    <row r="350" ht="3.25" customHeight="1"/>
-    <row r="351" ht="3.25" customHeight="1"/>
-    <row r="352" ht="3.25" customHeight="1"/>
-    <row r="353" ht="3.25" customHeight="1"/>
-    <row r="354" ht="3.25" customHeight="1"/>
-    <row r="355" ht="3.25" customHeight="1"/>
-    <row r="356" ht="3.25" customHeight="1"/>
-    <row r="357" ht="3.25" customHeight="1"/>
-    <row r="358" ht="3.25" customHeight="1"/>
-    <row r="359" ht="3.25" customHeight="1"/>
-    <row r="360" ht="3.25" customHeight="1"/>
-    <row r="361" ht="3.25" customHeight="1"/>
-    <row r="362" ht="3.25" customHeight="1"/>
-    <row r="363" ht="3.25" customHeight="1"/>
-    <row r="364" ht="3.25" customHeight="1"/>
-    <row r="365" ht="3.25" customHeight="1"/>
-    <row r="366" ht="3.25" customHeight="1"/>
-    <row r="367" ht="3.25" customHeight="1"/>
-    <row r="368" ht="3.25" customHeight="1"/>
-    <row r="369" ht="3.25" customHeight="1"/>
-    <row r="370" ht="3.25" customHeight="1"/>
-    <row r="371" ht="3.25" customHeight="1"/>
-    <row r="372" ht="3.25" customHeight="1"/>
-    <row r="373" ht="3.25" customHeight="1"/>
-    <row r="374" ht="3.25" customHeight="1"/>
-    <row r="375" ht="3.25" customHeight="1"/>
-    <row r="376" ht="3.25" customHeight="1"/>
-    <row r="377" ht="3.25" customHeight="1"/>
-    <row r="378" ht="3.25" customHeight="1"/>
-    <row r="379" ht="3.25" customHeight="1"/>
-    <row r="380" ht="3.25" customHeight="1"/>
-    <row r="381" ht="3.25" customHeight="1"/>
-    <row r="382" ht="3.25" customHeight="1"/>
-    <row r="383" ht="3.25" customHeight="1"/>
-    <row r="384" ht="3.25" customHeight="1"/>
-    <row r="385" ht="3.25" customHeight="1"/>
-    <row r="386" ht="3.25" customHeight="1"/>
-    <row r="387" ht="3.25" customHeight="1"/>
-    <row r="388" ht="3.25" customHeight="1"/>
-    <row r="389" ht="3.25" customHeight="1"/>
-    <row r="390" ht="3.25" customHeight="1"/>
-    <row r="391" ht="3.25" customHeight="1"/>
-    <row r="392" ht="3.25" customHeight="1"/>
-    <row r="393" ht="3.25" customHeight="1"/>
-    <row r="394" ht="3.25" customHeight="1"/>
-    <row r="395" ht="3.25" customHeight="1"/>
-    <row r="396" ht="3.25" customHeight="1"/>
-    <row r="397" ht="3.25" customHeight="1"/>
-    <row r="398" ht="3.25" customHeight="1"/>
-    <row r="399" ht="3.25" customHeight="1"/>
-    <row r="400" ht="3.25" customHeight="1"/>
-    <row r="401" ht="3.25" customHeight="1"/>
-    <row r="402" ht="3.25" customHeight="1"/>
-    <row r="403" ht="3.25" customHeight="1"/>
-    <row r="404" ht="3.25" customHeight="1"/>
-    <row r="405" ht="3.25" customHeight="1"/>
-    <row r="406" ht="3.25" customHeight="1"/>
-    <row r="407" ht="3.25" customHeight="1"/>
-    <row r="408" ht="3.25" customHeight="1"/>
-    <row r="409" ht="3.25" customHeight="1"/>
-    <row r="410" ht="3.25" customHeight="1"/>
-    <row r="411" ht="3.25" customHeight="1"/>
-    <row r="412" ht="3.25" customHeight="1"/>
-    <row r="413" ht="3.25" customHeight="1"/>
-    <row r="414" ht="3.25" customHeight="1"/>
-    <row r="415" ht="3.25" customHeight="1"/>
-    <row r="416" ht="3.25" customHeight="1"/>
-    <row r="417" ht="3.25" customHeight="1"/>
-    <row r="418" ht="3.25" customHeight="1"/>
-    <row r="419" ht="3.25" customHeight="1"/>
-    <row r="420" ht="3.25" customHeight="1"/>
-    <row r="421" ht="3.25" customHeight="1"/>
-    <row r="422" ht="3.25" customHeight="1"/>
-    <row r="423" ht="3.25" customHeight="1"/>
-    <row r="424" ht="3.25" customHeight="1"/>
-    <row r="425" ht="3.25" customHeight="1"/>
-    <row r="426" ht="3.25" customHeight="1"/>
-    <row r="427" ht="3.25" customHeight="1"/>
-    <row r="428" ht="3.25" customHeight="1"/>
-    <row r="429" ht="3.25" customHeight="1"/>
-    <row r="430" ht="3.25" customHeight="1"/>
-    <row r="431" ht="3.25" customHeight="1"/>
-    <row r="432" ht="3.25" customHeight="1"/>
-    <row r="433" ht="3.25" customHeight="1"/>
-    <row r="434" ht="3.25" customHeight="1"/>
-    <row r="435" ht="3.25" customHeight="1"/>
-    <row r="436" ht="3.25" customHeight="1"/>
-    <row r="437" ht="3.25" customHeight="1"/>
-    <row r="438" ht="3.25" customHeight="1"/>
-    <row r="439" ht="3.25" customHeight="1"/>
-    <row r="440" ht="3.25" customHeight="1"/>
-    <row r="441" ht="3.25" customHeight="1"/>
-    <row r="442" ht="3.25" customHeight="1"/>
-    <row r="443" ht="3.25" customHeight="1"/>
-    <row r="444" ht="3.25" customHeight="1"/>
-    <row r="445" ht="3.25" customHeight="1"/>
-    <row r="446" ht="3.25" customHeight="1"/>
-    <row r="447" ht="3.25" customHeight="1"/>
-    <row r="448" ht="3.25" customHeight="1"/>
-    <row r="449" ht="3.25" customHeight="1"/>
-    <row r="450" ht="3.25" customHeight="1"/>
-    <row r="451" ht="3.25" customHeight="1"/>
-    <row r="452" ht="3.25" customHeight="1"/>
-    <row r="453" ht="3.25" customHeight="1"/>
-    <row r="454" ht="3.25" customHeight="1"/>
-    <row r="455" ht="3.25" customHeight="1"/>
-    <row r="456" ht="3.25" customHeight="1"/>
-    <row r="457" ht="3.25" customHeight="1"/>
-    <row r="458" ht="3.25" customHeight="1"/>
-    <row r="459" ht="3.25" customHeight="1"/>
-    <row r="460" ht="3.25" customHeight="1"/>
-    <row r="461" ht="3.25" customHeight="1"/>
-    <row r="462" ht="3.25" customHeight="1"/>
-    <row r="463" ht="3.25" customHeight="1"/>
-    <row r="464" ht="3.25" customHeight="1"/>
-    <row r="465" ht="3.25" customHeight="1"/>
-    <row r="466" ht="3.25" customHeight="1"/>
-    <row r="467" ht="3.25" customHeight="1"/>
-    <row r="468" ht="3.25" customHeight="1"/>
-    <row r="469" ht="3.25" customHeight="1"/>
-    <row r="470" ht="3.25" customHeight="1"/>
-    <row r="471" ht="3.25" customHeight="1"/>
-    <row r="472" ht="3.25" customHeight="1"/>
-    <row r="473" ht="3.25" customHeight="1"/>
-    <row r="474" ht="3.25" customHeight="1"/>
-    <row r="475" ht="3.25" customHeight="1"/>
-    <row r="476" ht="3.25" customHeight="1"/>
-    <row r="477" ht="3.25" customHeight="1"/>
-    <row r="478" ht="3.25" customHeight="1"/>
-    <row r="479" ht="3.25" customHeight="1"/>
-    <row r="480" ht="3.25" customHeight="1"/>
-    <row r="481" ht="3.25" customHeight="1"/>
-    <row r="482" ht="3.25" customHeight="1"/>
-    <row r="483" ht="3.25" customHeight="1"/>
-    <row r="484" ht="3.25" customHeight="1"/>
-    <row r="485" ht="3.25" customHeight="1"/>
-    <row r="486" ht="3.25" customHeight="1"/>
-    <row r="487" ht="3.25" customHeight="1"/>
-    <row r="488" ht="3.25" customHeight="1"/>
-    <row r="489" ht="3.25" customHeight="1"/>
-    <row r="490" ht="3.25" customHeight="1"/>
-    <row r="491" ht="3.25" customHeight="1"/>
-    <row r="492" ht="3.25" customHeight="1"/>
-    <row r="493" ht="3.25" customHeight="1"/>
-    <row r="494" ht="3.25" customHeight="1"/>
-    <row r="495" ht="3.25" customHeight="1"/>
-    <row r="496" ht="3.25" customHeight="1"/>
-    <row r="497" ht="3.25" customHeight="1"/>
-    <row r="498" ht="3.25" customHeight="1"/>
-    <row r="499" ht="3.25" customHeight="1"/>
-    <row r="500" ht="3.25" customHeight="1"/>
-    <row r="501" ht="3.25" customHeight="1"/>
-    <row r="502" ht="3.25" customHeight="1"/>
-    <row r="503" ht="3.25" customHeight="1"/>
-    <row r="504" ht="3.25" customHeight="1"/>
-    <row r="505" ht="3.25" customHeight="1"/>
-    <row r="506" ht="3.25" customHeight="1"/>
-    <row r="507" ht="3.25" customHeight="1"/>
-    <row r="508" ht="3.25" customHeight="1"/>
-    <row r="509" ht="3.25" customHeight="1"/>
-    <row r="510" ht="3.25" customHeight="1"/>
-    <row r="511" ht="3.25" customHeight="1"/>
-    <row r="512" ht="3.25" customHeight="1"/>
-    <row r="513" ht="3.25" customHeight="1"/>
-    <row r="514" ht="3.25" customHeight="1"/>
-    <row r="515" ht="3.25" customHeight="1"/>
-    <row r="516" ht="3.25" customHeight="1"/>
-    <row r="517" ht="3.25" customHeight="1"/>
-    <row r="518" ht="3.25" customHeight="1"/>
-    <row r="519" ht="3.25" customHeight="1"/>
-    <row r="520" ht="3.25" customHeight="1"/>
-    <row r="521" ht="3.25" customHeight="1"/>
-    <row r="522" ht="3.25" customHeight="1"/>
-    <row r="523" ht="3.25" customHeight="1"/>
-    <row r="524" ht="3.25" customHeight="1"/>
-    <row r="525" ht="3.25" customHeight="1"/>
-    <row r="526" ht="3.25" customHeight="1"/>
-    <row r="527" ht="3.25" customHeight="1"/>
-    <row r="528" ht="3.25" customHeight="1"/>
-    <row r="529" ht="3.25" customHeight="1"/>
-    <row r="530" ht="3.25" customHeight="1"/>
-    <row r="531" ht="3.25" customHeight="1"/>
-    <row r="532" ht="3.25" customHeight="1"/>
-    <row r="533" ht="3.25" customHeight="1"/>
-    <row r="534" ht="3.25" customHeight="1"/>
-    <row r="535" ht="3.25" customHeight="1"/>
-    <row r="536" ht="3.25" customHeight="1"/>
-    <row r="537" ht="3.25" customHeight="1"/>
-    <row r="538" ht="3.25" customHeight="1"/>
-    <row r="539" ht="3.25" customHeight="1"/>
-    <row r="540" ht="3.25" customHeight="1"/>
-    <row r="541" ht="3.25" customHeight="1"/>
-    <row r="542" ht="3.25" customHeight="1"/>
-    <row r="543" ht="3.25" customHeight="1"/>
-    <row r="544" ht="3.25" customHeight="1"/>
-    <row r="545" ht="3.25" customHeight="1"/>
-    <row r="546" ht="3.25" customHeight="1"/>
-    <row r="547" ht="3.25" customHeight="1"/>
-    <row r="548" ht="3.25" customHeight="1"/>
-    <row r="549" ht="3.25" customHeight="1"/>
-    <row r="550" ht="3.25" customHeight="1"/>
-    <row r="551" ht="3.25" customHeight="1"/>
-    <row r="552" ht="3.25" customHeight="1"/>
-    <row r="553" ht="3.25" customHeight="1"/>
-    <row r="554" ht="3.25" customHeight="1"/>
-    <row r="555" ht="3.25" customHeight="1"/>
-    <row r="556" ht="3.25" customHeight="1"/>
-    <row r="557" ht="3.25" customHeight="1"/>
-    <row r="558" ht="3.25" customHeight="1"/>
-    <row r="559" ht="3.25" customHeight="1"/>
-    <row r="560" ht="3.25" customHeight="1"/>
-    <row r="561" ht="3.25" customHeight="1"/>
-    <row r="562" ht="3.25" customHeight="1"/>
-    <row r="563" ht="3.25" customHeight="1"/>
-    <row r="564" ht="3.25" customHeight="1"/>
-    <row r="565" ht="3.25" customHeight="1"/>
-    <row r="566" ht="3.25" customHeight="1"/>
-    <row r="567" ht="3.25" customHeight="1"/>
-    <row r="568" ht="3.25" customHeight="1"/>
-    <row r="569" ht="3.25" customHeight="1"/>
-    <row r="570" ht="3.25" customHeight="1"/>
-    <row r="571" ht="3.25" customHeight="1"/>
-    <row r="572" ht="3.25" customHeight="1"/>
-    <row r="573" ht="3.25" customHeight="1"/>
-    <row r="574" ht="3.25" customHeight="1"/>
-    <row r="575" ht="3.25" customHeight="1"/>
-    <row r="576" ht="3.25" customHeight="1"/>
-    <row r="577" ht="3.25" customHeight="1"/>
-    <row r="578" ht="3.25" customHeight="1"/>
-    <row r="579" ht="3.25" customHeight="1"/>
-    <row r="580" ht="3.25" customHeight="1"/>
-    <row r="581" ht="3.25" customHeight="1"/>
-    <row r="582" ht="3.25" customHeight="1"/>
-    <row r="583" ht="3.25" customHeight="1"/>
-    <row r="584" ht="3.25" customHeight="1"/>
-    <row r="585" ht="3.25" customHeight="1"/>
-    <row r="586" ht="3.25" customHeight="1"/>
-    <row r="587" ht="3.25" customHeight="1"/>
-    <row r="588" ht="3.25" customHeight="1"/>
-    <row r="589" ht="3.25" customHeight="1"/>
-    <row r="590" ht="3.25" customHeight="1"/>
-    <row r="591" ht="3.25" customHeight="1"/>
-    <row r="592" ht="3.25" customHeight="1"/>
-    <row r="593" ht="3.25" customHeight="1"/>
-    <row r="594" ht="3.25" customHeight="1"/>
-    <row r="595" ht="3.25" customHeight="1"/>
-    <row r="596" ht="3.25" customHeight="1"/>
-    <row r="597" ht="3.25" customHeight="1"/>
-    <row r="598" ht="3.25" customHeight="1"/>
-    <row r="599" ht="3.25" customHeight="1"/>
-    <row r="600" ht="3.25" customHeight="1"/>
-    <row r="601" ht="3.25" customHeight="1"/>
-    <row r="602" ht="3.25" customHeight="1"/>
-    <row r="603" ht="3.25" customHeight="1"/>
-    <row r="604" ht="3.25" customHeight="1"/>
-    <row r="605" ht="3.25" customHeight="1"/>
-    <row r="606" ht="3.25" customHeight="1"/>
-    <row r="607" ht="3.25" customHeight="1"/>
-    <row r="608" ht="3.25" customHeight="1"/>
-    <row r="609" ht="3.25" customHeight="1"/>
-    <row r="610" ht="3.25" customHeight="1"/>
-    <row r="611" ht="3.25" customHeight="1"/>
-    <row r="612" ht="3.25" customHeight="1"/>
-    <row r="613" ht="3.25" customHeight="1"/>
-    <row r="614" ht="3.25" customHeight="1"/>
-    <row r="615" ht="3.25" customHeight="1"/>
-    <row r="616" ht="3.25" customHeight="1"/>
-    <row r="617" ht="3.25" customHeight="1"/>
-    <row r="618" ht="3.25" customHeight="1"/>
-    <row r="619" ht="3.25" customHeight="1"/>
-    <row r="620" ht="3.25" customHeight="1"/>
-    <row r="621" ht="3.25" customHeight="1"/>
-    <row r="622" ht="3.25" customHeight="1"/>
-    <row r="623" ht="3.25" customHeight="1"/>
-    <row r="624" ht="3.25" customHeight="1"/>
-    <row r="625" ht="3.25" customHeight="1"/>
-    <row r="626" ht="3.25" customHeight="1"/>
-    <row r="627" ht="3.25" customHeight="1"/>
-    <row r="628" ht="3.25" customHeight="1"/>
-    <row r="629" ht="3.25" customHeight="1"/>
-    <row r="630" ht="3.25" customHeight="1"/>
-    <row r="631" ht="3.25" customHeight="1"/>
-    <row r="632" ht="3.25" customHeight="1"/>
-    <row r="633" ht="3.25" customHeight="1"/>
-    <row r="634" ht="3.25" customHeight="1"/>
-    <row r="635" ht="3.25" customHeight="1"/>
-    <row r="636" ht="3.25" customHeight="1"/>
-    <row r="637" ht="3.25" customHeight="1"/>
-    <row r="638" ht="3.25" customHeight="1"/>
-    <row r="639" ht="3.25" customHeight="1"/>
-    <row r="640" ht="3.25" customHeight="1"/>
-    <row r="641" ht="3.25" customHeight="1"/>
-    <row r="642" ht="3.25" customHeight="1"/>
-    <row r="643" ht="3.25" customHeight="1"/>
-    <row r="644" ht="3.25" customHeight="1"/>
-    <row r="645" ht="3.25" customHeight="1"/>
-    <row r="646" ht="3.25" customHeight="1"/>
-    <row r="647" ht="3.25" customHeight="1"/>
-    <row r="648" ht="3.25" customHeight="1"/>
-    <row r="649" ht="3.25" customHeight="1"/>
-    <row r="650" ht="3.25" customHeight="1"/>
-    <row r="651" ht="3.25" customHeight="1"/>
-    <row r="652" ht="3.25" customHeight="1"/>
-    <row r="653" ht="3.25" customHeight="1"/>
-    <row r="654" ht="3.25" customHeight="1"/>
-    <row r="655" ht="3.25" customHeight="1"/>
-    <row r="656" ht="3.25" customHeight="1"/>
-    <row r="657" ht="3.25" customHeight="1"/>
-    <row r="658" ht="3.25" customHeight="1"/>
-    <row r="659" ht="3.25" customHeight="1"/>
-    <row r="660" ht="3.25" customHeight="1"/>
-    <row r="661" ht="3.25" customHeight="1"/>
-    <row r="662" ht="3.25" customHeight="1"/>
-    <row r="663" ht="3.25" customHeight="1"/>
-    <row r="664" ht="3.25" customHeight="1"/>
-    <row r="665" ht="3.25" customHeight="1"/>
-    <row r="666" ht="3.25" customHeight="1"/>
-    <row r="667" ht="3.25" customHeight="1"/>
-    <row r="668" ht="3.25" customHeight="1"/>
-    <row r="669" ht="3.25" customHeight="1"/>
-    <row r="670" ht="3.25" customHeight="1"/>
-    <row r="671" ht="3.25" customHeight="1"/>
-    <row r="672" ht="3.25" customHeight="1"/>
-    <row r="673" ht="3.25" customHeight="1"/>
-    <row r="674" ht="3.25" customHeight="1"/>
-    <row r="675" ht="3.25" customHeight="1"/>
-    <row r="676" ht="3.25" customHeight="1"/>
-    <row r="677" ht="3.25" customHeight="1"/>
-    <row r="678" ht="3.25" customHeight="1"/>
-    <row r="679" ht="3.25" customHeight="1"/>
-    <row r="680" ht="3.25" customHeight="1"/>
-    <row r="681" ht="3.25" customHeight="1"/>
-    <row r="682" ht="3.25" customHeight="1"/>
-    <row r="683" ht="3.25" customHeight="1"/>
-    <row r="684" ht="3.25" customHeight="1"/>
-    <row r="685" ht="3.25" customHeight="1"/>
-    <row r="686" ht="3.25" customHeight="1"/>
-    <row r="687" ht="3.25" customHeight="1"/>
-    <row r="688" ht="3.25" customHeight="1"/>
-    <row r="689" ht="3.25" customHeight="1"/>
-    <row r="690" ht="3.25" customHeight="1"/>
-    <row r="691" ht="3.25" customHeight="1"/>
-    <row r="692" ht="3.25" customHeight="1"/>
-    <row r="693" ht="3.25" customHeight="1"/>
-    <row r="694" ht="3.25" customHeight="1"/>
-    <row r="695" ht="3.25" customHeight="1"/>
-    <row r="696" ht="3.25" customHeight="1"/>
-    <row r="697" ht="3.25" customHeight="1"/>
-    <row r="698" ht="3.25" customHeight="1"/>
-    <row r="699" ht="3.25" customHeight="1"/>
-    <row r="700" ht="3.25" customHeight="1"/>
-    <row r="701" ht="3.25" customHeight="1"/>
-    <row r="702" ht="3.25" customHeight="1"/>
-    <row r="703" ht="3.25" customHeight="1"/>
-    <row r="704" ht="3.25" customHeight="1"/>
-    <row r="705" ht="3.25" customHeight="1"/>
-    <row r="706" ht="3.25" customHeight="1"/>
-    <row r="707" ht="3.25" customHeight="1"/>
-    <row r="708" ht="3.25" customHeight="1"/>
-    <row r="709" ht="3.25" customHeight="1"/>
-    <row r="710" ht="3.25" customHeight="1"/>
-    <row r="711" ht="3.25" customHeight="1"/>
-    <row r="712" ht="3.25" customHeight="1"/>
-    <row r="713" ht="3.25" customHeight="1"/>
-    <row r="714" ht="3.25" customHeight="1"/>
-    <row r="715" ht="3.25" customHeight="1"/>
-    <row r="716" ht="3.25" customHeight="1"/>
-    <row r="717" ht="3.25" customHeight="1"/>
-    <row r="718" ht="3.25" customHeight="1"/>
-    <row r="719" ht="3.25" customHeight="1"/>
-    <row r="720" ht="3.25" customHeight="1"/>
-    <row r="721" ht="3.25" customHeight="1"/>
-    <row r="722" ht="3.25" customHeight="1"/>
-    <row r="723" ht="3.25" customHeight="1"/>
-    <row r="724" ht="3.25" customHeight="1"/>
-    <row r="725" ht="3.25" customHeight="1"/>
-    <row r="726" ht="3.25" customHeight="1"/>
-    <row r="727" ht="3.25" customHeight="1"/>
-    <row r="728" ht="3.25" customHeight="1"/>
-    <row r="729" ht="3.25" customHeight="1"/>
-    <row r="730" ht="3.25" customHeight="1"/>
-    <row r="731" ht="3.25" customHeight="1"/>
-    <row r="732" ht="3.25" customHeight="1"/>
-    <row r="733" ht="3.25" customHeight="1"/>
-    <row r="734" ht="3.25" customHeight="1"/>
-    <row r="735" ht="3.25" customHeight="1"/>
-    <row r="736" ht="3.25" customHeight="1"/>
-    <row r="737" ht="3.25" customHeight="1"/>
-    <row r="738" ht="3.25" customHeight="1"/>
-    <row r="739" ht="3.25" customHeight="1"/>
-    <row r="740" ht="3.25" customHeight="1"/>
-    <row r="741" ht="3.25" customHeight="1"/>
-    <row r="742" ht="3.25" customHeight="1"/>
-    <row r="743" ht="3.25" customHeight="1"/>
-    <row r="744" ht="3.25" customHeight="1"/>
-    <row r="745" ht="3.25" customHeight="1"/>
-    <row r="746" ht="3.25" customHeight="1"/>
-    <row r="747" ht="3.25" customHeight="1"/>
-    <row r="748" ht="3.25" customHeight="1"/>
-    <row r="749" ht="3.25" customHeight="1"/>
-    <row r="750" ht="3.25" customHeight="1"/>
-    <row r="751" ht="3.25" customHeight="1"/>
-    <row r="752" ht="3.25" customHeight="1"/>
-    <row r="753" ht="3.25" customHeight="1"/>
-    <row r="754" ht="3.25" customHeight="1"/>
-    <row r="755" ht="3.25" customHeight="1"/>
-    <row r="756" ht="3.25" customHeight="1"/>
-    <row r="757" ht="3.25" customHeight="1"/>
-    <row r="758" ht="3.25" customHeight="1"/>
-    <row r="759" ht="3.25" customHeight="1"/>
-    <row r="760" ht="3.25" customHeight="1"/>
-    <row r="761" ht="3.25" customHeight="1"/>
-    <row r="762" ht="3.25" customHeight="1"/>
-    <row r="763" ht="3.25" customHeight="1"/>
-    <row r="764" ht="3.25" customHeight="1"/>
-    <row r="765" ht="3.25" customHeight="1"/>
-    <row r="766" ht="3.25" customHeight="1"/>
-    <row r="767" ht="3.25" customHeight="1"/>
-    <row r="768" ht="3.25" customHeight="1"/>
-    <row r="769" ht="3.25" customHeight="1"/>
-    <row r="770" ht="3.25" customHeight="1"/>
-    <row r="771" ht="3.25" customHeight="1"/>
-    <row r="772" ht="3.25" customHeight="1"/>
-    <row r="773" ht="3.25" customHeight="1"/>
-    <row r="774" ht="3.25" customHeight="1"/>
-    <row r="775" ht="3.25" customHeight="1"/>
-    <row r="776" ht="3.25" customHeight="1"/>
-    <row r="777" ht="3.25" customHeight="1"/>
-    <row r="778" ht="3.25" customHeight="1"/>
-    <row r="779" ht="3.25" customHeight="1"/>
-    <row r="780" ht="3.25" customHeight="1"/>
-    <row r="781" ht="3.25" customHeight="1"/>
-    <row r="782" ht="3.25" customHeight="1"/>
-    <row r="783" ht="3.25" customHeight="1"/>
-    <row r="784" ht="3.25" customHeight="1"/>
-    <row r="785" ht="3.25" customHeight="1"/>
-    <row r="786" ht="3.25" customHeight="1"/>
-    <row r="787" ht="3.25" customHeight="1"/>
-    <row r="788" ht="3.25" customHeight="1"/>
-    <row r="789" ht="3.25" customHeight="1"/>
-    <row r="790" ht="3.25" customHeight="1"/>
-    <row r="791" ht="3.25" customHeight="1"/>
-    <row r="792" ht="3.25" customHeight="1"/>
-    <row r="793" ht="3.25" customHeight="1"/>
-    <row r="794" ht="3.25" customHeight="1"/>
-    <row r="795" ht="3.25" customHeight="1"/>
-    <row r="796" ht="3.25" customHeight="1"/>
-    <row r="797" ht="3.25" customHeight="1"/>
-    <row r="798" ht="3.25" customHeight="1"/>
-    <row r="799" ht="3.25" customHeight="1"/>
-    <row r="800" ht="3.25" customHeight="1"/>
-    <row r="801" ht="3.25" customHeight="1"/>
-    <row r="802" ht="3.25" customHeight="1"/>
-    <row r="803" ht="3.25" customHeight="1"/>
-    <row r="804" ht="3.25" customHeight="1"/>
-    <row r="805" ht="3.25" customHeight="1"/>
-    <row r="806" ht="3.25" customHeight="1"/>
-    <row r="807" ht="3.25" customHeight="1"/>
-    <row r="808" ht="3.25" customHeight="1"/>
-    <row r="809" ht="3.25" customHeight="1"/>
-    <row r="810" ht="3.25" customHeight="1"/>
-    <row r="811" ht="3.25" customHeight="1"/>
-    <row r="812" ht="3.25" customHeight="1"/>
-    <row r="813" ht="3.25" customHeight="1"/>
-    <row r="814" ht="3.25" customHeight="1"/>
-    <row r="815" ht="3.25" customHeight="1"/>
-    <row r="816" ht="3.25" customHeight="1"/>
-    <row r="817" ht="3.25" customHeight="1"/>
-    <row r="818" ht="3.25" customHeight="1"/>
-    <row r="819" ht="3.25" customHeight="1"/>
-    <row r="820" ht="3.25" customHeight="1"/>
-    <row r="821" ht="3.25" customHeight="1"/>
-    <row r="822" ht="3.25" customHeight="1"/>
-    <row r="823" ht="3.25" customHeight="1"/>
-    <row r="824" ht="3.25" customHeight="1"/>
-    <row r="825" ht="3.25" customHeight="1"/>
-    <row r="826" ht="3.25" customHeight="1"/>
-    <row r="827" ht="3.25" customHeight="1"/>
-    <row r="828" ht="3.25" customHeight="1"/>
-    <row r="829" ht="3.25" customHeight="1"/>
-    <row r="830" ht="3.25" customHeight="1"/>
-    <row r="831" ht="3.25" customHeight="1"/>
-    <row r="832" ht="3.25" customHeight="1"/>
-    <row r="833" ht="3.25" customHeight="1"/>
-    <row r="834" ht="3.25" customHeight="1"/>
-    <row r="835" ht="3.25" customHeight="1"/>
-    <row r="836" ht="3.25" customHeight="1"/>
-    <row r="837" ht="3.25" customHeight="1"/>
-    <row r="838" ht="3.25" customHeight="1"/>
-    <row r="839" ht="3.25" customHeight="1"/>
-    <row r="840" ht="3.25" customHeight="1"/>
-    <row r="841" ht="3.25" customHeight="1"/>
-    <row r="842" ht="3.25" customHeight="1"/>
-    <row r="843" ht="3.25" customHeight="1"/>
-    <row r="844" ht="3.25" customHeight="1"/>
-    <row r="845" ht="3.25" customHeight="1"/>
-    <row r="846" ht="3.25" customHeight="1"/>
-    <row r="847" ht="3.25" customHeight="1"/>
-    <row r="848" ht="3.25" customHeight="1"/>
-    <row r="849" ht="3.25" customHeight="1"/>
-    <row r="850" ht="3.25" customHeight="1"/>
-    <row r="851" ht="3.25" customHeight="1"/>
-    <row r="852" ht="3.25" customHeight="1"/>
-    <row r="853" ht="3.25" customHeight="1"/>
-    <row r="854" ht="3.25" customHeight="1"/>
-    <row r="855" ht="3.25" customHeight="1"/>
-    <row r="856" ht="3.25" customHeight="1"/>
-    <row r="857" ht="3.25" customHeight="1"/>
-    <row r="858" ht="3.25" customHeight="1"/>
-    <row r="859" ht="3.25" customHeight="1"/>
-    <row r="860" ht="3.25" customHeight="1"/>
-    <row r="861" ht="3.25" customHeight="1"/>
-    <row r="862" ht="3.25" customHeight="1"/>
-    <row r="863" ht="3.25" customHeight="1"/>
-    <row r="864" ht="3.25" customHeight="1"/>
-    <row r="865" ht="3.25" customHeight="1"/>
-    <row r="866" ht="3.25" customHeight="1"/>
-    <row r="867" ht="3.25" customHeight="1"/>
-    <row r="868" ht="3.25" customHeight="1"/>
-    <row r="869" ht="3.25" customHeight="1"/>
-    <row r="870" ht="3.25" customHeight="1"/>
-    <row r="871" ht="3.25" customHeight="1"/>
-    <row r="872" ht="3.25" customHeight="1"/>
-    <row r="873" ht="3.25" customHeight="1"/>
-    <row r="874" ht="3.25" customHeight="1"/>
-    <row r="875" ht="3.25" customHeight="1"/>
-    <row r="876" ht="3.25" customHeight="1"/>
-    <row r="877" ht="3.25" customHeight="1"/>
-    <row r="878" ht="3.25" customHeight="1"/>
-    <row r="879" ht="3.25" customHeight="1"/>
-    <row r="880" ht="3.25" customHeight="1"/>
-    <row r="881" ht="3.25" customHeight="1"/>
-    <row r="882" ht="3.25" customHeight="1"/>
-    <row r="883" ht="3.25" customHeight="1"/>
-    <row r="884" ht="3.25" customHeight="1"/>
-    <row r="885" ht="3.25" customHeight="1"/>
-    <row r="886" ht="3.25" customHeight="1"/>
-    <row r="887" ht="3.25" customHeight="1"/>
-    <row r="888" ht="3.25" customHeight="1"/>
-    <row r="889" ht="3.25" customHeight="1"/>
-    <row r="890" ht="3.25" customHeight="1"/>
-    <row r="891" ht="3.25" customHeight="1"/>
-    <row r="892" ht="3.25" customHeight="1"/>
-    <row r="893" ht="3.25" customHeight="1"/>
-    <row r="894" ht="3.25" customHeight="1"/>
-    <row r="895" ht="3.25" customHeight="1"/>
-    <row r="896" ht="3.25" customHeight="1"/>
-    <row r="897" ht="3.25" customHeight="1"/>
-    <row r="898" ht="3.25" customHeight="1"/>
-    <row r="899" ht="3.25" customHeight="1"/>
-    <row r="900" ht="3.25" customHeight="1"/>
-    <row r="901" ht="3.25" customHeight="1"/>
-    <row r="902" ht="3.25" customHeight="1"/>
-    <row r="903" ht="3.25" customHeight="1"/>
-    <row r="904" ht="3.25" customHeight="1"/>
-    <row r="905" ht="3.25" customHeight="1"/>
-    <row r="906" ht="3.25" customHeight="1"/>
-    <row r="907" ht="3.25" customHeight="1"/>
-    <row r="908" ht="3.25" customHeight="1"/>
-    <row r="909" ht="3.25" customHeight="1"/>
-    <row r="910" ht="3.25" customHeight="1"/>
-    <row r="911" ht="3.25" customHeight="1"/>
-    <row r="912" ht="3.25" customHeight="1"/>
-    <row r="913" ht="3.25" customHeight="1"/>
-    <row r="914" ht="3.25" customHeight="1"/>
-    <row r="915" ht="3.25" customHeight="1"/>
-    <row r="916" ht="3.25" customHeight="1"/>
-    <row r="917" ht="3.25" customHeight="1"/>
-    <row r="918" ht="3.25" customHeight="1"/>
-    <row r="919" ht="3.25" customHeight="1"/>
-    <row r="920" ht="3.25" customHeight="1"/>
-    <row r="921" ht="3.25" customHeight="1"/>
-    <row r="922" ht="3.25" customHeight="1"/>
-    <row r="923" ht="3.25" customHeight="1"/>
-    <row r="924" ht="3.25" customHeight="1"/>
-    <row r="925" ht="3.25" customHeight="1"/>
-    <row r="926" ht="3.25" customHeight="1"/>
-    <row r="927" ht="3.25" customHeight="1"/>
-    <row r="928" ht="3.25" customHeight="1"/>
-    <row r="929" ht="3.25" customHeight="1"/>
-    <row r="930" ht="3.25" customHeight="1"/>
-    <row r="931" ht="3.25" customHeight="1"/>
-    <row r="932" ht="3.25" customHeight="1"/>
-    <row r="933" ht="3.25" customHeight="1"/>
-    <row r="934" ht="3.25" customHeight="1"/>
-    <row r="935" ht="3.25" customHeight="1"/>
-    <row r="936" ht="3.25" customHeight="1"/>
-    <row r="937" ht="3.25" customHeight="1"/>
-    <row r="938" ht="3.25" customHeight="1"/>
-    <row r="939" ht="3.25" customHeight="1"/>
-    <row r="940" ht="3.25" customHeight="1"/>
-    <row r="941" ht="3.25" customHeight="1"/>
-    <row r="942" ht="3.25" customHeight="1"/>
-    <row r="943" ht="3.25" customHeight="1"/>
-    <row r="944" ht="3.25" customHeight="1"/>
-    <row r="945" ht="3.25" customHeight="1"/>
-    <row r="946" ht="3.25" customHeight="1"/>
-    <row r="947" ht="3.25" customHeight="1"/>
-    <row r="948" ht="3.25" customHeight="1"/>
-    <row r="949" ht="3.25" customHeight="1"/>
-    <row r="950" ht="3.25" customHeight="1"/>
-    <row r="951" ht="3.25" customHeight="1"/>
-    <row r="952" ht="3.25" customHeight="1"/>
-    <row r="953" ht="3.25" customHeight="1"/>
-    <row r="954" ht="3.25" customHeight="1"/>
-    <row r="955" ht="3.25" customHeight="1"/>
-    <row r="956" ht="3.25" customHeight="1"/>
-    <row r="957" ht="3.25" customHeight="1"/>
-    <row r="958" ht="3.25" customHeight="1"/>
-    <row r="959" ht="3.25" customHeight="1"/>
-    <row r="960" ht="3.25" customHeight="1"/>
-    <row r="961" ht="3.25" customHeight="1"/>
-    <row r="962" ht="3.25" customHeight="1"/>
-    <row r="963" ht="3.25" customHeight="1"/>
-    <row r="964" ht="3.25" customHeight="1"/>
-    <row r="965" ht="3.25" customHeight="1"/>
-    <row r="966" ht="3.25" customHeight="1"/>
-    <row r="967" ht="3.25" customHeight="1"/>
-    <row r="968" ht="3.25" customHeight="1"/>
-    <row r="969" ht="3.25" customHeight="1"/>
-    <row r="970" ht="3.25" customHeight="1"/>
-    <row r="971" ht="3.25" customHeight="1"/>
-    <row r="972" ht="3.25" customHeight="1"/>
-    <row r="973" ht="3.25" customHeight="1"/>
-    <row r="974" ht="3.25" customHeight="1"/>
-    <row r="975" ht="3.25" customHeight="1"/>
-    <row r="976" ht="3.25" customHeight="1"/>
-    <row r="977" ht="3.25" customHeight="1"/>
-    <row r="978" ht="3.25" customHeight="1"/>
-    <row r="979" ht="3.25" customHeight="1"/>
-    <row r="980" ht="3.25" customHeight="1"/>
-    <row r="981" ht="3.25" customHeight="1"/>
-    <row r="982" ht="3.25" customHeight="1"/>
-    <row r="983" ht="3.25" customHeight="1"/>
-    <row r="984" ht="3.25" customHeight="1"/>
-    <row r="985" ht="3.25" customHeight="1"/>
-    <row r="986" ht="3.25" customHeight="1"/>
-    <row r="987" ht="3.25" customHeight="1"/>
-    <row r="988" ht="3.25" customHeight="1"/>
-    <row r="989" ht="3.25" customHeight="1"/>
-    <row r="990" ht="3.25" customHeight="1"/>
-    <row r="991" ht="3.25" customHeight="1"/>
-    <row r="992" ht="3.25" customHeight="1"/>
-    <row r="993" ht="3.25" customHeight="1"/>
-    <row r="994" ht="3.25" customHeight="1"/>
-    <row r="995" ht="3.25" customHeight="1"/>
-    <row r="996" ht="3.25" customHeight="1"/>
-    <row r="997" ht="3.25" customHeight="1"/>
-    <row r="998" ht="3.25" customHeight="1"/>
-    <row r="999" ht="3.25" customHeight="1"/>
-    <row r="1000" ht="3.25" customHeight="1"/>
+    <row r="33" ht="3.9" customHeight="1"/>
+    <row r="34" ht="3.9" customHeight="1"/>
+    <row r="35" ht="3.9" customHeight="1"/>
+    <row r="36" ht="3.9" customHeight="1"/>
+    <row r="37" ht="3.9" customHeight="1"/>
+    <row r="38" ht="3.9" customHeight="1"/>
+    <row r="39" ht="3.9" customHeight="1"/>
+    <row r="40" ht="3.9" customHeight="1"/>
+    <row r="41" ht="3.9" customHeight="1"/>
+    <row r="42" ht="3.9" customHeight="1"/>
+    <row r="43" ht="3.9" customHeight="1"/>
+    <row r="44" ht="3.9" customHeight="1"/>
+    <row r="45" ht="3.9" customHeight="1"/>
+    <row r="46" ht="3.9" customHeight="1"/>
+    <row r="47" ht="3.9" customHeight="1"/>
+    <row r="48" ht="3.9" customHeight="1"/>
+    <row r="49" ht="3.9" customHeight="1"/>
+    <row r="50" ht="3.9" customHeight="1"/>
+    <row r="51" ht="3.9" customHeight="1"/>
+    <row r="52" ht="3.9" customHeight="1"/>
+    <row r="53" ht="3.9" customHeight="1"/>
+    <row r="54" ht="3.9" customHeight="1"/>
+    <row r="55" ht="3.9" customHeight="1"/>
+    <row r="56" ht="3.9" customHeight="1"/>
+    <row r="57" ht="3.9" customHeight="1"/>
+    <row r="58" ht="3.9" customHeight="1"/>
+    <row r="59" ht="3.9" customHeight="1"/>
+    <row r="60" ht="3.9" customHeight="1"/>
+    <row r="61" ht="3.9" customHeight="1"/>
+    <row r="62" ht="3.9" customHeight="1"/>
+    <row r="63" ht="3.9" customHeight="1"/>
+    <row r="64" ht="3.9" customHeight="1"/>
+    <row r="65" ht="3.9" customHeight="1"/>
+    <row r="66" ht="3.9" customHeight="1"/>
+    <row r="67" ht="3.9" customHeight="1"/>
+    <row r="68" ht="3.9" customHeight="1"/>
+    <row r="69" ht="3.9" customHeight="1"/>
+    <row r="70" ht="3.9" customHeight="1"/>
+    <row r="71" ht="3.9" customHeight="1"/>
+    <row r="72" ht="3.9" customHeight="1"/>
+    <row r="73" ht="3.9" customHeight="1"/>
+    <row r="74" ht="3.9" customHeight="1"/>
+    <row r="75" ht="3.9" customHeight="1"/>
+    <row r="76" ht="3.9" customHeight="1"/>
+    <row r="77" ht="3.9" customHeight="1"/>
+    <row r="78" ht="3.9" customHeight="1"/>
+    <row r="79" ht="3.9" customHeight="1"/>
+    <row r="80" ht="3.9" customHeight="1"/>
+    <row r="81" ht="3.9" customHeight="1"/>
+    <row r="82" ht="3.9" customHeight="1"/>
+    <row r="83" ht="3.9" customHeight="1"/>
+    <row r="84" ht="3.9" customHeight="1"/>
+    <row r="85" ht="3.9" customHeight="1"/>
+    <row r="86" ht="3.9" customHeight="1"/>
+    <row r="87" ht="3.9" customHeight="1"/>
+    <row r="88" ht="3.9" customHeight="1"/>
+    <row r="89" ht="3.9" customHeight="1"/>
+    <row r="90" ht="3.9" customHeight="1"/>
+    <row r="91" ht="3.9" customHeight="1"/>
+    <row r="92" ht="3.9" customHeight="1"/>
+    <row r="93" ht="3.9" customHeight="1"/>
+    <row r="94" ht="3.9" customHeight="1"/>
+    <row r="95" ht="3.9" customHeight="1"/>
+    <row r="96" ht="3.9" customHeight="1"/>
+    <row r="97" ht="3.9" customHeight="1"/>
+    <row r="98" ht="3.9" customHeight="1"/>
+    <row r="99" ht="3.9" customHeight="1"/>
+    <row r="100" ht="3.9" customHeight="1"/>
+    <row r="101" ht="3.9" customHeight="1"/>
+    <row r="102" ht="3.9" customHeight="1"/>
+    <row r="103" ht="3.9" customHeight="1"/>
+    <row r="104" ht="3.9" customHeight="1"/>
+    <row r="105" ht="3.9" customHeight="1"/>
+    <row r="106" ht="3.9" customHeight="1"/>
+    <row r="107" ht="3.9" customHeight="1"/>
+    <row r="108" ht="3.9" customHeight="1"/>
+    <row r="109" ht="3.9" customHeight="1"/>
+    <row r="110" ht="3.9" customHeight="1"/>
+    <row r="111" ht="3.9" customHeight="1"/>
+    <row r="112" ht="3.9" customHeight="1"/>
+    <row r="113" ht="3.9" customHeight="1"/>
+    <row r="114" ht="3.9" customHeight="1"/>
+    <row r="115" ht="3.9" customHeight="1"/>
+    <row r="116" ht="3.9" customHeight="1"/>
+    <row r="117" ht="3.9" customHeight="1"/>
+    <row r="118" ht="3.9" customHeight="1"/>
+    <row r="119" ht="3.9" customHeight="1"/>
+    <row r="120" ht="3.9" customHeight="1"/>
+    <row r="121" ht="3.9" customHeight="1"/>
+    <row r="122" ht="3.9" customHeight="1"/>
+    <row r="123" ht="3.9" customHeight="1"/>
+    <row r="124" ht="3.9" customHeight="1"/>
+    <row r="125" ht="3.9" customHeight="1"/>
+    <row r="126" ht="3.9" customHeight="1"/>
+    <row r="127" ht="3.9" customHeight="1"/>
+    <row r="128" ht="3.9" customHeight="1"/>
+    <row r="129" ht="3.9" customHeight="1"/>
+    <row r="130" ht="3.9" customHeight="1"/>
+    <row r="131" ht="3.9" customHeight="1"/>
+    <row r="132" ht="3.9" customHeight="1"/>
+    <row r="133" ht="3.9" customHeight="1"/>
+    <row r="134" ht="3.9" customHeight="1"/>
+    <row r="135" ht="3.9" customHeight="1"/>
+    <row r="136" ht="3.9" customHeight="1"/>
+    <row r="137" ht="3.9" customHeight="1"/>
+    <row r="138" ht="3.9" customHeight="1"/>
+    <row r="139" ht="3.9" customHeight="1"/>
+    <row r="140" ht="3.9" customHeight="1"/>
+    <row r="141" ht="3.9" customHeight="1"/>
+    <row r="142" ht="3.9" customHeight="1"/>
+    <row r="143" ht="3.9" customHeight="1"/>
+    <row r="144" ht="3.9" customHeight="1"/>
+    <row r="145" ht="3.9" customHeight="1"/>
+    <row r="146" ht="3.9" customHeight="1"/>
+    <row r="147" ht="3.9" customHeight="1"/>
+    <row r="148" ht="3.9" customHeight="1"/>
+    <row r="149" ht="3.9" customHeight="1"/>
+    <row r="150" ht="3.9" customHeight="1"/>
+    <row r="151" ht="3.9" customHeight="1"/>
+    <row r="152" ht="3.9" customHeight="1"/>
+    <row r="153" ht="3.9" customHeight="1"/>
+    <row r="154" ht="3.9" customHeight="1"/>
+    <row r="155" ht="3.9" customHeight="1"/>
+    <row r="156" ht="3.9" customHeight="1"/>
+    <row r="157" ht="3.9" customHeight="1"/>
+    <row r="158" ht="3.9" customHeight="1"/>
+    <row r="159" ht="3.9" customHeight="1"/>
+    <row r="160" ht="3.9" customHeight="1"/>
+    <row r="161" ht="3.9" customHeight="1"/>
+    <row r="162" ht="3.9" customHeight="1"/>
+    <row r="163" ht="3.9" customHeight="1"/>
+    <row r="164" ht="3.9" customHeight="1"/>
+    <row r="165" ht="3.9" customHeight="1"/>
+    <row r="166" ht="3.9" customHeight="1"/>
+    <row r="167" ht="3.9" customHeight="1"/>
+    <row r="168" ht="3.9" customHeight="1"/>
+    <row r="169" ht="3.9" customHeight="1"/>
+    <row r="170" ht="3.9" customHeight="1"/>
+    <row r="171" ht="3.9" customHeight="1"/>
+    <row r="172" ht="3.9" customHeight="1"/>
+    <row r="173" ht="3.9" customHeight="1"/>
+    <row r="174" ht="3.9" customHeight="1"/>
+    <row r="175" ht="3.9" customHeight="1"/>
+    <row r="176" ht="3.9" customHeight="1"/>
+    <row r="177" ht="3.9" customHeight="1"/>
+    <row r="178" ht="3.9" customHeight="1"/>
+    <row r="179" ht="3.9" customHeight="1"/>
+    <row r="180" ht="3.9" customHeight="1"/>
+    <row r="181" ht="3.9" customHeight="1"/>
+    <row r="182" ht="3.9" customHeight="1"/>
+    <row r="183" ht="3.9" customHeight="1"/>
+    <row r="184" ht="3.9" customHeight="1"/>
+    <row r="185" ht="3.9" customHeight="1"/>
+    <row r="186" ht="3.9" customHeight="1"/>
+    <row r="187" ht="3.9" customHeight="1"/>
+    <row r="188" ht="3.9" customHeight="1"/>
+    <row r="189" ht="3.9" customHeight="1"/>
+    <row r="190" ht="3.9" customHeight="1"/>
+    <row r="191" ht="3.9" customHeight="1"/>
+    <row r="192" ht="3.9" customHeight="1"/>
+    <row r="193" ht="3.9" customHeight="1"/>
+    <row r="194" ht="3.9" customHeight="1"/>
+    <row r="195" ht="3.9" customHeight="1"/>
+    <row r="196" ht="3.9" customHeight="1"/>
+    <row r="197" ht="3.9" customHeight="1"/>
+    <row r="198" ht="3.9" customHeight="1"/>
+    <row r="199" ht="3.9" customHeight="1"/>
+    <row r="200" ht="3.9" customHeight="1"/>
+    <row r="201" ht="3.9" customHeight="1"/>
+    <row r="202" ht="3.9" customHeight="1"/>
+    <row r="203" ht="3.9" customHeight="1"/>
+    <row r="204" ht="3.9" customHeight="1"/>
+    <row r="205" ht="3.9" customHeight="1"/>
+    <row r="206" ht="3.9" customHeight="1"/>
+    <row r="207" ht="3.9" customHeight="1"/>
+    <row r="208" ht="3.9" customHeight="1"/>
+    <row r="209" ht="3.9" customHeight="1"/>
+    <row r="210" ht="3.9" customHeight="1"/>
+    <row r="211" ht="3.9" customHeight="1"/>
+    <row r="212" ht="3.9" customHeight="1"/>
+    <row r="213" ht="3.9" customHeight="1"/>
+    <row r="214" ht="3.9" customHeight="1"/>
+    <row r="215" ht="3.9" customHeight="1"/>
+    <row r="216" ht="3.9" customHeight="1"/>
+    <row r="217" ht="3.9" customHeight="1"/>
+    <row r="218" ht="3.9" customHeight="1"/>
+    <row r="219" ht="3.9" customHeight="1"/>
+    <row r="220" ht="3.9" customHeight="1"/>
+    <row r="221" ht="3.9" customHeight="1"/>
+    <row r="222" ht="3.9" customHeight="1"/>
+    <row r="223" ht="3.9" customHeight="1"/>
+    <row r="224" ht="3.9" customHeight="1"/>
+    <row r="225" ht="3.9" customHeight="1"/>
+    <row r="226" ht="3.9" customHeight="1"/>
+    <row r="227" ht="3.9" customHeight="1"/>
+    <row r="228" ht="3.9" customHeight="1"/>
+    <row r="229" ht="3.9" customHeight="1"/>
+    <row r="230" ht="3.9" customHeight="1"/>
+    <row r="231" ht="3.9" customHeight="1"/>
+    <row r="232" ht="3.9" customHeight="1"/>
+    <row r="233" ht="3.9" customHeight="1"/>
+    <row r="234" ht="3.9" customHeight="1"/>
+    <row r="235" ht="3.9" customHeight="1"/>
+    <row r="236" ht="3.9" customHeight="1"/>
+    <row r="237" ht="3.9" customHeight="1"/>
+    <row r="238" ht="3.9" customHeight="1"/>
+    <row r="239" ht="3.9" customHeight="1"/>
+    <row r="240" ht="3.9" customHeight="1"/>
+    <row r="241" ht="3.9" customHeight="1"/>
+    <row r="242" ht="3.9" customHeight="1"/>
+    <row r="243" ht="3.9" customHeight="1"/>
+    <row r="244" ht="3.9" customHeight="1"/>
+    <row r="245" ht="3.9" customHeight="1"/>
+    <row r="246" ht="3.9" customHeight="1"/>
+    <row r="247" ht="3.9" customHeight="1"/>
+    <row r="248" ht="3.9" customHeight="1"/>
+    <row r="249" ht="3.9" customHeight="1"/>
+    <row r="250" ht="3.9" customHeight="1"/>
+    <row r="251" ht="3.9" customHeight="1"/>
+    <row r="252" ht="3.9" customHeight="1"/>
+    <row r="253" ht="3.9" customHeight="1"/>
+    <row r="254" ht="3.9" customHeight="1"/>
+    <row r="255" ht="3.9" customHeight="1"/>
+    <row r="256" ht="3.9" customHeight="1"/>
+    <row r="257" ht="3.9" customHeight="1"/>
+    <row r="258" ht="3.9" customHeight="1"/>
+    <row r="259" ht="3.9" customHeight="1"/>
+    <row r="260" ht="3.9" customHeight="1"/>
+    <row r="261" ht="3.9" customHeight="1"/>
+    <row r="262" ht="3.9" customHeight="1"/>
+    <row r="263" ht="3.9" customHeight="1"/>
+    <row r="264" ht="3.9" customHeight="1"/>
+    <row r="265" ht="3.9" customHeight="1"/>
+    <row r="266" ht="3.9" customHeight="1"/>
+    <row r="267" ht="3.9" customHeight="1"/>
+    <row r="268" ht="3.9" customHeight="1"/>
+    <row r="269" ht="3.9" customHeight="1"/>
+    <row r="270" ht="3.9" customHeight="1"/>
+    <row r="271" ht="3.9" customHeight="1"/>
+    <row r="272" ht="3.9" customHeight="1"/>
+    <row r="273" ht="3.9" customHeight="1"/>
+    <row r="274" ht="3.9" customHeight="1"/>
+    <row r="275" ht="3.9" customHeight="1"/>
+    <row r="276" ht="3.9" customHeight="1"/>
+    <row r="277" ht="3.9" customHeight="1"/>
+    <row r="278" ht="3.9" customHeight="1"/>
+    <row r="279" ht="3.9" customHeight="1"/>
+    <row r="280" ht="3.9" customHeight="1"/>
+    <row r="281" ht="3.9" customHeight="1"/>
+    <row r="282" ht="3.9" customHeight="1"/>
+    <row r="283" ht="3.9" customHeight="1"/>
+    <row r="284" ht="3.9" customHeight="1"/>
+    <row r="285" ht="3.9" customHeight="1"/>
+    <row r="286" ht="3.9" customHeight="1"/>
+    <row r="287" ht="3.9" customHeight="1"/>
+    <row r="288" ht="3.9" customHeight="1"/>
+    <row r="289" ht="3.9" customHeight="1"/>
+    <row r="290" ht="3.9" customHeight="1"/>
+    <row r="291" ht="3.9" customHeight="1"/>
+    <row r="292" ht="3.9" customHeight="1"/>
+    <row r="293" ht="3.9" customHeight="1"/>
+    <row r="294" ht="3.9" customHeight="1"/>
+    <row r="295" ht="3.9" customHeight="1"/>
+    <row r="296" ht="3.9" customHeight="1"/>
+    <row r="297" ht="3.9" customHeight="1"/>
+    <row r="298" ht="3.9" customHeight="1"/>
+    <row r="299" ht="3.9" customHeight="1"/>
+    <row r="300" ht="3.9" customHeight="1"/>
+    <row r="301" ht="3.9" customHeight="1"/>
+    <row r="302" ht="3.9" customHeight="1"/>
+    <row r="303" ht="3.9" customHeight="1"/>
+    <row r="304" ht="3.9" customHeight="1"/>
+    <row r="305" ht="3.9" customHeight="1"/>
+    <row r="306" ht="3.9" customHeight="1"/>
+    <row r="307" ht="3.9" customHeight="1"/>
+    <row r="308" ht="3.9" customHeight="1"/>
+    <row r="309" ht="3.9" customHeight="1"/>
+    <row r="310" ht="3.9" customHeight="1"/>
+    <row r="311" ht="3.9" customHeight="1"/>
+    <row r="312" ht="3.9" customHeight="1"/>
+    <row r="313" ht="3.9" customHeight="1"/>
+    <row r="314" ht="3.9" customHeight="1"/>
+    <row r="315" ht="3.9" customHeight="1"/>
+    <row r="316" ht="3.9" customHeight="1"/>
+    <row r="317" ht="3.9" customHeight="1"/>
+    <row r="318" ht="3.9" customHeight="1"/>
+    <row r="319" ht="3.9" customHeight="1"/>
+    <row r="320" ht="3.9" customHeight="1"/>
+    <row r="321" ht="3.9" customHeight="1"/>
+    <row r="322" ht="3.9" customHeight="1"/>
+    <row r="323" ht="3.9" customHeight="1"/>
+    <row r="324" ht="3.9" customHeight="1"/>
+    <row r="325" ht="3.9" customHeight="1"/>
+    <row r="326" ht="3.9" customHeight="1"/>
+    <row r="327" ht="3.9" customHeight="1"/>
+    <row r="328" ht="3.9" customHeight="1"/>
+    <row r="329" ht="3.9" customHeight="1"/>
+    <row r="330" ht="3.9" customHeight="1"/>
+    <row r="331" ht="3.9" customHeight="1"/>
+    <row r="332" ht="3.9" customHeight="1"/>
+    <row r="333" ht="3.9" customHeight="1"/>
+    <row r="334" ht="3.9" customHeight="1"/>
+    <row r="335" ht="3.9" customHeight="1"/>
+    <row r="336" ht="3.9" customHeight="1"/>
+    <row r="337" ht="3.9" customHeight="1"/>
+    <row r="338" ht="3.9" customHeight="1"/>
+    <row r="339" ht="3.9" customHeight="1"/>
+    <row r="340" ht="3.9" customHeight="1"/>
+    <row r="341" ht="3.9" customHeight="1"/>
+    <row r="342" ht="3.9" customHeight="1"/>
+    <row r="343" ht="3.9" customHeight="1"/>
+    <row r="344" ht="3.9" customHeight="1"/>
+    <row r="345" ht="3.9" customHeight="1"/>
+    <row r="346" ht="3.9" customHeight="1"/>
+    <row r="347" ht="3.9" customHeight="1"/>
+    <row r="348" ht="3.9" customHeight="1"/>
+    <row r="349" ht="3.9" customHeight="1"/>
+    <row r="350" ht="3.9" customHeight="1"/>
+    <row r="351" ht="3.9" customHeight="1"/>
+    <row r="352" ht="3.9" customHeight="1"/>
+    <row r="353" ht="3.9" customHeight="1"/>
+    <row r="354" ht="3.9" customHeight="1"/>
+    <row r="355" ht="3.9" customHeight="1"/>
+    <row r="356" ht="3.9" customHeight="1"/>
+    <row r="357" ht="3.9" customHeight="1"/>
+    <row r="358" ht="3.9" customHeight="1"/>
+    <row r="359" ht="3.9" customHeight="1"/>
+    <row r="360" ht="3.9" customHeight="1"/>
+    <row r="361" ht="3.9" customHeight="1"/>
+    <row r="362" ht="3.9" customHeight="1"/>
+    <row r="363" ht="3.9" customHeight="1"/>
+    <row r="364" ht="3.9" customHeight="1"/>
+    <row r="365" ht="3.9" customHeight="1"/>
+    <row r="366" ht="3.9" customHeight="1"/>
+    <row r="367" ht="3.9" customHeight="1"/>
+    <row r="368" ht="3.9" customHeight="1"/>
+    <row r="369" ht="3.9" customHeight="1"/>
+    <row r="370" ht="3.9" customHeight="1"/>
+    <row r="371" ht="3.9" customHeight="1"/>
+    <row r="372" ht="3.9" customHeight="1"/>
+    <row r="373" ht="3.9" customHeight="1"/>
+    <row r="374" ht="3.9" customHeight="1"/>
+    <row r="375" ht="3.9" customHeight="1"/>
+    <row r="376" ht="3.9" customHeight="1"/>
+    <row r="377" ht="3.9" customHeight="1"/>
+    <row r="378" ht="3.9" customHeight="1"/>
+    <row r="379" ht="3.9" customHeight="1"/>
+    <row r="380" ht="3.9" customHeight="1"/>
+    <row r="381" ht="3.9" customHeight="1"/>
+    <row r="382" ht="3.9" customHeight="1"/>
+    <row r="383" ht="3.9" customHeight="1"/>
+    <row r="384" ht="3.9" customHeight="1"/>
+    <row r="385" ht="3.9" customHeight="1"/>
+    <row r="386" ht="3.9" customHeight="1"/>
+    <row r="387" ht="3.9" customHeight="1"/>
+    <row r="388" ht="3.9" customHeight="1"/>
+    <row r="389" ht="3.9" customHeight="1"/>
+    <row r="390" ht="3.9" customHeight="1"/>
+    <row r="391" ht="3.9" customHeight="1"/>
+    <row r="392" ht="3.9" customHeight="1"/>
+    <row r="393" ht="3.9" customHeight="1"/>
+    <row r="394" ht="3.9" customHeight="1"/>
+    <row r="395" ht="3.9" customHeight="1"/>
+    <row r="396" ht="3.9" customHeight="1"/>
+    <row r="397" ht="3.9" customHeight="1"/>
+    <row r="398" ht="3.9" customHeight="1"/>
+    <row r="399" ht="3.9" customHeight="1"/>
+    <row r="400" ht="3.9" customHeight="1"/>
+    <row r="401" ht="3.9" customHeight="1"/>
+    <row r="402" ht="3.9" customHeight="1"/>
+    <row r="403" ht="3.9" customHeight="1"/>
+    <row r="404" ht="3.9" customHeight="1"/>
+    <row r="405" ht="3.9" customHeight="1"/>
+    <row r="406" ht="3.9" customHeight="1"/>
+    <row r="407" ht="3.9" customHeight="1"/>
+    <row r="408" ht="3.9" customHeight="1"/>
+    <row r="409" ht="3.9" customHeight="1"/>
+    <row r="410" ht="3.9" customHeight="1"/>
+    <row r="411" ht="3.9" customHeight="1"/>
+    <row r="412" ht="3.9" customHeight="1"/>
+    <row r="413" ht="3.9" customHeight="1"/>
+    <row r="414" ht="3.9" customHeight="1"/>
+    <row r="415" ht="3.9" customHeight="1"/>
+    <row r="416" ht="3.9" customHeight="1"/>
+    <row r="417" ht="3.9" customHeight="1"/>
+    <row r="418" ht="3.9" customHeight="1"/>
+    <row r="419" ht="3.9" customHeight="1"/>
+    <row r="420" ht="3.9" customHeight="1"/>
+    <row r="421" ht="3.9" customHeight="1"/>
+    <row r="422" ht="3.9" customHeight="1"/>
+    <row r="423" ht="3.9" customHeight="1"/>
+    <row r="424" ht="3.9" customHeight="1"/>
+    <row r="425" ht="3.9" customHeight="1"/>
+    <row r="426" ht="3.9" customHeight="1"/>
+    <row r="427" ht="3.9" customHeight="1"/>
+    <row r="428" ht="3.9" customHeight="1"/>
+    <row r="429" ht="3.9" customHeight="1"/>
+    <row r="430" ht="3.9" customHeight="1"/>
+    <row r="431" ht="3.9" customHeight="1"/>
+    <row r="432" ht="3.9" customHeight="1"/>
+    <row r="433" ht="3.9" customHeight="1"/>
+    <row r="434" ht="3.9" customHeight="1"/>
+    <row r="435" ht="3.9" customHeight="1"/>
+    <row r="436" ht="3.9" customHeight="1"/>
+    <row r="437" ht="3.9" customHeight="1"/>
+    <row r="438" ht="3.9" customHeight="1"/>
+    <row r="439" ht="3.9" customHeight="1"/>
+    <row r="440" ht="3.9" customHeight="1"/>
+    <row r="441" ht="3.9" customHeight="1"/>
+    <row r="442" ht="3.9" customHeight="1"/>
+    <row r="443" ht="3.9" customHeight="1"/>
+    <row r="444" ht="3.9" customHeight="1"/>
+    <row r="445" ht="3.9" customHeight="1"/>
+    <row r="446" ht="3.9" customHeight="1"/>
+    <row r="447" ht="3.9" customHeight="1"/>
+    <row r="448" ht="3.9" customHeight="1"/>
+    <row r="449" ht="3.9" customHeight="1"/>
+    <row r="450" ht="3.9" customHeight="1"/>
+    <row r="451" ht="3.9" customHeight="1"/>
+    <row r="452" ht="3.9" customHeight="1"/>
+    <row r="453" ht="3.9" customHeight="1"/>
+    <row r="454" ht="3.9" customHeight="1"/>
+    <row r="455" ht="3.9" customHeight="1"/>
+    <row r="456" ht="3.9" customHeight="1"/>
+    <row r="457" ht="3.9" customHeight="1"/>
+    <row r="458" ht="3.9" customHeight="1"/>
+    <row r="459" ht="3.9" customHeight="1"/>
+    <row r="460" ht="3.9" customHeight="1"/>
+    <row r="461" ht="3.9" customHeight="1"/>
+    <row r="462" ht="3.9" customHeight="1"/>
+    <row r="463" ht="3.9" customHeight="1"/>
+    <row r="464" ht="3.9" customHeight="1"/>
+    <row r="465" ht="3.9" customHeight="1"/>
+    <row r="466" ht="3.9" customHeight="1"/>
+    <row r="467" ht="3.9" customHeight="1"/>
+    <row r="468" ht="3.9" customHeight="1"/>
+    <row r="469" ht="3.9" customHeight="1"/>
+    <row r="470" ht="3.9" customHeight="1"/>
+    <row r="471" ht="3.9" customHeight="1"/>
+    <row r="472" ht="3.9" customHeight="1"/>
+    <row r="473" ht="3.9" customHeight="1"/>
+    <row r="474" ht="3.9" customHeight="1"/>
+    <row r="475" ht="3.9" customHeight="1"/>
+    <row r="476" ht="3.9" customHeight="1"/>
+    <row r="477" ht="3.9" customHeight="1"/>
+    <row r="478" ht="3.9" customHeight="1"/>
+    <row r="479" ht="3.9" customHeight="1"/>
+    <row r="480" ht="3.9" customHeight="1"/>
+    <row r="481" ht="3.9" customHeight="1"/>
+    <row r="482" ht="3.9" customHeight="1"/>
+    <row r="483" ht="3.9" customHeight="1"/>
+    <row r="484" ht="3.9" customHeight="1"/>
+    <row r="485" ht="3.9" customHeight="1"/>
+    <row r="486" ht="3.9" customHeight="1"/>
+    <row r="487" ht="3.9" customHeight="1"/>
+    <row r="488" ht="3.9" customHeight="1"/>
+    <row r="489" ht="3.9" customHeight="1"/>
+    <row r="490" ht="3.9" customHeight="1"/>
+    <row r="491" ht="3.9" customHeight="1"/>
+    <row r="492" ht="3.9" customHeight="1"/>
+    <row r="493" ht="3.9" customHeight="1"/>
+    <row r="494" ht="3.9" customHeight="1"/>
+    <row r="495" ht="3.9" customHeight="1"/>
+    <row r="496" ht="3.9" customHeight="1"/>
+    <row r="497" ht="3.9" customHeight="1"/>
+    <row r="498" ht="3.9" customHeight="1"/>
+    <row r="499" ht="3.9" customHeight="1"/>
+    <row r="500" ht="3.9" customHeight="1"/>
+    <row r="501" ht="3.9" customHeight="1"/>
+    <row r="502" ht="3.9" customHeight="1"/>
+    <row r="503" ht="3.9" customHeight="1"/>
+    <row r="504" ht="3.9" customHeight="1"/>
+    <row r="505" ht="3.9" customHeight="1"/>
+    <row r="506" ht="3.9" customHeight="1"/>
+    <row r="507" ht="3.9" customHeight="1"/>
+    <row r="508" ht="3.9" customHeight="1"/>
+    <row r="509" ht="3.9" customHeight="1"/>
+    <row r="510" ht="3.9" customHeight="1"/>
+    <row r="511" ht="3.9" customHeight="1"/>
+    <row r="512" ht="3.9" customHeight="1"/>
+    <row r="513" ht="3.9" customHeight="1"/>
+    <row r="514" ht="3.9" customHeight="1"/>
+    <row r="515" ht="3.9" customHeight="1"/>
+    <row r="516" ht="3.9" customHeight="1"/>
+    <row r="517" ht="3.9" customHeight="1"/>
+    <row r="518" ht="3.9" customHeight="1"/>
+    <row r="519" ht="3.9" customHeight="1"/>
+    <row r="520" ht="3.9" customHeight="1"/>
+    <row r="521" ht="3.9" customHeight="1"/>
+    <row r="522" ht="3.9" customHeight="1"/>
+    <row r="523" ht="3.9" customHeight="1"/>
+    <row r="524" ht="3.9" customHeight="1"/>
+    <row r="525" ht="3.9" customHeight="1"/>
+    <row r="526" ht="3.9" customHeight="1"/>
+    <row r="527" ht="3.9" customHeight="1"/>
+    <row r="528" ht="3.9" customHeight="1"/>
+    <row r="529" ht="3.9" customHeight="1"/>
+    <row r="530" ht="3.9" customHeight="1"/>
+    <row r="531" ht="3.9" customHeight="1"/>
+    <row r="532" ht="3.9" customHeight="1"/>
+    <row r="533" ht="3.9" customHeight="1"/>
+    <row r="534" ht="3.9" customHeight="1"/>
+    <row r="535" ht="3.9" customHeight="1"/>
+    <row r="536" ht="3.9" customHeight="1"/>
+    <row r="537" ht="3.9" customHeight="1"/>
+    <row r="538" ht="3.9" customHeight="1"/>
+    <row r="539" ht="3.9" customHeight="1"/>
+    <row r="540" ht="3.9" customHeight="1"/>
+    <row r="541" ht="3.9" customHeight="1"/>
+    <row r="542" ht="3.9" customHeight="1"/>
+    <row r="543" ht="3.9" customHeight="1"/>
+    <row r="544" ht="3.9" customHeight="1"/>
+    <row r="545" ht="3.9" customHeight="1"/>
+    <row r="546" ht="3.9" customHeight="1"/>
+    <row r="547" ht="3.9" customHeight="1"/>
+    <row r="548" ht="3.9" customHeight="1"/>
+    <row r="549" ht="3.9" customHeight="1"/>
+    <row r="550" ht="3.9" customHeight="1"/>
+    <row r="551" ht="3.9" customHeight="1"/>
+    <row r="552" ht="3.9" customHeight="1"/>
+    <row r="553" ht="3.9" customHeight="1"/>
+    <row r="554" ht="3.9" customHeight="1"/>
+    <row r="555" ht="3.9" customHeight="1"/>
+    <row r="556" ht="3.9" customHeight="1"/>
+    <row r="557" ht="3.9" customHeight="1"/>
+    <row r="558" ht="3.9" customHeight="1"/>
+    <row r="559" ht="3.9" customHeight="1"/>
+    <row r="560" ht="3.9" customHeight="1"/>
+    <row r="561" ht="3.9" customHeight="1"/>
+    <row r="562" ht="3.9" customHeight="1"/>
+    <row r="563" ht="3.9" customHeight="1"/>
+    <row r="564" ht="3.9" customHeight="1"/>
+    <row r="565" ht="3.9" customHeight="1"/>
+    <row r="566" ht="3.9" customHeight="1"/>
+    <row r="567" ht="3.9" customHeight="1"/>
+    <row r="568" ht="3.9" customHeight="1"/>
+    <row r="569" ht="3.9" customHeight="1"/>
+    <row r="570" ht="3.9" customHeight="1"/>
+    <row r="571" ht="3.9" customHeight="1"/>
+    <row r="572" ht="3.9" customHeight="1"/>
+    <row r="573" ht="3.9" customHeight="1"/>
+    <row r="574" ht="3.9" customHeight="1"/>
+    <row r="575" ht="3.9" customHeight="1"/>
+    <row r="576" ht="3.9" customHeight="1"/>
+    <row r="577" ht="3.9" customHeight="1"/>
+    <row r="578" ht="3.9" customHeight="1"/>
+    <row r="579" ht="3.9" customHeight="1"/>
+    <row r="580" ht="3.9" customHeight="1"/>
+    <row r="581" ht="3.9" customHeight="1"/>
+    <row r="582" ht="3.9" customHeight="1"/>
+    <row r="583" ht="3.9" customHeight="1"/>
+    <row r="584" ht="3.9" customHeight="1"/>
+    <row r="585" ht="3.9" customHeight="1"/>
+    <row r="586" ht="3.9" customHeight="1"/>
+    <row r="587" ht="3.9" customHeight="1"/>
+    <row r="588" ht="3.9" customHeight="1"/>
+    <row r="589" ht="3.9" customHeight="1"/>
+    <row r="590" ht="3.9" customHeight="1"/>
+    <row r="591" ht="3.9" customHeight="1"/>
+    <row r="592" ht="3.9" customHeight="1"/>
+    <row r="593" ht="3.9" customHeight="1"/>
+    <row r="594" ht="3.9" customHeight="1"/>
+    <row r="595" ht="3.9" customHeight="1"/>
+    <row r="596" ht="3.9" customHeight="1"/>
+    <row r="597" ht="3.9" customHeight="1"/>
+    <row r="598" ht="3.9" customHeight="1"/>
+    <row r="599" ht="3.9" customHeight="1"/>
+    <row r="600" ht="3.9" customHeight="1"/>
+    <row r="601" ht="3.9" customHeight="1"/>
+    <row r="602" ht="3.9" customHeight="1"/>
+    <row r="603" ht="3.9" customHeight="1"/>
+    <row r="604" ht="3.9" customHeight="1"/>
+    <row r="605" ht="3.9" customHeight="1"/>
+    <row r="606" ht="3.9" customHeight="1"/>
+    <row r="607" ht="3.9" customHeight="1"/>
+    <row r="608" ht="3.9" customHeight="1"/>
+    <row r="609" ht="3.9" customHeight="1"/>
+    <row r="610" ht="3.9" customHeight="1"/>
+    <row r="611" ht="3.9" customHeight="1"/>
+    <row r="612" ht="3.9" customHeight="1"/>
+    <row r="613" ht="3.9" customHeight="1"/>
+    <row r="614" ht="3.9" customHeight="1"/>
+    <row r="615" ht="3.9" customHeight="1"/>
+    <row r="616" ht="3.9" customHeight="1"/>
+    <row r="617" ht="3.9" customHeight="1"/>
+    <row r="618" ht="3.9" customHeight="1"/>
+    <row r="619" ht="3.9" customHeight="1"/>
+    <row r="620" ht="3.9" customHeight="1"/>
+    <row r="621" ht="3.9" customHeight="1"/>
+    <row r="622" ht="3.9" customHeight="1"/>
+    <row r="623" ht="3.9" customHeight="1"/>
+    <row r="624" ht="3.9" customHeight="1"/>
+    <row r="625" ht="3.9" customHeight="1"/>
+    <row r="626" ht="3.9" customHeight="1"/>
+    <row r="627" ht="3.9" customHeight="1"/>
+    <row r="628" ht="3.9" customHeight="1"/>
+    <row r="629" ht="3.9" customHeight="1"/>
+    <row r="630" ht="3.9" customHeight="1"/>
+    <row r="631" ht="3.9" customHeight="1"/>
+    <row r="632" ht="3.9" customHeight="1"/>
+    <row r="633" ht="3.9" customHeight="1"/>
+    <row r="634" ht="3.9" customHeight="1"/>
+    <row r="635" ht="3.9" customHeight="1"/>
+    <row r="636" ht="3.9" customHeight="1"/>
+    <row r="637" ht="3.9" customHeight="1"/>
+    <row r="638" ht="3.9" customHeight="1"/>
+    <row r="639" ht="3.9" customHeight="1"/>
+    <row r="640" ht="3.9" customHeight="1"/>
+    <row r="641" ht="3.9" customHeight="1"/>
+    <row r="642" ht="3.9" customHeight="1"/>
+    <row r="643" ht="3.9" customHeight="1"/>
+    <row r="644" ht="3.9" customHeight="1"/>
+    <row r="645" ht="3.9" customHeight="1"/>
+    <row r="646" ht="3.9" customHeight="1"/>
+    <row r="647" ht="3.9" customHeight="1"/>
+    <row r="648" ht="3.9" customHeight="1"/>
+    <row r="649" ht="3.9" customHeight="1"/>
+    <row r="650" ht="3.9" customHeight="1"/>
+    <row r="651" ht="3.9" customHeight="1"/>
+    <row r="652" ht="3.9" customHeight="1"/>
+    <row r="653" ht="3.9" customHeight="1"/>
+    <row r="654" ht="3.9" customHeight="1"/>
+    <row r="655" ht="3.9" customHeight="1"/>
+    <row r="656" ht="3.9" customHeight="1"/>
+    <row r="657" ht="3.9" customHeight="1"/>
+    <row r="658" ht="3.9" customHeight="1"/>
+    <row r="659" ht="3.9" customHeight="1"/>
+    <row r="660" ht="3.9" customHeight="1"/>
+    <row r="661" ht="3.9" customHeight="1"/>
+    <row r="662" ht="3.9" customHeight="1"/>
+    <row r="663" ht="3.9" customHeight="1"/>
+    <row r="664" ht="3.9" customHeight="1"/>
+    <row r="665" ht="3.9" customHeight="1"/>
+    <row r="666" ht="3.9" customHeight="1"/>
+    <row r="667" ht="3.9" customHeight="1"/>
+    <row r="668" ht="3.9" customHeight="1"/>
+    <row r="669" ht="3.9" customHeight="1"/>
+    <row r="670" ht="3.9" customHeight="1"/>
+    <row r="671" ht="3.9" customHeight="1"/>
+    <row r="672" ht="3.9" customHeight="1"/>
+    <row r="673" ht="3.9" customHeight="1"/>
+    <row r="674" ht="3.9" customHeight="1"/>
+    <row r="675" ht="3.9" customHeight="1"/>
+    <row r="676" ht="3.9" customHeight="1"/>
+    <row r="677" ht="3.9" customHeight="1"/>
+    <row r="678" ht="3.9" customHeight="1"/>
+    <row r="679" ht="3.9" customHeight="1"/>
+    <row r="680" ht="3.9" customHeight="1"/>
+    <row r="681" ht="3.9" customHeight="1"/>
+    <row r="682" ht="3.9" customHeight="1"/>
+    <row r="683" ht="3.9" customHeight="1"/>
+    <row r="684" ht="3.9" customHeight="1"/>
+    <row r="685" ht="3.9" customHeight="1"/>
+    <row r="686" ht="3.9" customHeight="1"/>
+    <row r="687" ht="3.9" customHeight="1"/>
+    <row r="688" ht="3.9" customHeight="1"/>
+    <row r="689" ht="3.9" customHeight="1"/>
+    <row r="690" ht="3.9" customHeight="1"/>
+    <row r="691" ht="3.9" customHeight="1"/>
+    <row r="692" ht="3.9" customHeight="1"/>
+    <row r="693" ht="3.9" customHeight="1"/>
+    <row r="694" ht="3.9" customHeight="1"/>
+    <row r="695" ht="3.9" customHeight="1"/>
+    <row r="696" ht="3.9" customHeight="1"/>
+    <row r="697" ht="3.9" customHeight="1"/>
+    <row r="698" ht="3.9" customHeight="1"/>
+    <row r="699" ht="3.9" customHeight="1"/>
+    <row r="700" ht="3.9" customHeight="1"/>
+    <row r="701" ht="3.9" customHeight="1"/>
+    <row r="702" ht="3.9" customHeight="1"/>
+    <row r="703" ht="3.9" customHeight="1"/>
+    <row r="704" ht="3.9" customHeight="1"/>
+    <row r="705" ht="3.9" customHeight="1"/>
+    <row r="706" ht="3.9" customHeight="1"/>
+    <row r="707" ht="3.9" customHeight="1"/>
+    <row r="708" ht="3.9" customHeight="1"/>
+    <row r="709" ht="3.9" customHeight="1"/>
+    <row r="710" ht="3.9" customHeight="1"/>
+    <row r="711" ht="3.9" customHeight="1"/>
+    <row r="712" ht="3.9" customHeight="1"/>
+    <row r="713" ht="3.9" customHeight="1"/>
+    <row r="714" ht="3.9" customHeight="1"/>
+    <row r="715" ht="3.9" customHeight="1"/>
+    <row r="716" ht="3.9" customHeight="1"/>
+    <row r="717" ht="3.9" customHeight="1"/>
+    <row r="718" ht="3.9" customHeight="1"/>
+    <row r="719" ht="3.9" customHeight="1"/>
+    <row r="720" ht="3.9" customHeight="1"/>
+    <row r="721" ht="3.9" customHeight="1"/>
+    <row r="722" ht="3.9" customHeight="1"/>
+    <row r="723" ht="3.9" customHeight="1"/>
+    <row r="724" ht="3.9" customHeight="1"/>
+    <row r="725" ht="3.9" customHeight="1"/>
+    <row r="726" ht="3.9" customHeight="1"/>
+    <row r="727" ht="3.9" customHeight="1"/>
+    <row r="728" ht="3.9" customHeight="1"/>
+    <row r="729" ht="3.9" customHeight="1"/>
+    <row r="730" ht="3.9" customHeight="1"/>
+    <row r="731" ht="3.9" customHeight="1"/>
+    <row r="732" ht="3.9" customHeight="1"/>
+    <row r="733" ht="3.9" customHeight="1"/>
+    <row r="734" ht="3.9" customHeight="1"/>
+    <row r="735" ht="3.9" customHeight="1"/>
+    <row r="736" ht="3.9" customHeight="1"/>
+    <row r="737" ht="3.9" customHeight="1"/>
+    <row r="738" ht="3.9" customHeight="1"/>
+    <row r="739" ht="3.9" customHeight="1"/>
+    <row r="740" ht="3.9" customHeight="1"/>
+    <row r="741" ht="3.9" customHeight="1"/>
+    <row r="742" ht="3.9" customHeight="1"/>
+    <row r="743" ht="3.9" customHeight="1"/>
+    <row r="744" ht="3.9" customHeight="1"/>
+    <row r="745" ht="3.9" customHeight="1"/>
+    <row r="746" ht="3.9" customHeight="1"/>
+    <row r="747" ht="3.9" customHeight="1"/>
+    <row r="748" ht="3.9" customHeight="1"/>
+    <row r="749" ht="3.9" customHeight="1"/>
+    <row r="750" ht="3.9" customHeight="1"/>
+    <row r="751" ht="3.9" customHeight="1"/>
+    <row r="752" ht="3.9" customHeight="1"/>
+    <row r="753" ht="3.9" customHeight="1"/>
+    <row r="754" ht="3.9" customHeight="1"/>
+    <row r="755" ht="3.9" customHeight="1"/>
+    <row r="756" ht="3.9" customHeight="1"/>
+    <row r="757" ht="3.9" customHeight="1"/>
+    <row r="758" ht="3.9" customHeight="1"/>
+    <row r="759" ht="3.9" customHeight="1"/>
+    <row r="760" ht="3.9" customHeight="1"/>
+    <row r="761" ht="3.9" customHeight="1"/>
+    <row r="762" ht="3.9" customHeight="1"/>
+    <row r="763" ht="3.9" customHeight="1"/>
+    <row r="764" ht="3.9" customHeight="1"/>
+    <row r="765" ht="3.9" customHeight="1"/>
+    <row r="766" ht="3.9" customHeight="1"/>
+    <row r="767" ht="3.9" customHeight="1"/>
+    <row r="768" ht="3.9" customHeight="1"/>
+    <row r="769" ht="3.9" customHeight="1"/>
+    <row r="770" ht="3.9" customHeight="1"/>
+    <row r="771" ht="3.9" customHeight="1"/>
+    <row r="772" ht="3.9" customHeight="1"/>
+    <row r="773" ht="3.9" customHeight="1"/>
+    <row r="774" ht="3.9" customHeight="1"/>
+    <row r="775" ht="3.9" customHeight="1"/>
+    <row r="776" ht="3.9" customHeight="1"/>
+    <row r="777" ht="3.9" customHeight="1"/>
+    <row r="778" ht="3.9" customHeight="1"/>
+    <row r="779" ht="3.9" customHeight="1"/>
+    <row r="780" ht="3.9" customHeight="1"/>
+    <row r="781" ht="3.9" customHeight="1"/>
+    <row r="782" ht="3.9" customHeight="1"/>
+    <row r="783" ht="3.9" customHeight="1"/>
+    <row r="784" ht="3.9" customHeight="1"/>
+    <row r="785" ht="3.9" customHeight="1"/>
+    <row r="786" ht="3.9" customHeight="1"/>
+    <row r="787" ht="3.9" customHeight="1"/>
+    <row r="788" ht="3.9" customHeight="1"/>
+    <row r="789" ht="3.9" customHeight="1"/>
+    <row r="790" ht="3.9" customHeight="1"/>
+    <row r="791" ht="3.9" customHeight="1"/>
+    <row r="792" ht="3.9" customHeight="1"/>
+    <row r="793" ht="3.9" customHeight="1"/>
+    <row r="794" ht="3.9" customHeight="1"/>
+    <row r="795" ht="3.9" customHeight="1"/>
+    <row r="796" ht="3.9" customHeight="1"/>
+    <row r="797" ht="3.9" customHeight="1"/>
+    <row r="798" ht="3.9" customHeight="1"/>
+    <row r="799" ht="3.9" customHeight="1"/>
+    <row r="800" ht="3.9" customHeight="1"/>
+    <row r="801" ht="3.9" customHeight="1"/>
+    <row r="802" ht="3.9" customHeight="1"/>
+    <row r="803" ht="3.9" customHeight="1"/>
+    <row r="804" ht="3.9" customHeight="1"/>
+    <row r="805" ht="3.9" customHeight="1"/>
+    <row r="806" ht="3.9" customHeight="1"/>
+    <row r="807" ht="3.9" customHeight="1"/>
+    <row r="808" ht="3.9" customHeight="1"/>
+    <row r="809" ht="3.9" customHeight="1"/>
+    <row r="810" ht="3.9" customHeight="1"/>
+    <row r="811" ht="3.9" customHeight="1"/>
+    <row r="812" ht="3.9" customHeight="1"/>
+    <row r="813" ht="3.9" customHeight="1"/>
+    <row r="814" ht="3.9" customHeight="1"/>
+    <row r="815" ht="3.9" customHeight="1"/>
+    <row r="816" ht="3.9" customHeight="1"/>
+    <row r="817" ht="3.9" customHeight="1"/>
+    <row r="818" ht="3.9" customHeight="1"/>
+    <row r="819" ht="3.9" customHeight="1"/>
+    <row r="820" ht="3.9" customHeight="1"/>
+    <row r="821" ht="3.9" customHeight="1"/>
+    <row r="822" ht="3.9" customHeight="1"/>
+    <row r="823" ht="3.9" customHeight="1"/>
+    <row r="824" ht="3.9" customHeight="1"/>
+    <row r="825" ht="3.9" customHeight="1"/>
+    <row r="826" ht="3.9" customHeight="1"/>
+    <row r="827" ht="3.9" customHeight="1"/>
+    <row r="828" ht="3.9" customHeight="1"/>
+    <row r="829" ht="3.9" customHeight="1"/>
+    <row r="830" ht="3.9" customHeight="1"/>
+    <row r="831" ht="3.9" customHeight="1"/>
+    <row r="832" ht="3.9" customHeight="1"/>
+    <row r="833" ht="3.9" customHeight="1"/>
+    <row r="834" ht="3.9" customHeight="1"/>
+    <row r="835" ht="3.9" customHeight="1"/>
+    <row r="836" ht="3.9" customHeight="1"/>
+    <row r="837" ht="3.9" customHeight="1"/>
+    <row r="838" ht="3.9" customHeight="1"/>
+    <row r="839" ht="3.9" customHeight="1"/>
+    <row r="840" ht="3.9" customHeight="1"/>
+    <row r="841" ht="3.9" customHeight="1"/>
+    <row r="842" ht="3.9" customHeight="1"/>
+    <row r="843" ht="3.9" customHeight="1"/>
+    <row r="844" ht="3.9" customHeight="1"/>
+    <row r="845" ht="3.9" customHeight="1"/>
+    <row r="846" ht="3.9" customHeight="1"/>
+    <row r="847" ht="3.9" customHeight="1"/>
+    <row r="848" ht="3.9" customHeight="1"/>
+    <row r="849" ht="3.9" customHeight="1"/>
+    <row r="850" ht="3.9" customHeight="1"/>
+    <row r="851" ht="3.9" customHeight="1"/>
+    <row r="852" ht="3.9" customHeight="1"/>
+    <row r="853" ht="3.9" customHeight="1"/>
+    <row r="854" ht="3.9" customHeight="1"/>
+    <row r="855" ht="3.9" customHeight="1"/>
+    <row r="856" ht="3.9" customHeight="1"/>
+    <row r="857" ht="3.9" customHeight="1"/>
+    <row r="858" ht="3.9" customHeight="1"/>
+    <row r="859" ht="3.9" customHeight="1"/>
+    <row r="860" ht="3.9" customHeight="1"/>
+    <row r="861" ht="3.9" customHeight="1"/>
+    <row r="862" ht="3.9" customHeight="1"/>
+    <row r="863" ht="3.9" customHeight="1"/>
+    <row r="864" ht="3.9" customHeight="1"/>
+    <row r="865" ht="3.9" customHeight="1"/>
+    <row r="866" ht="3.9" customHeight="1"/>
+    <row r="867" ht="3.9" customHeight="1"/>
+    <row r="868" ht="3.9" customHeight="1"/>
+    <row r="869" ht="3.9" customHeight="1"/>
+    <row r="870" ht="3.9" customHeight="1"/>
+    <row r="871" ht="3.9" customHeight="1"/>
+    <row r="872" ht="3.9" customHeight="1"/>
+    <row r="873" ht="3.9" customHeight="1"/>
+    <row r="874" ht="3.9" customHeight="1"/>
+    <row r="875" ht="3.9" customHeight="1"/>
+    <row r="876" ht="3.9" customHeight="1"/>
+    <row r="877" ht="3.9" customHeight="1"/>
+    <row r="878" ht="3.9" customHeight="1"/>
+    <row r="879" ht="3.9" customHeight="1"/>
+    <row r="880" ht="3.9" customHeight="1"/>
+    <row r="881" ht="3.9" customHeight="1"/>
+    <row r="882" ht="3.9" customHeight="1"/>
+    <row r="883" ht="3.9" customHeight="1"/>
+    <row r="884" ht="3.9" customHeight="1"/>
+    <row r="885" ht="3.9" customHeight="1"/>
+    <row r="886" ht="3.9" customHeight="1"/>
+    <row r="887" ht="3.9" customHeight="1"/>
+    <row r="888" ht="3.9" customHeight="1"/>
+    <row r="889" ht="3.9" customHeight="1"/>
+    <row r="890" ht="3.9" customHeight="1"/>
+    <row r="891" ht="3.9" customHeight="1"/>
+    <row r="892" ht="3.9" customHeight="1"/>
+    <row r="893" ht="3.9" customHeight="1"/>
+    <row r="894" ht="3.9" customHeight="1"/>
+    <row r="895" ht="3.9" customHeight="1"/>
+    <row r="896" ht="3.9" customHeight="1"/>
+    <row r="897" ht="3.9" customHeight="1"/>
+    <row r="898" ht="3.9" customHeight="1"/>
+    <row r="899" ht="3.9" customHeight="1"/>
+    <row r="900" ht="3.9" customHeight="1"/>
+    <row r="901" ht="3.9" customHeight="1"/>
+    <row r="902" ht="3.9" customHeight="1"/>
+    <row r="903" ht="3.9" customHeight="1"/>
+    <row r="904" ht="3.9" customHeight="1"/>
+    <row r="905" ht="3.9" customHeight="1"/>
+    <row r="906" ht="3.9" customHeight="1"/>
+    <row r="907" ht="3.9" customHeight="1"/>
+    <row r="908" ht="3.9" customHeight="1"/>
+    <row r="909" ht="3.9" customHeight="1"/>
+    <row r="910" ht="3.9" customHeight="1"/>
+    <row r="911" ht="3.9" customHeight="1"/>
+    <row r="912" ht="3.9" customHeight="1"/>
+    <row r="913" ht="3.9" customHeight="1"/>
+    <row r="914" ht="3.9" customHeight="1"/>
+    <row r="915" ht="3.9" customHeight="1"/>
+    <row r="916" ht="3.9" customHeight="1"/>
+    <row r="917" ht="3.9" customHeight="1"/>
+    <row r="918" ht="3.9" customHeight="1"/>
+    <row r="919" ht="3.9" customHeight="1"/>
+    <row r="920" ht="3.9" customHeight="1"/>
+    <row r="921" ht="3.9" customHeight="1"/>
+    <row r="922" ht="3.9" customHeight="1"/>
+    <row r="923" ht="3.9" customHeight="1"/>
+    <row r="924" ht="3.9" customHeight="1"/>
+    <row r="925" ht="3.9" customHeight="1"/>
+    <row r="926" ht="3.9" customHeight="1"/>
+    <row r="927" ht="3.9" customHeight="1"/>
+    <row r="928" ht="3.9" customHeight="1"/>
+    <row r="929" ht="3.9" customHeight="1"/>
+    <row r="930" ht="3.9" customHeight="1"/>
+    <row r="931" ht="3.9" customHeight="1"/>
+    <row r="932" ht="3.9" customHeight="1"/>
+    <row r="933" ht="3.9" customHeight="1"/>
+    <row r="934" ht="3.9" customHeight="1"/>
+    <row r="935" ht="3.9" customHeight="1"/>
+    <row r="936" ht="3.9" customHeight="1"/>
+    <row r="937" ht="3.9" customHeight="1"/>
+    <row r="938" ht="3.9" customHeight="1"/>
+    <row r="939" ht="3.9" customHeight="1"/>
+    <row r="940" ht="3.9" customHeight="1"/>
+    <row r="941" ht="3.9" customHeight="1"/>
+    <row r="942" ht="3.9" customHeight="1"/>
+    <row r="943" ht="3.9" customHeight="1"/>
+    <row r="944" ht="3.9" customHeight="1"/>
+    <row r="945" ht="3.9" customHeight="1"/>
+    <row r="946" ht="3.9" customHeight="1"/>
+    <row r="947" ht="3.9" customHeight="1"/>
+    <row r="948" ht="3.9" customHeight="1"/>
+    <row r="949" ht="3.9" customHeight="1"/>
+    <row r="950" ht="3.9" customHeight="1"/>
+    <row r="951" ht="3.9" customHeight="1"/>
+    <row r="952" ht="3.9" customHeight="1"/>
+    <row r="953" ht="3.9" customHeight="1"/>
+    <row r="954" ht="3.9" customHeight="1"/>
+    <row r="955" ht="3.9" customHeight="1"/>
+    <row r="956" ht="3.9" customHeight="1"/>
+    <row r="957" ht="3.9" customHeight="1"/>
+    <row r="958" ht="3.9" customHeight="1"/>
+    <row r="959" ht="3.9" customHeight="1"/>
+    <row r="960" ht="3.9" customHeight="1"/>
+    <row r="961" ht="3.9" customHeight="1"/>
+    <row r="962" ht="3.9" customHeight="1"/>
+    <row r="963" ht="3.9" customHeight="1"/>
+    <row r="964" ht="3.9" customHeight="1"/>
+    <row r="965" ht="3.9" customHeight="1"/>
+    <row r="966" ht="3.9" customHeight="1"/>
+    <row r="967" ht="3.9" customHeight="1"/>
+    <row r="968" ht="3.9" customHeight="1"/>
+    <row r="969" ht="3.9" customHeight="1"/>
+    <row r="970" ht="3.9" customHeight="1"/>
+    <row r="971" ht="3.9" customHeight="1"/>
+    <row r="972" ht="3.9" customHeight="1"/>
+    <row r="973" ht="3.9" customHeight="1"/>
+    <row r="974" ht="3.9" customHeight="1"/>
+    <row r="975" ht="3.9" customHeight="1"/>
+    <row r="976" ht="3.9" customHeight="1"/>
+    <row r="977" ht="3.9" customHeight="1"/>
+    <row r="978" ht="3.9" customHeight="1"/>
+    <row r="979" ht="3.9" customHeight="1"/>
+    <row r="980" ht="3.9" customHeight="1"/>
+    <row r="981" ht="3.9" customHeight="1"/>
+    <row r="982" ht="3.9" customHeight="1"/>
+    <row r="983" ht="3.9" customHeight="1"/>
+    <row r="984" ht="3.9" customHeight="1"/>
+    <row r="985" ht="3.9" customHeight="1"/>
+    <row r="986" ht="3.9" customHeight="1"/>
+    <row r="987" ht="3.9" customHeight="1"/>
+    <row r="988" ht="3.9" customHeight="1"/>
+    <row r="989" ht="3.9" customHeight="1"/>
+    <row r="990" ht="3.9" customHeight="1"/>
+    <row r="991" ht="3.9" customHeight="1"/>
+    <row r="992" ht="3.9" customHeight="1"/>
+    <row r="993" ht="3.9" customHeight="1"/>
+    <row r="994" ht="3.9" customHeight="1"/>
+    <row r="995" ht="3.9" customHeight="1"/>
+    <row r="996" ht="3.9" customHeight="1"/>
+    <row r="997" ht="3.9" customHeight="1"/>
+    <row r="998" ht="3.9" customHeight="1"/>
+    <row r="999" ht="3.9" customHeight="1"/>
+    <row r="1000" ht="3.9" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="I1:J1"/>
@@ -2782,8 +2797,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -2799,72 +2814,72 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="M1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E2" s="13">
         <v>2</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G2" s="14" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I2" s="25">
         <v>0</v>
@@ -2872,43 +2887,43 @@
       <c r="J2" s="25">
         <v>0</v>
       </c>
-      <c r="K2" s="35">
+      <c r="K2" s="36">
         <v>20</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="37">
         <v>2</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="36">
         <v>2</v>
       </c>
-      <c r="N2" s="36">
+      <c r="N2" s="37">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E3" s="19">
         <v>3</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G3" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I3" s="26">
         <v>0</v>
@@ -2916,31 +2931,31 @@
       <c r="J3" s="26">
         <v>0</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="36">
         <v>18</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="37">
         <v>1.3</v>
       </c>
-      <c r="M3" s="35">
-        <v>0</v>
-      </c>
-      <c r="N3" s="36">
+      <c r="M3" s="36">
+        <v>0</v>
+      </c>
+      <c r="N3" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E4" s="13">
         <v>1</v>
@@ -2950,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I4" s="25">
         <v>0</v>
@@ -2958,43 +2973,43 @@
       <c r="J4" s="25">
         <v>0</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="36">
         <v>15</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="37">
         <v>1.4</v>
       </c>
-      <c r="M4" s="35">
-        <v>0</v>
-      </c>
-      <c r="N4" s="36">
+      <c r="M4" s="36">
+        <v>0</v>
+      </c>
+      <c r="N4" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" s="19">
         <v>2</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G5" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I5" s="26">
         <v>0</v>
@@ -3002,31 +3017,31 @@
       <c r="J5" s="26">
         <v>0</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="36">
         <v>30</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="37">
         <v>2</v>
       </c>
-      <c r="M5" s="35">
-        <v>0</v>
-      </c>
-      <c r="N5" s="36">
+      <c r="M5" s="36">
+        <v>0</v>
+      </c>
+      <c r="N5" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E6" s="13">
         <v>2</v>
@@ -3036,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I6" s="25">
         <v>0</v>
@@ -3044,43 +3059,43 @@
       <c r="J6" s="25">
         <v>0</v>
       </c>
-      <c r="K6" s="35">
-        <v>0</v>
-      </c>
-      <c r="L6" s="36">
-        <v>0</v>
-      </c>
-      <c r="M6" s="35">
-        <v>0</v>
-      </c>
-      <c r="N6" s="36">
+      <c r="K6" s="36">
+        <v>0</v>
+      </c>
+      <c r="L6" s="37">
+        <v>0</v>
+      </c>
+      <c r="M6" s="36">
+        <v>0</v>
+      </c>
+      <c r="N6" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E7" s="19">
         <v>3</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G7" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I7" s="26">
         <v>0</v>
@@ -3088,43 +3103,43 @@
       <c r="J7" s="26">
         <v>0</v>
       </c>
-      <c r="K7" s="35">
-        <v>0</v>
-      </c>
-      <c r="L7" s="36">
-        <v>0</v>
-      </c>
-      <c r="M7" s="35">
+      <c r="K7" s="36">
+        <v>0</v>
+      </c>
+      <c r="L7" s="37">
+        <v>0</v>
+      </c>
+      <c r="M7" s="36">
         <v>12</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E8" s="13">
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G8" s="14" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I8" s="25">
         <v>0</v>
@@ -3132,43 +3147,43 @@
       <c r="J8" s="25">
         <v>0</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="36">
         <v>25</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="37">
         <v>1.6</v>
       </c>
-      <c r="M8" s="35">
-        <v>0</v>
-      </c>
-      <c r="N8" s="36">
+      <c r="M8" s="36">
+        <v>0</v>
+      </c>
+      <c r="N8" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E9" s="19">
         <v>4</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G9" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I9" s="26">
         <v>0</v>
@@ -3176,290 +3191,314 @@
       <c r="J9" s="26">
         <v>0</v>
       </c>
-      <c r="K9" s="35">
+      <c r="K9" s="36">
         <v>20</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="37">
         <v>1.5</v>
       </c>
-      <c r="M9" s="35">
-        <v>0</v>
-      </c>
-      <c r="N9" s="36">
+      <c r="M9" s="36">
+        <v>0</v>
+      </c>
+      <c r="N9" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="36">
+        <v>12</v>
+      </c>
+      <c r="L10" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="36">
+        <v>0</v>
+      </c>
+      <c r="N10" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="30" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="19">
+        <v>3</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="26">
+        <v>0</v>
+      </c>
+      <c r="J11" s="26">
+        <v>0</v>
+      </c>
+      <c r="K11" s="36">
+        <v>0</v>
+      </c>
+      <c r="L11" s="37">
+        <v>0</v>
+      </c>
+      <c r="M11" s="36">
+        <v>0</v>
+      </c>
+      <c r="N11" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="13">
+        <v>3</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="25">
+        <v>0</v>
+      </c>
+      <c r="J12" s="25">
+        <v>0</v>
+      </c>
+      <c r="K12" s="36">
+        <v>0</v>
+      </c>
+      <c r="L12" s="37">
+        <v>0</v>
+      </c>
+      <c r="M12" s="36">
+        <v>0</v>
+      </c>
+      <c r="N12" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="30" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="C13" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="19">
-        <v>3</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="20" t="b">
+      <c r="D13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="21">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="26">
-        <v>0</v>
-      </c>
-      <c r="J10" s="26">
-        <v>0</v>
-      </c>
-      <c r="K10" s="35">
-        <v>0</v>
-      </c>
-      <c r="L10" s="36">
-        <v>0</v>
-      </c>
-      <c r="M10" s="35">
-        <v>0</v>
-      </c>
-      <c r="N10" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="H13" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="26">
+        <v>100</v>
+      </c>
+      <c r="J13" s="26">
+        <v>0</v>
+      </c>
+      <c r="K13" s="36">
+        <v>0</v>
+      </c>
+      <c r="L13" s="37">
+        <v>0</v>
+      </c>
+      <c r="M13" s="36">
+        <v>0</v>
+      </c>
+      <c r="N13" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="30" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="13">
-        <v>3</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="14" t="b">
+      <c r="E14" s="23">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="25">
-        <v>0</v>
-      </c>
-      <c r="J11" s="25">
-        <v>0</v>
-      </c>
-      <c r="K11" s="35">
-        <v>0</v>
-      </c>
-      <c r="L11" s="36">
-        <v>0</v>
-      </c>
-      <c r="M11" s="35">
-        <v>0</v>
-      </c>
-      <c r="N11" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="H14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="21">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="22" t="b">
+      <c r="I14" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="J14" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="K14" s="36">
+        <v>0</v>
+      </c>
+      <c r="L14" s="37">
+        <v>0</v>
+      </c>
+      <c r="M14" s="36">
+        <v>0</v>
+      </c>
+      <c r="N14" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="30" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="21">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="26">
-        <v>100</v>
-      </c>
-      <c r="J12" s="26">
-        <v>0</v>
-      </c>
-      <c r="K12" s="35">
-        <v>0</v>
-      </c>
-      <c r="L12" s="36">
-        <v>0</v>
-      </c>
-      <c r="M12" s="35">
-        <v>0</v>
-      </c>
-      <c r="N12" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="30" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="H15" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="24" t="b">
+      <c r="I15" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="26">
         <v>1</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="25">
-        <v>0.05</v>
-      </c>
-      <c r="J13" s="25">
-        <v>0.75</v>
-      </c>
-      <c r="K13" s="35">
-        <v>0</v>
-      </c>
-      <c r="L13" s="36">
-        <v>0</v>
-      </c>
-      <c r="M13" s="35">
-        <v>0</v>
-      </c>
-      <c r="N13" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="30" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="21">
-        <v>0</v>
-      </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="22" t="b">
+      <c r="K15" s="36">
+        <v>0</v>
+      </c>
+      <c r="L15" s="37">
+        <v>0</v>
+      </c>
+      <c r="M15" s="36">
+        <v>0</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="I14" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="J14" s="26">
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="K14" s="35">
-        <v>0</v>
-      </c>
-      <c r="L14" s="36">
-        <v>0</v>
-      </c>
-      <c r="M14" s="35">
-        <v>0</v>
-      </c>
-      <c r="N14" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="H15" xr:uid="{00000000-0002-0000-0100-000004000000}">
-      <formula1>"None,MaxHp,DamageReduction,HealingReceived,AttackPowerLevel"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D2:D199" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Active,StatUpgrade"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="E2:E199" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" sqref="E2:E200" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>1</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G199" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="G2:G200" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H14" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" sqref="H2:H15" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"None,MaxHp,DamageReduction,HealingReceived"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H16" xr:uid="{00000000-0002-0000-0100-000004000000}">
+      <formula1>"None,MaxHp,DamageReduction,HealingReceived,AttackPowerLevel"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3472,46 +3511,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.05" customHeight="1">
       <c r="A2" s="28" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B2" s="30">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1">
+    <row r="3" spans="1:2" ht="28.05" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B3" s="31">
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1">
+    <row r="4" spans="1:2" ht="28.05" customHeight="1">
       <c r="A4" s="28" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B4" s="30">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1">
+    <row r="5" spans="1:2" ht="28.05" customHeight="1">
       <c r="A5" s="29" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B5" s="31">
         <v>0.2</v>

--- a/GameData/GameData_Skill.xlsx
+++ b/GameData/GameData_Skill.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09dcef194f9948e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillInfo" sheetId="2" r:id="Rc43e349b4b494049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JudgementBalance" sheetId="3" r:id="Radd8d132a72543a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1d18d7f88274525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillInfo" sheetId="2" r:id="R26a6413f35094252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JudgementBalance" sheetId="3" r:id="Rcc92a799222047d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2721,7 +2721,7 @@
     <x:col min="3" max="3" width="56" customWidth="1"/>
     <x:col min="4" max="4" width="16" customWidth="1"/>
     <x:col min="5" max="5" width="9" customWidth="1"/>
-    <x:col min="6" max="6" width="28" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10" customWidth="1"/>
     <x:col min="8" max="8" width="22" customWidth="1"/>
     <x:col min="9" max="10" width="13" customWidth="1"/>
@@ -2852,7 +2852,9 @@
       <x:c r="E4" s="13">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="12"/>
+      <x:c r="F4" s="12" t="str">
+        <x:v>Assets/Image/skill_003.png</x:v>
+      </x:c>
       <x:c r="G4" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -2922,7 +2924,9 @@
       <x:c r="E6" s="13">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F6" s="12"/>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Assets/Image/skill_005.png</x:v>
+      </x:c>
       <x:c r="G6" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -3116,7 +3120,9 @@
       <x:c r="E12" s="13">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F12" s="12"/>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Assets/Image/Caffeine addiction.png</x:v>
+      </x:c>
       <x:c r="G12" s="14" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -3150,7 +3156,9 @@
       <x:c r="E13" s="21">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="15"/>
+      <x:c r="F13" s="15" t="str">
+        <x:v>Assets/Image/stat_001.png</x:v>
+      </x:c>
       <x:c r="G13" s="22" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -3184,7 +3192,9 @@
       <x:c r="E14" s="23">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="9"/>
+      <x:c r="F14" s="9" t="str">
+        <x:v>Assets/Image/stat_002.png</x:v>
+      </x:c>
       <x:c r="G14" s="24" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -3218,7 +3228,9 @@
       <x:c r="E15" s="21">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="15"/>
+      <x:c r="F15" s="15" t="str">
+        <x:v>Assets/Image/stat_003.png</x:v>
+      </x:c>
       <x:c r="G15" s="22" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -3251,6 +3263,9 @@
       </x:c>
       <x:c r="E16">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Assets/Image/stat_004.png</x:v>
       </x:c>
       <x:c r="G16" s="38" t="b">
         <x:v>1</x:v>
@@ -3290,7 +3305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93788cf9b4174204"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5114341a5c046cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
